--- a/Kedarnath_final_kobo.xlsx
+++ b/Kedarnath_final_kobo.xlsx
@@ -768,7 +768,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>'2026-10-03.c8aeef'</t>
+          <t>'2026-10-05.c8aeef'</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -11743,7 +11743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E329"/>
+  <dimension ref="A1:E327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14145,7 +14145,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>gpserr</t>
+          <t>hohrel</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -14153,12 +14153,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Location not allowed in the browser</t>
+          <t>Self (respondent is the head)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ब्राउज़र में स्थान की अनुमति नहीं</t>
+          <t>मैं खुद मुखिया हूँ</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -14168,7 +14168,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>gpserr</t>
+          <t>hohrel</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -14176,12 +14176,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>No fix obtained</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>कोई स्थान नहीं मिला</t>
+          <t>पति</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -14195,20 +14195,20 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Self (respondent is the head)</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>मैं खुद मुखिया हूँ</t>
+          <t>पत्नी</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -14218,20 +14218,20 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>पति</t>
+          <t>पिता</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109">
@@ -14241,20 +14241,20 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>पत्नी</t>
+          <t>माता</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110">
@@ -14264,20 +14264,20 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>पिता</t>
+          <t>बेटा</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111">
@@ -14287,20 +14287,20 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>माता</t>
+          <t>बेटी</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112">
@@ -14310,20 +14310,20 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>बेटा</t>
+          <t>भाई</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113">
@@ -14333,20 +14333,20 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>बेटी</t>
+          <t>बहन</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114">
@@ -14356,20 +14356,20 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Other male relative</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>भाई</t>
+          <t>कोई और पुरुष रिश्तेदार</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="115">
@@ -14379,20 +14379,20 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Other female relative</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>बहन</t>
+          <t>कोई और महिला रिश्तेदार</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="116">
@@ -14402,20 +14402,20 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Other male relative</t>
+          <t>Other, non-relative (male)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>कोई और पुरुष रिश्तेदार</t>
+          <t>रिश्तेदार नहीं, पुरुष</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="117">
@@ -14425,66 +14425,66 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Other female relative</t>
+          <t>Other, non-relative (female)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>कोई और महिला रिश्तेदार</t>
+          <t>रिश्तेदार नहीं, महिला</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>hohrel</t>
+          <t>jobperm</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Other, non-relative (male)</t>
+          <t>Permanent</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>रिश्तेदार नहीं, पुरुष</t>
+          <t>पक्का</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>hohrel</t>
+          <t>jobperm</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Other, non-relative (female)</t>
+          <t>Seasonal or temporary</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>रिश्तेदार नहीं, महिला</t>
+          <t>मौसमी या कुछ समय का</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
@@ -14494,20 +14494,20 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Permanent</t>
+          <t>Occasional or casual</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>पक्का</t>
+          <t>कभी-कभार का</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
@@ -14517,20 +14517,20 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Seasonal or temporary</t>
+          <t>On probation</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>मौसमी या कुछ समय का</t>
+          <t>परखने की अवधि पर</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122">
@@ -14540,66 +14540,66 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Occasional or casual</t>
+          <t>Fixed-term</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>कभी-कभार का</t>
+          <t>तय समय के लिए</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>jobperm</t>
+          <t>jobsit</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>On probation</t>
+          <t>Works for pay full-time</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>परखने की अवधि पर</t>
+          <t>पूरे समय पैसे के लिए काम</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>jobperm</t>
+          <t>jobsit</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Fixed-term</t>
+          <t>Works for pay part-time or occasional jobs</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>तय समय के लिए</t>
+          <t>कुछ समय या कभी-कभार का काम</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
@@ -14609,20 +14609,20 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Works for pay full-time</t>
+          <t>Studies and works</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>पूरे समय पैसे के लिए काम</t>
+          <t>पढ़ाई के साथ काम</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
@@ -14632,20 +14632,20 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Works for pay part-time or occasional jobs</t>
+          <t>Only studies</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>कुछ समय या कभी-कभार का काम</t>
+          <t>सिर्फ़ पढ़ाई</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127">
@@ -14655,20 +14655,20 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Studies and works</t>
+          <t>Being trained for work only</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>पढ़ाई के साथ काम</t>
+          <t>सिर्फ़ काम की ट्रेनिंग</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128">
@@ -14678,20 +14678,20 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Only studies</t>
+          <t>Retired or pensioned</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>सिर्फ़ पढ़ाई</t>
+          <t>रिटायर या पेंशन पर</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="129">
@@ -14701,20 +14701,20 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Being trained for work only</t>
+          <t>Unpaid household tasks or caring for others</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>सिर्फ़ काम की ट्रेनिंग</t>
+          <t>घर का बिना पैसे का काम या देखभाल</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130">
@@ -14724,20 +14724,20 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Retired or pensioned</t>
+          <t>Unemployed, actively seeking work</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>रिटायर या पेंशन पर</t>
+          <t>काम नहीं है, ढूँढ रहे हैं</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="131">
@@ -14747,20 +14747,20 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Unpaid household tasks or caring for others</t>
+          <t>Sick or disabled, cannot work</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>घर का बिना पैसे का काम या देखभाल</t>
+          <t>बीमारी या विकलांगता से काम नहीं कर सकते</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132">
@@ -14770,20 +14770,20 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Unemployed, actively seeking work</t>
+          <t>Neither studying, working nor seeking work</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>काम नहीं है, ढूँढ रहे हैं</t>
+          <t>न पढ़ाई, न काम, न ढूँढ रहे हैं</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="133">
@@ -14793,66 +14793,66 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>9</v>
+        <v>97</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Sick or disabled, cannot work</t>
+          <t>Does not know</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>बीमारी या विकलांगता से काम नहीं कर सकते</t>
+          <t>पता नहीं</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>9</v>
+        <v>97</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>jobsit</t>
+          <t>landunit</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Neither studying, working nor seeking work</t>
+          <t>Nali</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>न पढ़ाई, न काम, न ढूँढ रहे हैं</t>
+          <t>नाली</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>jobsit</t>
+          <t>landunit</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>97</v>
+        <v>2</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Does not know</t>
+          <t>Bigha</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>पता नहीं</t>
+          <t>बीघा</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>97</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
@@ -14862,20 +14862,20 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Nali</t>
+          <t>Acres</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>नाली</t>
+          <t>एकड़</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137">
@@ -14885,20 +14885,20 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bigha</t>
+          <t>Hectares</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>बीघा</t>
+          <t>हेक्टेयर</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138">
@@ -14908,66 +14908,66 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Acres</t>
+          <t>No land</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>एकड़</t>
+          <t>ज़मीन नहीं है</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>landunit</t>
+          <t>loanpurpose</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Hectares</t>
+          <t>Medical or hospital costs</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>हेक्टेयर</t>
+          <t>इलाज या अस्पताल का ख़र्च</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>landunit</t>
+          <t>loanpurpose</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>No land</t>
+          <t>Buying an animal, vehicle or equipment for work</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ज़मीन नहीं है</t>
+          <t>काम के लिए जानवर, गाड़ी या औज़ार ख़रीदने</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
@@ -14977,20 +14977,20 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Medical or hospital costs</t>
+          <t>Shop stock or business</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>इलाज या अस्पताल का ख़र्च</t>
+          <t>दुकान का सामान या धंधा</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142">
@@ -15000,20 +15000,20 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Buying an animal, vehicle or equipment for work</t>
+          <t>Food or daily household needs</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>काम के लिए जानवर, गाड़ी या औज़ार ख़रीदने</t>
+          <t>खाने या घर की रोज़ की ज़रूरत</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="143">
@@ -15023,20 +15023,20 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Shop stock or business</t>
+          <t>A wedding, funeral or ceremony</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>दुकान का सामान या धंधा</t>
+          <t>शादी, मृत्यु-भोज या कोई समारोह</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144">
@@ -15046,20 +15046,20 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Food or daily household needs</t>
+          <t>House building or repair</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>खाने या घर की रोज़ की ज़रूरत</t>
+          <t>मकान बनाने या मरम्मत</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="145">
@@ -15069,20 +15069,20 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>A wedding, funeral or ceremony</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>शादी, मृत्यु-भोज या कोई समारोह</t>
+          <t>पढ़ाई</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146">
@@ -15092,20 +15092,20 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>House building or repair</t>
+          <t>Repaying another loan</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>मकान बनाने या मरम्मत</t>
+          <t>पुराना क़र्ज़ चुकाने</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="147">
@@ -15115,66 +15115,66 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Something else</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>पढ़ाई</t>
+          <t>कोई और काम</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>loanpurpose</t>
+          <t>marital</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Repaying another loan</t>
+          <t>Currently married</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>पुराना क़र्ज़ चुकाने</t>
+          <t>शादीशुदा</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>loanpurpose</t>
+          <t>marital</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Something else</t>
+          <t>Never married</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>कोई और काम</t>
+          <t>शादी नहीं हुई</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -15184,66 +15184,66 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Currently married</t>
+          <t>Widowed/divorced/separated</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>शादीशुदा</t>
+          <t>विधवा/विधुर या अलग</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>marital</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Never married</t>
+          <t>January</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>शादी नहीं हुई</t>
+          <t>जनवरी</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>marital</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Widowed/divorced/separated</t>
+          <t>February</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>विधवा/विधुर या अलग</t>
+          <t>फ़रवरी</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153">
@@ -15253,20 +15253,20 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>March</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>जनवरी</t>
+          <t>मार्च</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154">
@@ -15276,20 +15276,20 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>April</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>फ़रवरी</t>
+          <t>अप्रैल</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="155">
@@ -15299,20 +15299,20 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>मार्च</t>
+          <t>मई</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156">
@@ -15322,20 +15322,20 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>June</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>अप्रैल</t>
+          <t>जून</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="157">
@@ -15345,20 +15345,20 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>July</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>मई</t>
+          <t>जुलाई</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="158">
@@ -15368,20 +15368,20 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>August</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>जून</t>
+          <t>अगस्त</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="159">
@@ -15391,20 +15391,20 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>September</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>जुलाई</t>
+          <t>सितंबर</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="160">
@@ -15414,20 +15414,20 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>October</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>अगस्त</t>
+          <t>अक्टूबर</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="161">
@@ -15437,20 +15437,20 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>November</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>सितंबर</t>
+          <t>नवंबर</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="162">
@@ -15460,66 +15460,66 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>October</t>
+          <t>December</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>अक्टूबर</t>
+          <t>दिसंबर</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>nativelang</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>Garhwali</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>नवंबर</t>
+          <t>गढ़वाली</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>nativelang</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>Kumaoni</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>दिसंबर</t>
+          <t>कुमाऊँनी</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -15529,20 +15529,20 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Garhwali</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>गढ़वाली</t>
+          <t>हिंदी</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166">
@@ -15552,20 +15552,20 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Kumaoni</t>
+          <t>Nepali</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>कुमाऊँनी</t>
+          <t>नेपाली</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="167">
@@ -15575,20 +15575,20 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Bhojpuri</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>हिंदी</t>
+          <t>भोजपुरी</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168">
@@ -15598,20 +15598,20 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Nepali</t>
+          <t>Assamese</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>नेपाली</t>
+          <t>असमिया</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="169">
@@ -15621,20 +15621,20 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Bhojpuri</t>
+          <t>Bengali</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>भोजपुरी</t>
+          <t>बांग्ला</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="170">
@@ -15644,20 +15644,20 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Assamese</t>
+          <t>Bodo</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>असमिया</t>
+          <t>बोडो</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="171">
@@ -15667,20 +15667,20 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Bengali</t>
+          <t>Dogri</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>बांग्ला</t>
+          <t>डोगरी</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="172">
@@ -15690,20 +15690,20 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Bodo</t>
+          <t>Gujarati</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>बोडो</t>
+          <t>गुजराती</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="173">
@@ -15713,20 +15713,20 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Dogri</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>डोगरी</t>
+          <t>कन्नड़</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="174">
@@ -15736,20 +15736,20 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Gujarati</t>
+          <t>Kashmiri</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>गुजराती</t>
+          <t>कश्मीरी</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="175">
@@ -15759,20 +15759,20 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Konkani</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>कन्नड़</t>
+          <t>कोंकणी</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="176">
@@ -15782,20 +15782,20 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Kashmiri</t>
+          <t>Maithili</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>कश्मीरी</t>
+          <t>मैथिली</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="177">
@@ -15805,20 +15805,20 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Konkani</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>कोंकणी</t>
+          <t>मलयालम</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="178">
@@ -15828,20 +15828,20 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Maithili</t>
+          <t>Manipuri (Meitei)</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>मैथिली</t>
+          <t>मणिपुरी (मैतेई)</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="179">
@@ -15851,20 +15851,20 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Marathi</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>मलयालम</t>
+          <t>मराठी</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="180">
@@ -15874,20 +15874,20 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Manipuri (Meitei)</t>
+          <t>Odia</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>मणिपुरी (मैतेई)</t>
+          <t>ओड़िया</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="181">
@@ -15897,20 +15897,20 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Marathi</t>
+          <t>Punjabi</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>मराठी</t>
+          <t>पंजाबी</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="182">
@@ -15920,20 +15920,20 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Odia</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ओड़िया</t>
+          <t>संस्कृत</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="183">
@@ -15943,20 +15943,20 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Punjabi</t>
+          <t>Santali</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>पंजाबी</t>
+          <t>संताली</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="184">
@@ -15966,20 +15966,20 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Sindhi</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>संस्कृत</t>
+          <t>सिंधी</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="185">
@@ -15989,20 +15989,20 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Santali</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>संताली</t>
+          <t>तमिल</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="186">
@@ -16012,20 +16012,20 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Sindhi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>सिंधी</t>
+          <t>तेलुगु</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="187">
@@ -16035,20 +16035,20 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Urdu</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>तमिल</t>
+          <t>उर्दू</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="188">
@@ -16058,20 +16058,20 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Other Indian language</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>तेलुगु</t>
+          <t>कोई और भारतीय भाषा</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>24</v>
+        <v>96</v>
       </c>
     </row>
     <row r="189">
@@ -16081,66 +16081,66 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Urdu</t>
+          <t>Other / foreign language</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>उर्दू</t>
+          <t>कोई और / विदेशी भाषा</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>25</v>
+        <v>97</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>nativelang</t>
+          <t>obsage</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Other Indian language</t>
+          <t>Under 25</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>कोई और भारतीय भाषा</t>
+          <t>25 से कम</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>96</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>nativelang</t>
+          <t>obsage</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>97</v>
+        <v>2</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Other / foreign language</t>
+          <t>25 to 40</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>कोई और / विदेशी भाषा</t>
+          <t>25 से 40</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>97</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192">
@@ -16150,20 +16150,20 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Under 25</t>
+          <t>Over 40</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>25 से कम</t>
+          <t>40 से ऊपर</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="193">
@@ -16173,66 +16173,66 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>25 to 40</t>
+          <t>Cannot tell</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>25 से 40</t>
+          <t>अंदाज़ा नहीं</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>2</v>
+        <v>97</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>obsage</t>
+          <t>obsset</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Over 40</t>
+          <t>On the route</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>40 से ऊपर</t>
+          <t>मार्ग पर</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>obsage</t>
+          <t>obsset</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>97</v>
+        <v>2</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Cannot tell</t>
+          <t>At a worksite</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>अंदाज़ा नहीं</t>
+          <t>काम की जगह पर</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>97</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196">
@@ -16242,20 +16242,20 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>On the route</t>
+          <t>At lodging or a camp</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>मार्ग पर</t>
+          <t>ठहरने की जगह या कैंप में</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197">
@@ -16265,72 +16265,72 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>At a worksite</t>
+          <t>Somewhere else</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>काम की जगह पर</t>
+          <t>कहीं और</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>obsset</t>
+          <t>obssex</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>At lodging or a camp</t>
+          <t>Man</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>ठहरने की जगह या कैंप में</t>
+          <t>पुरुष</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>obsset</t>
+          <t>obssex</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Somewhere else</t>
+          <t>Woman</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>कहीं और</t>
+          <t>महिला</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>obssex</t>
+          <t>occ</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -16338,12 +16338,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Man</t>
+          <t>Pony/mule worker (works the animals, does not own them)</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>पुरुष</t>
+          <t>घोड़े/खच्चर वाला (जानवर चलाते हैं, मालिक नहीं)</t>
         </is>
       </c>
       <c r="E200" t="n">
@@ -16353,7 +16353,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>obssex</t>
+          <t>occ</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -16361,12 +16361,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Woman</t>
+          <t>Pony/mule owner (owns the animals)</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>महिला</t>
+          <t>घोड़े/खच्चर का मालिक</t>
         </is>
       </c>
       <c r="E201" t="n">
@@ -16380,20 +16380,20 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Pony/mule worker (works the animals, does not own them)</t>
+          <t>Porter (carries on own back/shoulders - goods, luggage, or a person in a kandi)</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>घोड़े/खच्चर वाला (जानवर चलाते हैं, मालिक नहीं)</t>
+          <t>पोर्टर/कुली (अपनी पीठ या कंधे पर — सामान या कंडी में कोई व्यक्ति)</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203">
@@ -16403,20 +16403,20 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Pony/mule owner (owns the animals)</t>
+          <t>Palki / dandi bearer (carries a person on a palanquin, as part of a team)</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>घोड़े/खच्चर का मालिक</t>
+          <t>पालकी / डंडी वाला (पालकी पर व्यक्ति, कई लोग मिलकर)</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="204">
@@ -16426,20 +16426,20 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Porter (carries on own back/shoulders - goods, luggage, or a person in a kandi)</t>
+          <t>Dhaba, tea stall or food stall WORKER (prepared food or tea)</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>पोर्टर/कुली (अपनी पीठ या कंधे पर — सामान या कंडी में कोई व्यक्ति)</t>
+          <t>ढाबा, चाय या खाने की दुकान में काम (बना हुआ खाना या चाय)</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205">
@@ -16449,20 +16449,20 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Palki / dandi bearer (carries a person on a palanquin, as part of a team)</t>
+          <t>Dhaba, tea stall or food stall OWNER (prepared food or tea)</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>पालकी / डंडी वाला (पालकी पर व्यक्ति, कई लोग मिलकर)</t>
+          <t>ढाबा, चाय या खाने की दुकान का मालिक</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="206">
@@ -16472,20 +16472,20 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Dhaba, tea stall or food stall WORKER (prepared food or tea)</t>
+          <t>Shop WORKER (goods: prasad, puja items, clothes, general store)</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>ढाबा, चाय या खाने की दुकान में काम (बना हुआ खाना या चाय)</t>
+          <t>दुकान में काम (सामान: प्रसाद, पूजा का सामान, कपड़े, परचून)</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="207">
@@ -16495,20 +16495,20 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Dhaba, tea stall or food stall OWNER (prepared food or tea)</t>
+          <t>Shop OWNER (goods, not prepared food)</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>ढाबा, चाय या खाने की दुकान का मालिक</t>
+          <t>दुकान का मालिक (सामान, बना हुआ खाना नहीं)</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="208">
@@ -16518,20 +16518,20 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Shop WORKER (goods: prasad, puja items, clothes, general store)</t>
+          <t>Hotel / lodge WORKER</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>दुकान में काम (सामान: प्रसाद, पूजा का सामान, कपड़े, परचून)</t>
+          <t>होटल / लॉज में काम</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="209">
@@ -16541,20 +16541,20 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Shop OWNER (goods, not prepared food)</t>
+          <t>Hotel / lodge OWNER</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>दुकान का मालिक (सामान, बना हुआ खाना नहीं)</t>
+          <t>होटल / लॉज का मालिक</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="210">
@@ -16564,20 +16564,20 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Hotel / lodge WORKER</t>
+          <t>Driver (any motor vehicle)</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>होटल / लॉज में काम</t>
+          <t>ड्राइवर (कोई भी गाड़ी)</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="211">
@@ -16587,20 +16587,20 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Hotel / lodge OWNER</t>
+          <t>Guide</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>होटल / लॉज का मालिक</t>
+          <t>गाइड</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="212">
@@ -16610,20 +16610,20 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Driver (any motor vehicle)</t>
+          <t>Wage labourer (construction, loading, odd jobs)</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>ड्राइवर (कोई भी गाड़ी)</t>
+          <t>दिहाड़ी मज़दूर (निर्माण, सामान चढ़ाना, फुटकर काम)</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="213">
@@ -16633,66 +16633,66 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Guide</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>गाइड</t>
+          <t>कोई और</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>occ</t>
+          <t>origin</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Wage labourer (construction, loading, odd jobs)</t>
+          <t>Local (same district)</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>दिहाड़ी मज़दूर (निर्माण, सामान चढ़ाना, फुटकर काम)</t>
+          <t>यहीं का (इसी ज़िले का)</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>occ</t>
+          <t>origin</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other Uttarakhand district</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>कोई और</t>
+          <t>उत्तराखंड का दूसरा ज़िला</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="216">
@@ -16702,20 +16702,20 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Local (same district)</t>
+          <t>Other Indian state</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>यहीं का (इसी ज़िले का)</t>
+          <t>भारत का दूसरा राज्य</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217">
@@ -16725,66 +16725,66 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Other Uttarakhand district</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>उत्तराखंड का दूसरा ज़िला</t>
+          <t>नेपाल</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>origin</t>
+          <t>pension</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Other Indian state</t>
+          <t>Yes, employer deducts it</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>भारत का दूसरा राज्य</t>
+          <t>हाँ, मालिक काटता है</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>origin</t>
+          <t>pension</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Yes, contributes voluntarily</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>नेपाल</t>
+          <t>हाँ, अपनी मर्ज़ी से</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220">
@@ -16794,66 +16794,66 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Yes, employer deducts it</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>हाँ, मालिक काटता है</t>
+          <t>नहीं</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>pension</t>
+          <t>portable</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Yes, contributes voluntarily</t>
+          <t>Yes, can draw it here</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>हाँ, अपनी मर्ज़ी से</t>
+          <t>हाँ, यहाँ मिल जाता है</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>pension</t>
+          <t>portable</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No, only at the home place</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>नहीं</t>
+          <t>नहीं, सिर्फ़ अपने घर वाली जगह पर</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223">
@@ -16863,20 +16863,20 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Yes, can draw it here</t>
+          <t>Has never tried</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>हाँ, यहाँ मिल जाता है</t>
+          <t>कभी कोशिश नहीं की</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="224">
@@ -16886,20 +16886,20 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>No, only at the home place</t>
+          <t>We have no ration card</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>नहीं, सिर्फ़ अपने घर वाली जगह पर</t>
+          <t>हमारा राशन कार्ड नहीं है</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="225">
@@ -16909,66 +16909,66 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>3</v>
+        <v>97</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Has never tried</t>
+          <t>Does not know</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>कभी कोशिश नहीं की</t>
+          <t>पता नहीं</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>3</v>
+        <v>97</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>portable</t>
+          <t>prevreason</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>We have no ration card</t>
+          <t>Better income</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>हमारा राशन कार्ड नहीं है</t>
+          <t>ज़्यादा कमाई</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>portable</t>
+          <t>prevreason</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>97</v>
+        <v>2</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Does not know</t>
+          <t>Lost the previous work</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>पता नहीं</t>
+          <t>पहला काम छूट गया</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>97</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228">
@@ -16978,20 +16978,20 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Better income</t>
+          <t>Work ended with the season</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>ज़्यादा कमाई</t>
+          <t>मौसम के साथ काम ख़त्म हो गया</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229">
@@ -17001,20 +17001,20 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Lost the previous work</t>
+          <t>Family reasons</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>पहला काम छूट गया</t>
+          <t>घर की वजह से</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="230">
@@ -17024,20 +17024,20 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Work ended with the season</t>
+          <t>Health or injury</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>मौसम के साथ काम ख़त्म हो गया</t>
+          <t>सेहत या चोट</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="231">
@@ -17047,72 +17047,72 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Family reasons</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>घर की वजह से</t>
+          <t>कोई और वजह</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>prevreason</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Health or injury</t>
+          <t>Month by month</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>सेहत या चोट</t>
+          <t>हर महीने का अलग-अलग</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>prevreason</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>One total for the whole year</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>कोई और वजह</t>
+          <t>पूरे साल का एक जोड़</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -17120,12 +17120,12 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Month by month</t>
+          <t>A family member already working here</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>हर महीने का अलग-अलग</t>
+          <t>यहाँ पहले से काम कर रहा घरवाला</t>
         </is>
       </c>
       <c r="E234" t="n">
@@ -17135,24 +17135,24 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>One total for the whole year</t>
+          <t>A friend or someone from the village</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>पूरे साल का एक जोड़</t>
+          <t>दोस्त या गाँव का कोई आदमी</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -17162,20 +17162,20 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>A family member already working here</t>
+          <t>A thekedar or contractor I now work for</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>यहाँ पहले से काम कर रहा घरवाला</t>
+          <t>ठेकेदार जिसके लिए मैं अब काम करता हूँ</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
@@ -17185,20 +17185,20 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>A friend or someone from the village</t>
+          <t>An agent or middleman who placed me (usually for a fee)</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>दोस्त या गाँव का कोई आदमी</t>
+          <t>एजेंट या बिचौलिया जिसने लगवाया (आम तौर पर पैसे लेकर)</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="238">
@@ -17208,20 +17208,20 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>A thekedar or contractor I now work for</t>
+          <t>No one; I found it myself</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>ठेकेदार जिसके लिए मैं अब काम करता हूँ</t>
+          <t>कोई नहीं, ख़ुद ढूँढा</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="239">
@@ -17231,20 +17231,20 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>An agent or middleman who placed me (usually for a fee)</t>
+          <t>The employer called me directly</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>एजेंट या बिचौलिया जिसने लगवाया (आम तौर पर पैसे लेकर)</t>
+          <t>मालिक ने सीधे बुलाया</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="240">
@@ -17254,66 +17254,66 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>No one; I found it myself</t>
+          <t>Someone else</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>कोई नहीं, ख़ुद ढूँढा</t>
+          <t>कोई और</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>remitmode</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>The employer called me directly</t>
+          <t>From my own phone (UPI or net banking)</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>मालिक ने सीधे बुलाया</t>
+          <t>अपने फ़ोन से (UPI या नेट बैंकिंग)</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>remitmode</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Someone else</t>
+          <t>In person at a bank branch or bank mitra / CSP</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>कोई और</t>
+          <t>ख़ुद जाकर बैंक शाखा या बैंक मित्र / CSP पर</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243">
@@ -17323,20 +17323,20 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>From my own phone (UPI or net banking)</t>
+          <t>Money order or post office</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>अपने फ़ोन से (UPI या नेट बैंकिंग)</t>
+          <t>मनीऑर्डर या डाकघर से</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -17346,20 +17346,20 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>In person at a bank branch or bank mitra / CSP</t>
+          <t>Sent with someone going home</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>ख़ुद जाकर बैंक शाखा या बैंक मित्र / CSP पर</t>
+          <t>घर जा रहे किसी के हाथ</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="245">
@@ -17369,20 +17369,20 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Money order or post office</t>
+          <t>Carried it myself</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>मनीऑर्डर या डाकघर से</t>
+          <t>ख़ुद लेकर गए</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="246">
@@ -17392,20 +17392,20 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Sent with someone going home</t>
+          <t>Through an agent or middleman</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>घर जा रहे किसी के हाथ</t>
+          <t>किसी एजेंट या बिचौलिए के ज़रिए</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="247">
@@ -17415,66 +17415,66 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Carried it myself</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>ख़ुद लेकर गए</t>
+          <t>कोई और तरीक़ा</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>remitmode</t>
+          <t>roof</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Through an agent or middleman</t>
+          <t>Thatch/wood/mud</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>किसी एजेंट या बिचौलिए के ज़रिए</t>
+          <t>फूस/लकड़ी/मिट्टी</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>remitmode</t>
+          <t>roof</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Tin/GI sheet</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>कोई और तरीक़ा</t>
+          <t>टीन/चादर</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250">
@@ -17484,164 +17484,164 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Thatch/wood/mud</t>
+          <t>Concrete/RCC</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>फूस/लकड़ी/मिट्टी</t>
+          <t>छत (कंक्रीट/RCC)</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>roof</t>
+          <t>ruralurban</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Tin/GI sheet</t>
+          <t>Village (rural)</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>टीन/चादर</t>
+          <t>गाँव में</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>roof</t>
+          <t>ruralurban</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Concrete/RCC</t>
+          <t>Town or city (urban)</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>छत (कंक्रीट/RCC)</t>
+          <t>शहर या क़स्बे में</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ruralurban</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Village (rural)</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>गाँव में</t>
+          <t>पुरुष</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ruralurban</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Town or city (urban)</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>शहर या क़स्बे में</t>
+          <t>महिला</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>site</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Kedarnath (Gaurikund to Kedarnath)</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>पुरुष</t>
+          <t>केदारनाथ (गौरीकुंड से केदारनाथ)</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>site</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Hemkund Sahib (Govindghat to Hemkund)</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>महिला</t>
+          <t>हेमकुंड साहिब (गोविंदघाट से हेमकुंड)</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>stance</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -17649,12 +17649,12 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Kedarnath (Gaurikund to Kedarnath)</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>केदारनाथ (गौरीकुंड से केदारनाथ)</t>
+          <t>समर्थन में</t>
         </is>
       </c>
       <c r="E257" t="n">
@@ -17664,7 +17664,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>stance</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -17672,12 +17672,12 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Hemkund Sahib (Govindghat to Hemkund)</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>हेमकुंड साहिब (गोविंदघाट से हेमकुंड)</t>
+          <t>तटस्थ</t>
         </is>
       </c>
       <c r="E258" t="n">
@@ -17691,20 +17691,20 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Oppose</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>समर्थन में</t>
+          <t>विरोध में</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="260">
@@ -17714,66 +17714,66 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Prefer not to say</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>तटस्थ</t>
+          <t>बताना नहीं चाहते</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>2</v>
+        <v>98</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>stance</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Oppose</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>विरोध में</t>
+          <t>आंध्र प्रदेश</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>stance</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Prefer not to say</t>
+          <t>Arunachal Pradesh</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>बताना नहीं चाहते</t>
+          <t>अरुणाचल प्रदेश</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
     </row>
     <row r="263">
@@ -17783,20 +17783,20 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>आंध्र प्रदेश</t>
+          <t>असम</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="264">
@@ -17806,20 +17806,20 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Arunachal Pradesh</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>अरुणाचल प्रदेश</t>
+          <t>बिहार</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="265">
@@ -17829,20 +17829,20 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>असम</t>
+          <t>छत्तीसगढ़</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="266">
@@ -17852,20 +17852,20 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>बिहार</t>
+          <t>गोवा</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="267">
@@ -17875,20 +17875,20 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>छत्तीसगढ़</t>
+          <t>गुजरात</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="268">
@@ -17898,20 +17898,20 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>गोवा</t>
+          <t>हरियाणा</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="269">
@@ -17921,20 +17921,20 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>गुजरात</t>
+          <t>हिमाचल प्रदेश</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="270">
@@ -17944,20 +17944,20 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>हरियाणा</t>
+          <t>झारखंड</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="271">
@@ -17967,20 +17967,20 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>हिमाचल प्रदेश</t>
+          <t>कर्नाटक</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="272">
@@ -17990,20 +17990,20 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>झारखंड</t>
+          <t>केरल</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="273">
@@ -18013,20 +18013,20 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>कर्नाटक</t>
+          <t>मध्य प्रदेश</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="274">
@@ -18036,20 +18036,20 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>केरल</t>
+          <t>महाराष्ट्र</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="275">
@@ -18059,20 +18059,20 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Manipur</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>मध्य प्रदेश</t>
+          <t>मणिपुर</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="276">
@@ -18082,20 +18082,20 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Meghalaya</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>महाराष्ट्र</t>
+          <t>मेघालय</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="277">
@@ -18105,20 +18105,20 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Manipur</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>मणिपुर</t>
+          <t>मिज़ोरम</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="278">
@@ -18128,20 +18128,20 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Meghalaya</t>
+          <t>Nagaland</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>मेघालय</t>
+          <t>नागालैंड</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="279">
@@ -18151,20 +18151,20 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>मिज़ोरम</t>
+          <t>ओडिशा</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="280">
@@ -18174,20 +18174,20 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Nagaland</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>नागालैंड</t>
+          <t>पंजाब</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="281">
@@ -18197,20 +18197,20 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>ओडिशा</t>
+          <t>राजस्थान</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="282">
@@ -18220,20 +18220,20 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>पंजाब</t>
+          <t>सिक्किम</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="283">
@@ -18243,20 +18243,20 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>राजस्थान</t>
+          <t>तमिलनाडु</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="284">
@@ -18266,20 +18266,20 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>सिक्किम</t>
+          <t>तेलंगाना</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="285">
@@ -18289,20 +18289,20 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Tripura</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>तमिलनाडु</t>
+          <t>त्रिपुरा</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="286">
@@ -18312,20 +18312,20 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>तेलंगाना</t>
+          <t>उत्तर प्रदेश</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="287">
@@ -18335,20 +18335,20 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Tripura</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>त्रिपुरा</t>
+          <t>पश्चिम बंगाल</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="288">
@@ -18358,20 +18358,20 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Andaman and Nicobar Islands</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>उत्तर प्रदेश</t>
+          <t>अंडमान और निकोबार द्वीप समूह</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="289">
@@ -18381,20 +18381,20 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>पश्चिम बंगाल</t>
+          <t>चंडीगढ़</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="290">
@@ -18404,20 +18404,20 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Andaman and Nicobar Islands</t>
+          <t>Dadra and Nagar Haveli and Daman and Diu</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>अंडमान और निकोबार द्वीप समूह</t>
+          <t>दादरा और नगर हवेली तथा दमन और दीव</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="291">
@@ -18427,20 +18427,20 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>चंडीगढ़</t>
+          <t>दिल्ली</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="292">
@@ -18450,20 +18450,20 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Dadra and Nagar Haveli and Daman and Diu</t>
+          <t>Jammu and Kashmir</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>दादरा और नगर हवेली तथा दमन और दीव</t>
+          <t>जम्मू और कश्मीर</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="293">
@@ -18473,20 +18473,20 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Ladakh</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>दिल्ली</t>
+          <t>लद्दाख</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="294">
@@ -18496,20 +18496,20 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Jammu and Kashmir</t>
+          <t>Lakshadweep</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>जम्मू और कश्मीर</t>
+          <t>लक्षद्वीप</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="295">
@@ -18519,66 +18519,66 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Ladakh</t>
+          <t>Puducherry</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>लद्दाख</t>
+          <t>पुदुच्चेरी</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>task3</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Lakshadweep</t>
+          <t>Yes, regularly in my main Yatra work</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>लक्षद्वीप</t>
+          <t>हाँ, अपने मुख्य यात्रा-काम में नियमित</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>task3</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Puducherry</t>
+          <t>Not in my main work, but done before elsewhere</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>पुदुच्चेरी</t>
+          <t>मुख्य काम में नहीं, पर पहले कहीं और किया है</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298">
@@ -18588,66 +18588,66 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Yes, regularly in my main Yatra work</t>
+          <t>Never done</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>हाँ, अपने मुख्य यात्रा-काम में नियमित</t>
+          <t>कभी नहीं किया</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>task3</t>
+          <t>toilet</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Not in my main work, but done before elsewhere</t>
+          <t>No toilet / open defecation</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>मुख्य काम में नहीं, पर पहले कहीं और किया है</t>
+          <t>शौचालय नहीं / खुले में</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>task3</t>
+          <t>toilet</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Never done</t>
+          <t>Pit latrine without slab or open pit</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>कभी नहीं किया</t>
+          <t>बिना ढँके गड्ढे वाला शौचालय</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -18657,20 +18657,20 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>No toilet / open defecation</t>
+          <t>Improved toilet, but shared with other households</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>शौचालय नहीं / खुले में</t>
+          <t>अच्छा शौचालय, पर दूसरे घरों के साथ साझा</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302">
@@ -18680,66 +18680,66 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Pit latrine without slab or open pit</t>
+          <t>Improved toilet, used only by this household</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>बिना ढँके गड्ढे वाला शौचालय</t>
+          <t>अच्छा शौचालय, सिर्फ़ इसी घर के लिए</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>toilet</t>
+          <t>wall</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Improved toilet, but shared with other households</t>
+          <t>Mud, thatch, bamboo or other natural material</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>अच्छा शौचालय, पर दूसरे घरों के साथ साझा</t>
+          <t>मिट्टी, फूस, बाँस या ऐसी ही कोई चीज़</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>toilet</t>
+          <t>wall</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Improved toilet, used only by this household</t>
+          <t>Unburnt brick, wood or tin</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>अच्छा शौचालय, सिर्फ़ इसी घर के लिए</t>
+          <t>कच्ची ईंट, लकड़ी या टीन</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="305">
@@ -18749,66 +18749,66 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Mud, thatch, bamboo or other natural material</t>
+          <t>Burnt brick, cement, concrete or stone</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>मिट्टी, फूस, बाँस या ऐसी ही कोई चीज़</t>
+          <t>पक्की ईंट, सीमेंट, कंक्रीट या पत्थर</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>wall</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Unburnt brick, wood or tin</t>
+          <t>Piped into the house or yard</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>कच्ची ईंट, लकड़ी या टीन</t>
+          <t>घर या आँगन में नल</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>wall</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Burnt brick, cement, concrete or stone</t>
+          <t>Public tap or standpipe</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>पक्की ईंट, सीमेंट, कंक्रीट या पत्थर</t>
+          <t>सार्वजनिक नल या स्टैंडपोस्ट</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="308">
@@ -18818,20 +18818,20 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Piped into the house or yard</t>
+          <t>Handpump, tubewell or borewell</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>घर या आँगन में नल</t>
+          <t>हैंडपंप, ट्यूबवेल या बोरवेल</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="309">
@@ -18841,20 +18841,20 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Public tap or standpipe</t>
+          <t>Protected well or protected spring</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>सार्वजनिक नल या स्टैंडपोस्ट</t>
+          <t>ढका हुआ कुआँ या ढका हुआ सोता</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="310">
@@ -18864,20 +18864,20 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Handpump, tubewell or borewell</t>
+          <t>Rainwater collection</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>हैंडपंप, ट्यूबवेल या बोरवेल</t>
+          <t>बारिश का पानी जमा करके</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="311">
@@ -18887,20 +18887,20 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Protected well or protected spring</t>
+          <t>Bottled, packaged or community RO</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>ढका हुआ कुआँ या ढका हुआ सोता</t>
+          <t>बोतलबंद, पैकेट या सामुदायिक RO</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="312">
@@ -18910,20 +18910,20 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Rainwater collection</t>
+          <t>Unprotected well or unprotected spring</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>बारिश का पानी जमा करके</t>
+          <t>खुला कुआँ या खुला सोता</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="313">
@@ -18933,20 +18933,20 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Bottled, packaged or community RO</t>
+          <t>River, stream, pond or canal</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>बोतलबंद, पैकेट या सामुदायिक RO</t>
+          <t>नदी, गाड़, तालाब या नहर</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="314">
@@ -18956,66 +18956,66 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Unprotected well or unprotected spring</t>
+          <t>Tanker truck or cart with drum</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>खुला कुआँ या खुला सोता</t>
+          <t>टैंकर या ड्रम वाली गाड़ी</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>wgdiff</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>River, stream, pond or canal</t>
+          <t>No difficulty</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>नदी, गाड़, तालाब या नहर</t>
+          <t>कोई दिक़्क़त नहीं</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>wgdiff</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Tanker truck or cart with drum</t>
+          <t>Some difficulty</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>टैंकर या ड्रम वाली गाड़ी</t>
+          <t>थोड़ी दिक़्क़त</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317">
@@ -19025,20 +19025,20 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>No difficulty</t>
+          <t>A lot of difficulty</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>कोई दिक़्क़त नहीं</t>
+          <t>बहुत दिक़्क़त</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318">
@@ -19048,66 +19048,66 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Some difficulty</t>
+          <t>Cannot do it at all</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>थोड़ी दिक़्क़त</t>
+          <t>बिलकुल नहीं कर पाते</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>wgdiff</t>
+          <t>workins</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>A lot of difficulty</t>
+          <t>Yes, through work</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>बहुत दिक़्क़त</t>
+          <t>हाँ, काम की तरफ़ से</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>wgdiff</t>
+          <t>workins</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Cannot do it at all</t>
+          <t>Only private or other insurance</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>बिलकुल नहीं कर पाते</t>
+          <t>सिर्फ़ अपना या कोई और बीमा</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="321">
@@ -19117,20 +19117,20 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Yes, through work</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>हाँ, काम की तरफ़ से</t>
+          <t>कोई नहीं</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="322">
@@ -19140,72 +19140,72 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Only private or other insurance</t>
+          <t>Don't know</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>सिर्फ़ अपना या कोई और बीमा</t>
+          <t>पता नहीं</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>workins</t>
+          <t>yn</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>कोई नहीं</t>
+          <t>नहीं</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>workins</t>
+          <t>yn</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Don't know</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>पता नहीं</t>
+          <t>हाँ</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>yn</t>
+          <t>yndk</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -19228,7 +19228,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>yn</t>
+          <t>yndk</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -19255,65 +19255,19 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Don't know</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>नहीं</t>
+          <t>पता नहीं</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>yndk</t>
-        </is>
-      </c>
-      <c r="B328" t="n">
-        <v>1</v>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>हाँ</t>
-        </is>
-      </c>
-      <c r="E328" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>yndk</t>
-        </is>
-      </c>
-      <c r="B329" t="n">
-        <v>97</v>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>Don't know</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>पता नहीं</t>
-        </is>
-      </c>
-      <c r="E329" t="n">
         <v>97</v>
       </c>
     </row>

--- a/Kedarnath_final_kobo.xlsx
+++ b/Kedarnath_final_kobo.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O286"/>
+  <dimension ref="A1:O289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -768,7 +768,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>'2026-10-05.c8aeef'</t>
+          <t>'2026-10-05.696592'</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -9475,22 +9475,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one ropexp</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>trek_dependent</t>
+          <t>ropeway_expect_work</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Is your main work carrying, transporting or guiding people or goods on foot along the pilgrimage trek?</t>
+          <t>If the ropeway is built, what do you think will happen to your own work? More work for you; less work; about the same; or don't know?</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
+          <t>अगर रोपवे बन गया, तो आपके अपने काम पर क्या असर होगा? मेरे लिए ज़्यादा काम; मेरे लिए कम काम; लगभग वैसा ही; या पता नहीं?</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -9500,7 +9500,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr"/>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>${site} = 1</t>
+        </is>
+      </c>
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr"/>
@@ -9512,16 +9516,36 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr"/>
-      <c r="C228" t="inlineStr"/>
-      <c r="D228" t="inlineStr"/>
+          <t>select_one ropjobs</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>ropeway_expect_jobs</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Who do you think will get most of the jobs the ropeway creates? People from these villages; people from outside the area; nobody will get jobs; or don't know?</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>रोपवे में जो नौकरियाँ बनेंगी, वे ज़्यादातर किसे मिलेंगी? इन गाँवों के लोगों को; इलाके के बाहर के लोगों को; किसी को नहीं मिलेंगी; या पता नहीं?</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr"/>
-      <c r="G228" t="inlineStr"/>
-      <c r="H228" t="inlineStr"/>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>${site} = 1</t>
+        </is>
+      </c>
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr"/>
@@ -9533,64 +9557,72 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_one yndk</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>grp_K</t>
+          <t>ropeway_trust</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Do you think the ropeway will improve the livelihoods of people here? Yes; no; or don't know?</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
+          <t>क्या आपको लगता है कि रोपवे से यहाँ के लोगों की रोज़ी-रोटी सुधरेगी? हाँ; नहीं; या पता नहीं?</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr"/>
-      <c r="G229" t="inlineStr"/>
-      <c r="H229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>${site} = 1</t>
+        </is>
+      </c>
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr"/>
       <c r="M229" t="inlineStr"/>
       <c r="N229" t="inlineStr"/>
-      <c r="O229" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>intro_K</t>
+          <t>trek_dependent</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Now a set of questions about the conditions of your work — hours, pay, contract and so on. These come from a standard list used in many countries, so one or two may not fit your situation. Say so and we will move on.</t>
+          <t>Is your main work carrying, transporting or guiding people or goods on foot along the pilgrimage trek?</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>अब आपके काम के हालात पर कुछ सवाल — घंटे, मज़दूरी, ठेका वग़ैरह। ये एक बनी-बनाई सूची से हैं जो कई देशों में इस्तेमाल होती है, इसलिए एक-दो सवाल आपकी स्थिति पर शायद ठीक न बैठें। बता दीजिएगा, हम आगे बढ़ जाएँगे।</t>
+          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr"/>
-      <c r="G230" t="inlineStr"/>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr"/>
@@ -9603,39 +9635,15 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>select_one jobsit</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>job_situation</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>During the last month, what were you mainly doing? Ask it open and code the closest one; do not read the list out.</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>पिछले महीने आप मुख्य रूप से क्या कर रहे थे? खुला पूछें और जो सबसे मिलता हो वह कोड करें; पूरी सूची पढ़कर न सुनाएँ।</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>Code what they were MAINLY doing, by time, over the last month. Work for pay = full-time if it was their main activity on most working days, part-time or occasional if it was picked up here and there around something else. Seasonal preparation (buying stock, repairing tack, bringing animals up) IS working for pay — it is their trade — so code 1 or 2, not 10. Unemployed (8) means looking for work and not finding it; between seasons with work expected is not unemployed. Code 10 is the genuine none: not working, not studying, not looking.</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>Code what they were MAINLY doing, by time, over the last month. Work for pay = full-time if it was their main activity on most working days, part-time or occasional if it was picked up here and there around something else. Seasonal preparation (buying stock, repairing tack, bringing animals up) IS working for pay — it is their trade — so code 1 or 2, not 10. Unemployed (8) means looking for work and not finding it; between seasons with work expected is not unemployed. Code 10 is the genuine none: not working, not studying, not looking.</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr"/>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr"/>
@@ -9648,85 +9656,65 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>select_one jobperm</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>job_permanence</t>
+          <t>grp_K</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
+          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>Both will sound seasonal here — the Yatra closes for everyone. Ask about WITHIN the season. One employer keeps them on for a stretch = Seasonal or temporary. They take work day by day from whoever offers it = Occasional or casual. Self-employed: answer for how their own work runs. On probation and Fixed-term are rare here; do not reach for them.</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>यहाँ दोनों ही मौसमी लगेंगे — यात्रा तो सबके लिए बंद होती है। मौसम के अंदर की बात पूछिए। एक ही मालिक कुछ समय तक रखे हुए है = मौसमी या अस्थायी। जो भी काम रोज़-रोज़ मिल जाए वह कर लेते हैं = कभी-कभार या दिहाड़ी। अपना काम करने वालों के लिए: उनका अपना काम कैसे चलता है, वह देखिए। परख पर और तय अवधि वाले यहाँ बहुत कम मिलेंगे; इन्हें यूँ ही न चुनें।</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>${job_situation} &lt;= 3</t>
-        </is>
-      </c>
+          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr"/>
       <c r="N232" t="inlineStr"/>
-      <c r="O232" t="inlineStr"/>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>select_one contract</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>contract_status</t>
+          <t>intro_K</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
+          <t>Now a set of questions about the conditions of your work — hours, pay, contract and so on. These come from a standard list used in many countries, so one or two may not fit your situation. Say so and we will move on.</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
+          <t>अब आपके काम के हालात पर कुछ सवाल — घंटे, मज़दूरी, ठेका वग़ैरह। ये एक बनी-बनाई सूची से हैं जो कई देशों में इस्तेमाल होती है, इसलिए एक-दो सवाल आपकी स्थिति पर शायद ठीक न बैठें। बता दीजिएगा, हम आगे बढ़ जाएँगे।</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr"/>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
-        </is>
-      </c>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr"/>
@@ -9738,36 +9726,40 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one jobsit</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>workplace_registered</t>
+          <t>job_situation</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
+          <t>During the last month, what were you mainly doing? Ask it open and code the closest one; do not read the list out.</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr"/>
+          <t>पिछले महीने आप मुख्य रूप से क्या कर रहे थे? खुला पूछें और जो सबसे मिलता हो वह कोड करें; पूरी सूची पढ़कर न सुनाएँ।</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Code what they were MAINLY doing, by time, over the last month. Work for pay = full-time if it was their main activity on most working days, part-time or occasional if it was picked up here and there around something else. Seasonal preparation (buying stock, repairing tack, bringing animals up) IS working for pay — it is their trade — so code 1 or 2, not 10. Unemployed (8) means looking for work and not finding it; between seasons with work expected is not unemployed. Code 10 is the genuine none: not working, not studying, not looking.</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Code what they were MAINLY doing, by time, over the last month. Work for pay = full-time if it was their main activity on most working days, part-time or occasional if it was picked up here and there around something else. Seasonal preparation (buying stock, repairing tack, bringing animals up) IS working for pay — it is their trade — so code 1 or 2, not 10. Unemployed (8) means looking for work and not finding it; between seasons with work expected is not unemployed. Code 10 is the genuine none: not working, not studying, not looking.</t>
+        </is>
+      </c>
       <c r="G234" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>${job_situation} &lt;= 3</t>
-        </is>
-      </c>
+      <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr"/>
@@ -9779,26 +9771,34 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>select_one pension</t>
+          <t>select_one jobperm</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>pension_contrib</t>
+          <t>job_permanence</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
+          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
+          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Both will sound seasonal here — the Yatra closes for everyone. Ask about WITHIN the season. One employer keeps them on for a stretch = Seasonal or temporary. They take work day by day from whoever offers it = Occasional or casual. Self-employed: answer for how their own work runs. On probation and Fixed-term are rare here; do not reach for them.</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>यहाँ दोनों ही मौसमी लगेंगे — यात्रा तो सबके लिए बंद होती है। मौसम के अंदर की बात पूछिए। एक ही मालिक कुछ समय तक रखे हुए है = मौसमी या अस्थायी। जो भी काम रोज़-रोज़ मिल जाए वह कर लेते हैं = कभी-कभार या दिहाड़ी। अपना काम करने वालों के लिए: उनका अपना काम कैसे चलता है, वह देखिए। परख पर और तय अवधि वाले यहाँ बहुत कम मिलेंगे; इन्हें यूँ ही न चुनें।</t>
+        </is>
+      </c>
       <c r="G235" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
+          <t>${job_situation} &lt;= 3</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -9820,22 +9820,22 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>select_one workins</t>
+          <t>select_one contract</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>work_health_ins</t>
+          <t>contract_status</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
+          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
+          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -9861,22 +9861,22 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>leave_rights</t>
+          <t>workplace_registered</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
+          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
+          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -9888,7 +9888,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
+          <t>${job_situation} &lt;= 3</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -9902,22 +9902,22 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>select_one pension</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>injured_ever</t>
+          <t>pension_contrib</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Have you ever been physically injured at your workplace?</t>
+          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
+          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -9929,7 +9929,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>${job_situation} &lt;= 3</t>
+          <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -9943,22 +9943,22 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>select_one workins</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>workplace_injury_12m</t>
+          <t>work_health_ins</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>In the last 12 months, was anyone physically injured at your workplace because of work?</t>
+          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी?</t>
+          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>${job_situation} &lt;= 3</t>
+          <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -9989,17 +9989,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>workplace_death_12m</t>
+          <t>leave_rights</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>And in the last 12 months, did anyone die at your workplace because of work?</t>
+          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>और पिछले 12 महीनों में, क्या आपके काम की जगह पर काम की वजह से किसी की मौत हुई?</t>
+          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -10011,7 +10011,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>${job_situation} &lt;= 3</t>
+          <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -10030,17 +10030,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>wants_more_work</t>
+          <t>injured_ever</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Would you like to work more hours than you do?</t>
+          <t>Have you ever been physically injured at your workplace?</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
+          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>${job_situation} &lt;= 7</t>
+          <t>${job_situation} &lt;= 3</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -10066,22 +10066,22 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yndk</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>more_hours_day</t>
+          <t>workplace_injury_12m</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>On a working day, how many MORE hours would you like to work?</t>
+          <t>In the last 12 months, was anyone physically injured at your workplace because of work?</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
+          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी?</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -10093,24 +10093,12 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>${wants_more_work} = 1 or ${job_situation} = 8</t>
-        </is>
-      </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . + ${hours_day_yatra} &lt;= 18</t>
-        </is>
-      </c>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t>Hours wanted plus hours already worked cannot exceed 18 in a day.</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t>Hours wanted plus hours already worked cannot exceed 18 in a day.</t>
-        </is>
-      </c>
+          <t>${job_situation} &lt;= 3</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr"/>
       <c r="M242" t="inlineStr"/>
       <c r="N242" t="inlineStr"/>
@@ -10119,22 +10107,22 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yndk</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>months_looked_for_work</t>
+          <t>workplace_death_12m</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
+          <t>And in the last 12 months, did anyone die at your workplace because of work?</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
+          <t>और पिछले 12 महीनों में, क्या आपके काम की जगह पर काम की वजह से किसी की मौत हुई?</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -10146,7 +10134,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>${calc_months_no_work} &gt; 0 or ${job_situation} = 8</t>
+          <t>${job_situation} &lt;= 3</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -10165,17 +10153,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>first_job_ever</t>
+          <t>wants_more_work</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Was your current work the first paid job you ever had?</t>
+          <t>Would you like to work more hours than you do?</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
+          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -10185,7 +10173,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr"/>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>${job_situation} &lt;= 7</t>
+        </is>
+      </c>
       <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr"/>
@@ -10197,22 +10189,22 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>higher_ed</t>
+          <t>more_hours_day</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Have you completed any college, diploma or university course?</t>
+          <t>On a working day, how many MORE hours would you like to work?</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>क्या आपने कॉलेज, डिप्लोमा या यूनिवर्सिटी का कोई कोर्स पूरा किया है?</t>
+          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -10224,12 +10216,24 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>${job_situation} &lt;= 3</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
+          <t>${wants_more_work} = 1 or ${job_situation} = 8</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . + ${hours_day_yatra} &lt;= 18</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>Hours wanted plus hours already worked cannot exceed 18 in a day.</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Hours wanted plus hours already worked cannot exceed 18 in a day.</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr"/>
       <c r="M245" t="inlineStr"/>
       <c r="N245" t="inlineStr"/>
@@ -10238,22 +10242,22 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>social_security_any</t>
+          <t>months_looked_for_work</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Are you enrolled in any pension, insurance or social-security scheme? For example, EPFO or PM-SYM pension, or Ayushman Bharat health cover.</t>
+          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>क्या आप किसी पेंशन, बीमा या सरकारी सामाजिक सुरक्षा योजना में शामिल हैं? जैसे EPFO या PM-SYM पेंशन, या आयुष्मान भारत स्वास्थ्य कवर।</t>
+          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -10265,7 +10269,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>${job_situation} &lt;= 3</t>
+          <t>${calc_months_no_work} &gt; 0 or ${job_situation} = 8</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -10284,17 +10288,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>intens_speed</t>
+          <t>first_job_ever</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you work at very high speed?</t>
+          <t>Was your current work the first paid job you ever had?</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप बहुत तेज़ रफ़्तार से काम करते हैं?</t>
+          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -10304,11 +10308,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>${job_situation} &lt;= 3</t>
-        </is>
-      </c>
+      <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr"/>
@@ -10325,17 +10325,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>intens_deadline</t>
+          <t>higher_ed</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you work to tight deadlines?</t>
+          <t>Have you completed any college, diploma or university course?</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आपको कड़ी समय-सीमा में काम करना पड़ता है?</t>
+          <t>क्या आपने कॉलेज, डिप्लोमा या यूनिवर्सिटी का कोई कोर्स पूरा किया है?</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -10366,17 +10366,17 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>intens_time</t>
+          <t>social_security_any</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you not have enough time to finish your tasks?</t>
+          <t>Are you enrolled in any pension, insurance or social-security scheme? For example, EPFO or PM-SYM pension, or Ayushman Bharat health cover.</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आपके पास काम पूरा करने के लिए काफ़ी समय नहीं होता?</t>
+          <t>क्या आप किसी पेंशन, बीमा या सरकारी सामाजिक सुरक्षा योजना में शामिल हैं? जैसे EPFO या PM-SYM पेंशन, या आयुष्मान भारत स्वास्थ्य कवर।</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
@@ -10407,17 +10407,17 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>posture_position</t>
+          <t>intens_speed</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you work in a tiring or painful position?</t>
+          <t>For more than half of your working day, do you work at very high speed?</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप थकाने वाली या दर्द वाली स्थिति में काम करते हैं?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप बहुत तेज़ रफ़्तार से काम करते हैं?</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -10448,17 +10448,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>posture_loads</t>
+          <t>intens_deadline</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you carry or move heavy loads?</t>
+          <t>For more than half of your working day, do you work to tight deadlines?</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप भारी बोझ उठाते या ढोते हैं?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आपको कड़ी समय-सीमा में काम करना पड़ता है?</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -10489,17 +10489,17 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>posture_repetitive</t>
+          <t>intens_time</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you make the same movements again and again?</t>
+          <t>For more than half of your working day, do you not have enough time to finish your tasks?</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप एक ही तरह की हरकत बार-बार करते हैं?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आपके पास काम पूरा करने के लिए काफ़ी समय नहीं होता?</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -10530,17 +10530,17 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>phys_noise</t>
+          <t>posture_position</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>For more than half of your working day, are you exposed to loud noise?</t>
+          <t>For more than half of your working day, do you work in a tiring or painful position?</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप तेज़ शोर में रहते हैं?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप थकाने वाली या दर्द वाली स्थिति में काम करते हैं?</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -10571,17 +10571,17 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>phys_temperature</t>
+          <t>posture_loads</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>For more than half of your working day, are you exposed to extreme heat or cold?</t>
+          <t>For more than half of your working day, do you carry or move heavy loads?</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप बहुत गर्मी या बहुत ठंड में रहते हैं?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप भारी बोझ उठाते या ढोते हैं?</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -10607,16 +10607,36 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr"/>
-      <c r="C255" t="inlineStr"/>
-      <c r="D255" t="inlineStr"/>
+          <t>select_one yndk</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>posture_repetitive</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>For more than half of your working day, do you make the same movements again and again?</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप एक ही तरह की हरकत बार-बार करते हैं?</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr"/>
-      <c r="G255" t="inlineStr"/>
-      <c r="H255" t="inlineStr"/>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>${job_situation} &lt;= 3</t>
+        </is>
+      </c>
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr"/>
@@ -10628,65 +10648,77 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_one yndk</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>grp_L</t>
+          <t>phys_noise</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Module L: Tasks and skills (short block)</t>
+          <t>For more than half of your working day, are you exposed to loud noise?</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Module L: Tasks and skills (short block)</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप तेज़ शोर में रहते हैं?</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr"/>
-      <c r="G256" t="inlineStr"/>
-      <c r="H256" t="inlineStr"/>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>${job_situation} &lt;= 3</t>
+        </is>
+      </c>
       <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr"/>
       <c r="M256" t="inlineStr"/>
       <c r="N256" t="inlineStr"/>
-      <c r="O256" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one yndk</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>intro_L</t>
+          <t>phys_temperature</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Last, I will read out some kinds of work-tasks and ask whether you do them. There is no right or wrong answer — we are trying to understand what skills the work here actually uses.</t>
+          <t>For more than half of your working day, are you exposed to extreme heat or cold?</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>आख़िर में, मैं कुछ तरह के कामों के नाम पढ़ूँगा और पूछूँगा कि आप वे करते हैं या नहीं। इसमें सही या ग़लत जवाब कुछ नहीं है — हम बस यह समझना चाहते हैं कि यहाँ के काम में कौन-कौन से हुनर लगते हैं।</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप बहुत गर्मी या बहुत ठंड में रहते हैं?</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr"/>
-      <c r="H257" t="inlineStr"/>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>${job_situation} &lt;= 3</t>
+        </is>
+      </c>
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr"/>
@@ -10698,31 +10730,15 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>select_one task3</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>tk_load</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Do you load, unload, stack or count goods? </t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr"/>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr"/>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr"/>
@@ -10735,31 +10751,27 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>select_one task3</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>tk_drive</t>
+          <t>grp_L</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you drive a motor vehicle? </t>
+          <t>Module L: Tasks and skills (short block)</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>Module L: Tasks and skills (short block)</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr"/>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr"/>
@@ -10767,36 +10779,36 @@
       <c r="L259" t="inlineStr"/>
       <c r="M259" t="inlineStr"/>
       <c r="N259" t="inlineStr"/>
-      <c r="O259" t="inlineStr"/>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>select_one task3</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>tk_engine</t>
+          <t>intro_L</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you operate an engine or machine? </t>
+          <t>Last, I will read out some kinds of work-tasks and ask whether you do them. There is no right or wrong answer — we are trying to understand what skills the work here actually uses.</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>आख़िर में, मैं कुछ तरह के कामों के नाम पढ़ूँगा और पूछूँगा कि आप वे करते हैं या नहीं। इसमें सही या ग़लत जवाब कुछ नहीं है — हम बस यह समझना चाहते हैं कि यहाँ के काम में कौन-कौन से हुनर लगते हैं।</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr"/>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr"/>
@@ -10814,17 +10826,17 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>tk_electric</t>
+          <t>tk_load</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you do electrical or wiring work? </t>
+          <t xml:space="preserve">Do you load, unload, stack or count goods? </t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
@@ -10851,17 +10863,17 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>tk_safety</t>
+          <t>tk_drive</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you check equipment or the route for safety? </t>
+          <t xml:space="preserve">Do you drive a motor vehicle? </t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
@@ -10888,17 +10900,17 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>tk_sell</t>
+          <t>tk_engine</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you sell goods or services? </t>
+          <t xml:space="preserve">Do you operate an engine or machine? </t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E263" t="inlineStr"/>
@@ -10925,17 +10937,17 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>tk_cash</t>
+          <t>tk_electric</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you handle cash and payments? </t>
+          <t xml:space="preserve">Do you do electrical or wiring work? </t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
@@ -10962,17 +10974,17 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>tk_cook</t>
+          <t>tk_safety</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you cook or prepare food or drink? </t>
+          <t xml:space="preserve">Do you check equipment or the route for safety? </t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E265" t="inlineStr"/>
@@ -10999,17 +11011,17 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>tk_serve</t>
+          <t>tk_sell</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you serve guests or customers? </t>
+          <t xml:space="preserve">Do you sell goods or services? </t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E266" t="inlineStr"/>
@@ -11036,17 +11048,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>tk_clean</t>
+          <t>tk_cash</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you clean rooms or public areas? </t>
+          <t xml:space="preserve">Do you handle cash and payments? </t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -11073,17 +11085,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>tk_guide</t>
+          <t>tk_cook</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you guide or explain things to visitors? </t>
+          <t xml:space="preserve">Do you cook or prepare food or drink? </t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -11110,17 +11122,17 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>tk_coord</t>
+          <t>tk_serve</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you coordinate work by phone, radio or signals? </t>
+          <t xml:space="preserve">Do you serve guests or customers? </t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E269" t="inlineStr"/>
@@ -11142,22 +11154,22 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one task3</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>drove_twowheeler</t>
+          <t>tk_clean</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
+          <t xml:space="preserve">Do you clean rooms or public areas? </t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
+          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
@@ -11167,11 +11179,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>${tk_drive} = 1 or ${tk_drive} = 2</t>
-        </is>
-      </c>
+      <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr"/>
       <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr"/>
@@ -11183,22 +11191,22 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one task3</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>drove_car</t>
+          <t>tk_guide</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>... a car or jeep?</t>
+          <t xml:space="preserve">Do you guide or explain things to visitors? </t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>...कार या जीप?</t>
+          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E271" t="inlineStr"/>
@@ -11208,11 +11216,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>${tk_drive} = 1 or ${tk_drive} = 2</t>
-        </is>
-      </c>
+      <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr"/>
@@ -11224,22 +11228,22 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one task3</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>drove_heavy</t>
+          <t>tk_coord</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>... a truck or bus?</t>
+          <t xml:space="preserve">Do you coordinate work by phone, radio or signals? </t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>...ट्रक या बस?</t>
+          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E272" t="inlineStr"/>
@@ -11249,11 +11253,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>${tk_drive} = 1 or ${tk_drive} = 2</t>
-        </is>
-      </c>
+      <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr"/>
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr"/>
@@ -11270,17 +11270,17 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>read_at_work</t>
+          <t>drove_twowheeler</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
+          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
+          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
         </is>
       </c>
       <c r="E273" t="inlineStr"/>
@@ -11290,7 +11290,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr"/>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>${tk_drive} = 1 or ${tk_drive} = 2</t>
+        </is>
+      </c>
       <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr"/>
@@ -11307,17 +11311,17 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>calc_at_work</t>
+          <t>drove_car</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>In your work, do you work out prices or costs?</t>
+          <t>... a car or jeep?</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
+          <t>...कार या जीप?</t>
         </is>
       </c>
       <c r="E274" t="inlineStr"/>
@@ -11327,7 +11331,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr"/>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>${tk_drive} = 1 or ${tk_drive} = 2</t>
+        </is>
+      </c>
       <c r="I274" t="inlineStr"/>
       <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr"/>
@@ -11339,16 +11347,36 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr"/>
-      <c r="C275" t="inlineStr"/>
-      <c r="D275" t="inlineStr"/>
+          <t>select_one yn</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>drove_heavy</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>... a truck or bus?</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>...ट्रक या बस?</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr"/>
-      <c r="G275" t="inlineStr"/>
-      <c r="H275" t="inlineStr"/>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>${tk_drive} = 1 or ${tk_drive} = 2</t>
+        </is>
+      </c>
       <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr"/>
@@ -11360,27 +11388,31 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>grp_M</t>
+          <t>read_at_work</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Module M: Access to common resources (short block)</t>
+          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Module M: Access to common resources (short block)</t>
+          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr"/>
-      <c r="G276" t="inlineStr"/>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H276" t="inlineStr"/>
       <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr"/>
@@ -11388,31 +11420,27 @@
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="inlineStr"/>
       <c r="N276" t="inlineStr"/>
-      <c r="O276" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>cpr_firewood</t>
+          <t>calc_at_work</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>In the last 12 months, did anyone in your household collect firewood or dead wood from common land or forest near here?</t>
+          <t>In your work, do you work out prices or costs?</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने आस-पास की साझा ज़मीन या जंगल से लकड़ी या सूखी टहनियाँ इकट्ठी कीं?</t>
+          <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
@@ -11434,31 +11462,15 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>cpr_fodder</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>In the last 12 months, did anyone in your household cut grass or fodder from common land near here?</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने साझा ज़मीन से घास या चारा काटा?</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr"/>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr"/>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G278" t="inlineStr"/>
       <c r="H278" t="inlineStr"/>
       <c r="I278" t="inlineStr"/>
       <c r="J278" t="inlineStr"/>
@@ -11471,31 +11483,27 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>cpr_forest_produce</t>
+          <t>grp_M</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>In the last 12 months, did anyone in your household collect herbs, mushrooms or wild fruit from the forest?</t>
+          <t>Module M: Access to common resources (short block)</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने जंगल से जड़ी-बूटी, मशरूम या जंगली फल इकट्ठे किए?</t>
+          <t>Module M: Access to common resources (short block)</t>
         </is>
       </c>
       <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr"/>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr"/>
       <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr"/>
@@ -11503,7 +11511,11 @@
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="inlineStr"/>
       <c r="N279" t="inlineStr"/>
-      <c r="O279" t="inlineStr"/>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -11513,17 +11525,17 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>cpr_grazing</t>
+          <t>cpr_firewood</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>In the last 12 months, did any animal of your household graze on common pasture?</t>
+          <t>In the last 12 months, did anyone in your household collect firewood or dead wood from common land or forest near here?</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर का कोई जानवर साझा चरागाह में चरा?</t>
+          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने आस-पास की साझा ज़मीन या जंगल से लकड़ी या सूखी टहनियाँ इकट्ठी कीं?</t>
         </is>
       </c>
       <c r="E280" t="inlineStr"/>
@@ -11550,17 +11562,17 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>cpr_restricted</t>
+          <t>cpr_fodder</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>In the last 12 months, has anyone in your household been stopped from using a common forest, pasture or path, or been asked to pay to use it?</t>
+          <t>In the last 12 months, did anyone in your household cut grass or fodder from common land near here?</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी को साझा जंगल, चरागाह या रास्ते के इस्तेमाल से रोका गया, या इसके लिए पैसे देने को कहा गया?</t>
+          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने साझा ज़मीन से घास या चारा काटा?</t>
         </is>
       </c>
       <c r="E281" t="inlineStr"/>
@@ -11587,17 +11599,17 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>cpr_lost_access</t>
+          <t>cpr_forest_produce</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>In the last 12 months, has a common place you used to collect from or graze on been closed because of building, road or ropeway work?</t>
+          <t>In the last 12 months, did anyone in your household collect herbs, mushrooms or wild fruit from the forest?</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या कोई साझा जगह, जहाँ आप पहले लकड़ी, घास या चारा लेते थे, निर्माण, सड़क या रोपवे के काम की वजह से बंद हो गई?</t>
+          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने जंगल से जड़ी-बूटी, मशरूम या जंगली फल इकट्ठे किए?</t>
         </is>
       </c>
       <c r="E282" t="inlineStr"/>
@@ -11619,22 +11631,22 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>select_one cprwater</t>
+          <t>select_one yndk</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>cpr_water_route</t>
+          <t>cpr_grazing</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>On your route or near your worksite, can you use a common water source (spring, tap or stream) without paying?</t>
+          <t>In the last 12 months, did any animal of your household graze on common pasture?</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>रास्ते पर या काम की जगह के पास, क्या आप कोई साझा पानी का स्रोत (झरना, नल या नदी-नाला) बिना पैसे दिए इस्तेमाल कर सकते हैं?</t>
+          <t>पिछले 12 महीनों में, क्या आपके घर का कोई जानवर साझा चरागाह में चरा?</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
@@ -11656,22 +11668,22 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>select_one cprgov</t>
+          <t>select_one yndk</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>cpr_governance</t>
+          <t>cpr_restricted</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>In this area, who decides who may use the common land and forest? Ask and code what they name; do not read the list.</t>
+          <t>In the last 12 months, has anyone in your household been stopped from using a common forest, pasture or path, or been asked to pay to use it?</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>इस इलाके की साझा ज़मीन और जंगल का फ़ैसला कौन करता है, कि कौन उसका इस्तेमाल कर सकता है? जो नाम लें वही लिख लें; सूची न पढ़ें।</t>
+          <t>पिछले 12 महीनों में, क्या आपके घर के किसी को साझा जंगल, चरागाह या रास्ते के इस्तेमाल से रोका गया, या इसके लिए पैसे देने को कहा गया?</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
@@ -11693,15 +11705,31 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr"/>
-      <c r="C285" t="inlineStr"/>
-      <c r="D285" t="inlineStr"/>
+          <t>select_one yndk</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>cpr_lost_access</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>In the last 12 months, has a common place you used to collect from or graze on been closed because of building, road or ropeway work?</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>पिछले 12 महीनों में, क्या कोई साझा जगह, जहाँ आप पहले लकड़ी, घास या चारा लेते थे, निर्माण, सड़क या रोपवे के काम की वजह से बंद हो गई?</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr"/>
-      <c r="G285" t="inlineStr"/>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H285" t="inlineStr"/>
       <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr"/>
@@ -11714,15 +11742,31 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr"/>
-      <c r="C286" t="inlineStr"/>
-      <c r="D286" t="inlineStr"/>
+          <t>select_one cprwater</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>cpr_water_route</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>On your route or near your worksite, can you use a common water source (spring, tap or stream) without paying?</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>रास्ते पर या काम की जगह के पास, क्या आप कोई साझा पानी का स्रोत (झरना, नल या नदी-नाला) बिना पैसे दिए इस्तेमाल कर सकते हैं?</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr"/>
-      <c r="G286" t="inlineStr"/>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H286" t="inlineStr"/>
       <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr"/>
@@ -11731,6 +11775,85 @@
       <c r="M286" t="inlineStr"/>
       <c r="N286" t="inlineStr"/>
       <c r="O286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>select_one cprgov</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>cpr_governance</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>In this area, who decides who may use the common land and forest? Ask and code what they name; do not read the list.</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>इस इलाके की साझा ज़मीन और जंगल का फ़ैसला कौन करता है, कि कौन उसका इस्तेमाल कर सकता है? जो नाम लें वही लिख लें; सूची न पढ़ें।</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr"/>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr"/>
+      <c r="J287" t="inlineStr"/>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="inlineStr"/>
+      <c r="N287" t="inlineStr"/>
+      <c r="O287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr"/>
+      <c r="C288" t="inlineStr"/>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" t="inlineStr"/>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr"/>
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr"/>
+      <c r="J288" t="inlineStr"/>
+      <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr"/>
+      <c r="M288" t="inlineStr"/>
+      <c r="N288" t="inlineStr"/>
+      <c r="O288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr"/>
+      <c r="C289" t="inlineStr"/>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr"/>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr"/>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr"/>
+      <c r="J289" t="inlineStr"/>
+      <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr"/>
+      <c r="M289" t="inlineStr"/>
+      <c r="N289" t="inlineStr"/>
+      <c r="O289" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11743,7 +11866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E327"/>
+  <dimension ref="A1:E335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17503,7 +17626,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ruralurban</t>
+          <t>ropexp</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -17511,12 +17634,12 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Village (rural)</t>
+          <t>More work for me</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>गाँव में</t>
+          <t>मेरे लिए ज़्यादा काम</t>
         </is>
       </c>
       <c r="E251" t="n">
@@ -17526,7 +17649,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ruralurban</t>
+          <t>ropexp</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -17534,12 +17657,12 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Town or city (urban)</t>
+          <t>Less work for me</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>शहर या क़स्बे में</t>
+          <t>मेरे लिए कम काम</t>
         </is>
       </c>
       <c r="E252" t="n">
@@ -17549,53 +17672,53 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>ropexp</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>About the same</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>पुरुष</t>
+          <t>लगभग वैसा ही</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>ropexp</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Don't know</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>महिला</t>
+          <t>पता नहीं</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>ropjobs</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -17603,12 +17726,12 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Kedarnath (Gaurikund to Kedarnath)</t>
+          <t>People from these villages</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>केदारनाथ (गौरीकुंड से केदारनाथ)</t>
+          <t>इन गाँवों के लोगों को</t>
         </is>
       </c>
       <c r="E255" t="n">
@@ -17618,7 +17741,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>ropjobs</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -17626,12 +17749,12 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Hemkund Sahib (Govindghat to Hemkund)</t>
+          <t>People from outside the area</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>हेमकुंड साहिब (गोविंदघाट से हेमकुंड)</t>
+          <t>इलाके के बाहर के लोगों को</t>
         </is>
       </c>
       <c r="E256" t="n">
@@ -17641,277 +17764,277 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>stance</t>
+          <t>ropjobs</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Nobody will get jobs</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>समर्थन में</t>
+          <t>किसी को नहीं मिलेंगी</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>stance</t>
+          <t>ropjobs</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Don't know</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>तटस्थ</t>
+          <t>पता नहीं</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>2</v>
+        <v>97</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>stance</t>
+          <t>ruralurban</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Oppose</t>
+          <t>Village (rural)</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>विरोध में</t>
+          <t>गाँव में</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>stance</t>
+          <t>ruralurban</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Prefer not to say</t>
+          <t>Town or city (urban)</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>बताना नहीं चाहते</t>
+          <t>शहर या क़स्बे में</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>आंध्र प्रदेश</t>
+          <t>पुरुष</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Arunachal Pradesh</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>अरुणाचल प्रदेश</t>
+          <t>महिला</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>site</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Kedarnath (Gaurikund to Kedarnath)</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>असम</t>
+          <t>केदारनाथ (गौरीकुंड से केदारनाथ)</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>site</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Hemkund Sahib (Govindghat to Hemkund)</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>बिहार</t>
+          <t>हेमकुंड साहिब (गोविंदघाट से हेमकुंड)</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>stance</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>छत्तीसगढ़</t>
+          <t>समर्थन में</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>stance</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>गोवा</t>
+          <t>तटस्थ</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>stance</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Oppose</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>गुजरात</t>
+          <t>विरोध में</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>stance</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Prefer not to say</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>हरियाणा</t>
+          <t>बताना नहीं चाहते</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>8</v>
+        <v>98</v>
       </c>
     </row>
     <row r="269">
@@ -17921,20 +18044,20 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>हिमाचल प्रदेश</t>
+          <t>आंध्र प्रदेश</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -17944,20 +18067,20 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Arunachal Pradesh</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>झारखंड</t>
+          <t>अरुणाचल प्रदेश</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
@@ -17967,20 +18090,20 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>कर्नाटक</t>
+          <t>असम</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272">
@@ -17990,20 +18113,20 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>केरल</t>
+          <t>बिहार</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="273">
@@ -18013,20 +18136,20 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>मध्य प्रदेश</t>
+          <t>छत्तीसगढ़</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="274">
@@ -18036,20 +18159,20 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>महाराष्ट्र</t>
+          <t>गोवा</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="275">
@@ -18059,20 +18182,20 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Manipur</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>मणिपुर</t>
+          <t>गुजरात</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="276">
@@ -18082,20 +18205,20 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Meghalaya</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>मेघालय</t>
+          <t>हरियाणा</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="277">
@@ -18105,20 +18228,20 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>मिज़ोरम</t>
+          <t>हिमाचल प्रदेश</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="278">
@@ -18128,20 +18251,20 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Nagaland</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>नागालैंड</t>
+          <t>झारखंड</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="279">
@@ -18151,20 +18274,20 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>ओडिशा</t>
+          <t>कर्नाटक</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="280">
@@ -18174,20 +18297,20 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>पंजाब</t>
+          <t>केरल</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="281">
@@ -18197,20 +18320,20 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>राजस्थान</t>
+          <t>मध्य प्रदेश</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="282">
@@ -18220,20 +18343,20 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>सिक्किम</t>
+          <t>महाराष्ट्र</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="283">
@@ -18243,20 +18366,20 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Manipur</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>तमिलनाडु</t>
+          <t>मणिपुर</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="284">
@@ -18266,20 +18389,20 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Meghalaya</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>तेलंगाना</t>
+          <t>मेघालय</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="285">
@@ -18289,20 +18412,20 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Tripura</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>त्रिपुरा</t>
+          <t>मिज़ोरम</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="286">
@@ -18312,20 +18435,20 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Nagaland</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>उत्तर प्रदेश</t>
+          <t>नागालैंड</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="287">
@@ -18335,20 +18458,20 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>पश्चिम बंगाल</t>
+          <t>ओडिशा</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="288">
@@ -18358,20 +18481,20 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Andaman and Nicobar Islands</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>अंडमान और निकोबार द्वीप समूह</t>
+          <t>पंजाब</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="289">
@@ -18381,20 +18504,20 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>चंडीगढ़</t>
+          <t>राजस्थान</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="290">
@@ -18404,20 +18527,20 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Dadra and Nagar Haveli and Daman and Diu</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>दादरा और नगर हवेली तथा दमन और दीव</t>
+          <t>सिक्किम</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="291">
@@ -18427,20 +18550,20 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>दिल्ली</t>
+          <t>तमिलनाडु</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="292">
@@ -18450,20 +18573,20 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Jammu and Kashmir</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>जम्मू और कश्मीर</t>
+          <t>तेलंगाना</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="293">
@@ -18473,20 +18596,20 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Ladakh</t>
+          <t>Tripura</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>लद्दाख</t>
+          <t>त्रिपुरा</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="294">
@@ -18496,20 +18619,20 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Lakshadweep</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>लक्षद्वीप</t>
+          <t>उत्तर प्रदेश</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="295">
@@ -18519,434 +18642,434 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Puducherry</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>पुदुच्चेरी</t>
+          <t>पश्चिम बंगाल</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>task3</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Yes, regularly in my main Yatra work</t>
+          <t>Andaman and Nicobar Islands</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>हाँ, अपने मुख्य यात्रा-काम में नियमित</t>
+          <t>अंडमान और निकोबार द्वीप समूह</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>task3</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Not in my main work, but done before elsewhere</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>मुख्य काम में नहीं, पर पहले कहीं और किया है</t>
+          <t>चंडीगढ़</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>task3</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Never done</t>
+          <t>Dadra and Nagar Haveli and Daman and Diu</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>कभी नहीं किया</t>
+          <t>दादरा और नगर हवेली तथा दमन और दीव</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>toilet</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>No toilet / open defecation</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>शौचालय नहीं / खुले में</t>
+          <t>दिल्ली</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>toilet</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Pit latrine without slab or open pit</t>
+          <t>Jammu and Kashmir</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>बिना ढँके गड्ढे वाला शौचालय</t>
+          <t>जम्मू और कश्मीर</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>toilet</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Improved toilet, but shared with other households</t>
+          <t>Ladakh</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>अच्छा शौचालय, पर दूसरे घरों के साथ साझा</t>
+          <t>लद्दाख</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>toilet</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Improved toilet, used only by this household</t>
+          <t>Lakshadweep</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>अच्छा शौचालय, सिर्फ़ इसी घर के लिए</t>
+          <t>लक्षद्वीप</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>wall</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Mud, thatch, bamboo or other natural material</t>
+          <t>Puducherry</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>मिट्टी, फूस, बाँस या ऐसी ही कोई चीज़</t>
+          <t>पुदुच्चेरी</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>wall</t>
+          <t>task3</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Unburnt brick, wood or tin</t>
+          <t>Yes, regularly in my main Yatra work</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>कच्ची ईंट, लकड़ी या टीन</t>
+          <t>हाँ, अपने मुख्य यात्रा-काम में नियमित</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>wall</t>
+          <t>task3</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Burnt brick, cement, concrete or stone</t>
+          <t>Not in my main work, but done before elsewhere</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>पक्की ईंट, सीमेंट, कंक्रीट या पत्थर</t>
+          <t>मुख्य काम में नहीं, पर पहले कहीं और किया है</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>task3</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Piped into the house or yard</t>
+          <t>Never done</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>घर या आँगन में नल</t>
+          <t>कभी नहीं किया</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>toilet</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Public tap or standpipe</t>
+          <t>No toilet / open defecation</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>सार्वजनिक नल या स्टैंडपोस्ट</t>
+          <t>शौचालय नहीं / खुले में</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>toilet</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Handpump, tubewell or borewell</t>
+          <t>Pit latrine without slab or open pit</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>हैंडपंप, ट्यूबवेल या बोरवेल</t>
+          <t>बिना ढँके गड्ढे वाला शौचालय</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>toilet</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Protected well or protected spring</t>
+          <t>Improved toilet, but shared with other households</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>ढका हुआ कुआँ या ढका हुआ सोता</t>
+          <t>अच्छा शौचालय, पर दूसरे घरों के साथ साझा</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>toilet</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Rainwater collection</t>
+          <t>Improved toilet, used only by this household</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>बारिश का पानी जमा करके</t>
+          <t>अच्छा शौचालय, सिर्फ़ इसी घर के लिए</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>wall</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Bottled, packaged or community RO</t>
+          <t>Mud, thatch, bamboo or other natural material</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>बोतलबंद, पैकेट या सामुदायिक RO</t>
+          <t>मिट्टी, फूस, बाँस या ऐसी ही कोई चीज़</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>wall</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Unprotected well or unprotected spring</t>
+          <t>Unburnt brick, wood or tin</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>खुला कुआँ या खुला सोता</t>
+          <t>कच्ची ईंट, लकड़ी या टीन</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>wall</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>River, stream, pond or canal</t>
+          <t>Burnt brick, cement, concrete or stone</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>नदी, गाड़, तालाब या नहर</t>
+          <t>पक्की ईंट, सीमेंट, कंक्रीट या पत्थर</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -18956,318 +19079,502 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Tanker truck or cart with drum</t>
+          <t>Piped into the house or yard</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>टैंकर या ड्रम वाली गाड़ी</t>
+          <t>घर या आँगन में नल</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>wgdiff</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>No difficulty</t>
+          <t>Public tap or standpipe</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>कोई दिक़्क़त नहीं</t>
+          <t>सार्वजनिक नल या स्टैंडपोस्ट</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>wgdiff</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Some difficulty</t>
+          <t>Handpump, tubewell or borewell</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>थोड़ी दिक़्क़त</t>
+          <t>हैंडपंप, ट्यूबवेल या बोरवेल</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>wgdiff</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>A lot of difficulty</t>
+          <t>Protected well or protected spring</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>बहुत दिक़्क़त</t>
+          <t>ढका हुआ कुआँ या ढका हुआ सोता</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>wgdiff</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Cannot do it at all</t>
+          <t>Rainwater collection</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>बिलकुल नहीं कर पाते</t>
+          <t>बारिश का पानी जमा करके</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>workins</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Yes, through work</t>
+          <t>Bottled, packaged or community RO</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>हाँ, काम की तरफ़ से</t>
+          <t>बोतलबंद, पैकेट या सामुदायिक RO</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>workins</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Only private or other insurance</t>
+          <t>Unprotected well or unprotected spring</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>सिर्फ़ अपना या कोई और बीमा</t>
+          <t>खुला कुआँ या खुला सोता</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>workins</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>River, stream, pond or canal</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>कोई नहीं</t>
+          <t>नदी, गाड़, तालाब या नहर</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>workins</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Don't know</t>
+          <t>Tanker truck or cart with drum</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>पता नहीं</t>
+          <t>टैंकर या ड्रम वाली गाड़ी</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>yn</t>
+          <t>wgdiff</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No difficulty</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>नहीं</t>
+          <t>कोई दिक़्क़त नहीं</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>yn</t>
+          <t>wgdiff</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some difficulty</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>हाँ</t>
+          <t>थोड़ी दिक़्क़त</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>yndk</t>
+          <t>wgdiff</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>A lot of difficulty</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>नहीं</t>
+          <t>बहुत दिक़्क़त</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>yndk</t>
+          <t>wgdiff</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot do it at all</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>हाँ</t>
+          <t>बिलकुल नहीं कर पाते</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
+          <t>workins</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>1</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Yes, through work</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>हाँ, काम की तरफ़ से</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>workins</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>2</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Only private or other insurance</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>सिर्फ़ अपना या कोई और बीमा</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>workins</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>3</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>कोई नहीं</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>workins</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>4</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Don't know</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>पता नहीं</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>yn</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>0</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>नहीं</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>yn</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>1</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>हाँ</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
           <t>yndk</t>
         </is>
       </c>
-      <c r="B327" t="n">
+      <c r="B333" t="n">
+        <v>0</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>नहीं</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>yndk</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>1</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>हाँ</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>yndk</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
         <v>97</v>
       </c>
-      <c r="C327" t="inlineStr">
+      <c r="C335" t="inlineStr">
         <is>
           <t>Don't know</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr">
+      <c r="D335" t="inlineStr">
         <is>
           <t>पता नहीं</t>
         </is>
       </c>
-      <c r="E327" t="n">
+      <c r="E335" t="n">
         <v>97</v>
       </c>
     </row>

--- a/Kedarnath_final_kobo.xlsx
+++ b/Kedarnath_final_kobo.xlsx
@@ -740,7 +740,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>${consent}</t>
+          <t>${consent} = 1</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>

--- a/Kedarnath_final_kobo.xlsx
+++ b/Kedarnath_final_kobo.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O288"/>
+  <dimension ref="A1:O289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -768,7 +768,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>'2026-10-05.cce909'</t>
+          <t>'2026-10-05.4b87e5'</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1889,47 +1889,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one wageemp</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>n_other_activities</t>
+          <t>wage_employer</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Besides your main work, how many OTHER paid activities or income-generating activities do you have? (0 if none. For example, a shop owner who also rents out a pony and drives in the off-season would say 2.)</t>
+          <t>Who employs you? A private company; a government or public body; a household (domestic work); a contractor or agent; or an individual employer?</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>अपने मुख्य काम के अलावा, आप और कितने काम करते हैं जिनसे पैसा आता है? (अगर कोई नहीं तो 0। जैसे, दुकान वाला जो घोड़ा भी किराये पर देता है और जाड़ों में गाड़ी चलाता है, वह 2 बताएगा।)</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>आपको काम पर कौन रखता है? कोई निजी कंपनी; सरकारी या सार्वजनिक विभाग; कोई घर (घरेलू काम); ठेकेदार या एजेंट; या कोई व्यक्ति जो सीधे पैसे देता है?</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ENUMERATOR: private company = a registered firm or hotel chain; government or public body = a government department, Yatra board, PWD or other public office; household = a family that hires them for domestic work; contractor or agent = a thekedar or agent who arranged and pays for the work; individual employer = one person who pays them directly, such as a shop or dhaba owner. If the respondent says 'the owner' or 'the boss' without more, ask who arranged the job. If they came through an agent (see the migration referral question), code 4. If unsure, code 97 and write the words in the notes.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>सर्वेक्षक के लिए: निजी कंपनी = रजिस्टर्ड फ़र्म या होटल; सरकारी = सरकारी विभाग, बोर्ड या सार्वजनिक दफ़्तर; घर = परिवार जो घरेलू काम कराता है; ठेकेदार या एजेंट = जिसने काम दिलाया और पैसे देता है; व्यक्ति = एक आदमी जो सीधे पैसे देता है, जैसे दुकान या ढाबे का मालिक। अगर सिर्फ़ 'मालिक' कहें तो पूछें काम किसने दिलाया। अगर एजेंट के ज़रिए आए हों तो 4 चुनें। पक्का न हो तो 97 चुनें और शब्द नोट में लिखें।</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 6</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Must be between 0 and 6.</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>0 से 6 के बीच होना चाहिए।</t>
-        </is>
-      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>${employment_type} = 3 or ${employment_type} = 4</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -1938,22 +1938,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>select_multiple occ</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>other_activity_types</t>
+          <t>n_other_activities</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Which ones are they? Check every one that applies. Ask and code the closest group for each; do not read the list aloud unless needed.</t>
+          <t>Besides your main work, how many OTHER paid activities or income-generating activities do you have? (0 if none. For example, a shop owner who also rents out a pony and drives in the off-season would say 2.)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>वे कौन-कौन से काम हैं? जो-जो लागू हो, सब बताइए।</t>
+          <t>अपने मुख्य काम के अलावा, आप और कितने काम करते हैं जिनसे पैसा आता है? (अगर कोई नहीं तो 0। जैसे, दुकान वाला जो घोड़ा भी किराये पर देता है और जाड़ों में गाड़ी चलाता है, वह 2 बताएगा।)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1963,42 +1963,46 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>${n_other_activities} &gt; 0</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 6</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Must be between 0 and 6.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0 से 6 के बीच होना चाहिए।</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>code != ${occupation}</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_multiple occ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>other_activity_income_pm</t>
+          <t>other_activity_types</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Taking all of that other work together, about how much do you usually earn from it in a month? (Rs)</t>
+          <t>Which ones are they? Check every one that applies. Ask and code the closest group for each; do not read the list aloud unless needed.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>वह सारा दूसरा काम मिलाकर, महीने में लगभग कितना कमा लेते हैं? (रुपये)</t>
+          <t>वे कौन-कौन से काम हैं? जो-जो लागू हो, सब बताइए।</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2013,66 +2017,66 @@
           <t>${n_other_activities} &gt; 0</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>. &gt;= 0</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Earnings cannot be negative.</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Earnings cannot be negative.</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>code != ${occupation}</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>tenure_under_1</t>
+          <t>other_activity_income_pm</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Have you been in this job for less than one year?</t>
+          <t>Taking all of that other work together, about how much do you usually earn from it in a month? (Rs)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>क्या आप इस काम में एक साल से कम से हैं?</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>ENUMERATOR: tick Yes if the person has been in this job for less than one year. Do not ask for months. If Yes, skip the years question.</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>अगर वे इस काम में एक साल से कम से हैं तो हाँ चुनें। महीने न पूछें।</t>
-        </is>
-      </c>
+          <t>वह सारा दूसरा काम मिलाकर, महीने में लगभग कितना कमा लेते हैं? (रुपये)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>${n_other_activities} &gt; 0</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -2081,32 +2085,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>years_current_job</t>
+          <t>tenure_under_1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>If one year or more: how many years have you been in this job? Write it as a decimal if needed, for example 1.5 for one year and six months.</t>
+          <t>Have you been in this job for less than one year?</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>अगर एक साल या ज़्यादा: आप इस काम में कितने साल से हैं? दशमलव में लिखें, जैसे डेढ़ साल के लिए 1.5।</t>
+          <t>क्या आप इस काम में एक साल से कम से हैं?</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ENUMERATOR: only if the person has been in this job one year or more. Write the number of years; use a decimal for part years (1.5 = one year and six months).</t>
+          <t>ENUMERATOR: tick Yes if the person has been in this job for less than one year. Do not ask for months. If Yes, skip the years question.</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>अगर वे एक साल या उससे ज़्यादा से हैं तो साल लिखें। आधा या चौथाई साल हो तो दशमलव में लिखें (1.5 मतलब डेढ़ साल)।</t>
+          <t>अगर वे इस काम में एक साल से कम से हैं तो हाँ चुनें। महीने न पूछें।</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2114,26 +2118,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>${tenure_under_1} = 0</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= ${age} - 10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>More Yatra seasons than the respondent's age allows.</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>More Yatra seasons than the respondent's age allows.</t>
-        </is>
-      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
@@ -2142,45 +2130,57 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>hours_day_yatra</t>
+          <t>years_current_job</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>In the Yatra season, on a normal working day, how many hours do you work in total, across all your work?</t>
+          <t>If one year or more: how many years have you been in this job? Write it as a decimal if needed, for example 1.5 for one year and six months.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम में, आम दिन में आप कुल कितने घंटे काम करते हैं, सारे कामों को मिलाकर?</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+          <t>अगर एक साल या ज़्यादा: आप इस काम में कितने साल से हैं? दशमलव में लिखें, जैसे डेढ़ साल के लिए 1.5।</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ENUMERATOR: only if the person has been in this job one year or more. Write the number of years; use a decimal for part years (1.5 = one year and six months).</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>अगर वे एक साल या उससे ज़्यादा से हैं तो साल लिखें। आधा या चौथाई साल हो तो दशमलव में लिखें (1.5 मतलब डेढ़ साल)।</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>${tenure_under_1} = 0</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>. &gt;= 1 and . &lt;= 18</t>
+          <t>. &gt;= 0 and . &lt;= ${age} - 10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Hours a day must be between 1 and 18.</t>
+          <t>More Yatra seasons than the respondent's age allows.</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>दिन के घंटे 1 से 18 के बीच होने चाहिए।</t>
+          <t>More Yatra seasons than the respondent's age allows.</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -2196,17 +2196,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>days_week_yatra</t>
+          <t>hours_day_yatra</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>How many days a week do you usually work in the season?</t>
+          <t>In the Yatra season, on a normal working day, how many hours do you work in total, across all your work?</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>सीज़न में आप हफ़्ते में कितने दिन काम करते हैं?</t>
+          <t>यात्रा के मौसम में, आम दिन में आप कुल कितने घंटे काम करते हैं, सारे कामों को मिलाकर?</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2219,17 +2219,17 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>. &gt;= 1 and . &lt;= 7</t>
+          <t>. &gt;= 1 and . &lt;= 18</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Days a week must be between 1 and 7.</t>
+          <t>Hours a day must be between 1 and 18.</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>हफ़्ते के दिन 1 से 7 के बीच होने चाहिए।</t>
+          <t>दिन के घंटे 1 से 18 के बीच होने चाहिए।</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -2240,22 +2240,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>prev_occ_change</t>
+          <t>days_week_yatra</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>In the last ten years, did you change your main kind of work?</t>
+          <t>How many days a week do you usually work in the season?</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>पिछले दस साल में, क्या आपने अपना मुख्य काम बदला?</t>
+          <t>सीज़न में आप हफ़्ते में कितने दिन काम करते हैं?</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2266,9 +2266,21 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 7</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Days a week must be between 1 and 7.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>हफ़्ते के दिन 1 से 7 के बीच होने चाहिए।</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -2277,22 +2289,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>prev_occ</t>
+          <t>prev_occ_change</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>What was your previous main work? Write down exactly what they say, in their words — do not pick from a list.</t>
+          <t>In the last ten years, did you change your main kind of work?</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>इससे पहले आपका मुख्य काम क्या था?</t>
+          <t>पिछले दस साल में, क्या आपने अपना मुख्य काम बदला?</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2302,11 +2314,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>${prev_occ_change} = 1</t>
-        </is>
-      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -2323,17 +2331,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>target_occ</t>
+          <t>prev_occ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>If you could not continue this work at all, what work would you move to instead? Write down exactly what they say, in their words — do not pick from a list, and do not prompt with examples.</t>
+          <t>What was your previous main work? Write down exactly what they say, in their words — do not pick from a list.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>अगर यह काम बिल्कुल बंद हो जाए, तो आप कौन सा काम करेंगे?</t>
+          <t>इससे पहले आपका मुख्य काम क्या था?</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2343,7 +2351,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>${prev_occ_change} = 1</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -2355,22 +2367,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>select_one prevreason</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>prev_occ_reason</t>
+          <t>target_occ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>What was the main reason you changed?</t>
+          <t>If you could not continue this work at all, what work would you move to instead? Write down exactly what they say, in their words — do not pick from a list, and do not prompt with examples.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>काम बदलने की मुख्य वजह क्या थी?</t>
+          <t>अगर यह काम बिल्कुल बंद हो जाए, तो आप कौन सा काम करेंगे?</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2380,11 +2392,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>${prev_occ_change} = 1</t>
-        </is>
-      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -2396,22 +2404,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one prevreason</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>training_received</t>
+          <t>prev_occ_reason</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Apart from school and college, have you ever completed any training course or apprenticeship?</t>
+          <t>What was the main reason you changed?</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>स्कूल और कॉलेज की पढ़ाई छोड़कर, क्या आपने कभी कोई ट्रेनिंग या सीखने का कोर्स पूरा किया है?</t>
+          <t>काम बदलने की मुख्य वजह क्या थी?</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2421,7 +2429,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>${prev_occ_change} = 1</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -2433,15 +2445,31 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+          <t>select_one yn</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>training_received</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Apart from school and college, have you ever completed any training course or apprenticeship?</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>स्कूल और कॉलेज की पढ़ाई छोड़कर, क्या आपने कभी कोई ट्रेनिंग या सीखने का कोर्स पूरा किया है?</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
@@ -2454,24 +2482,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>grp_C</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Module C: Monthly calendar of work and income</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Module C: Monthly calendar of work and income</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
@@ -2482,31 +2498,27 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>intro_C</t>
+          <t>grp_C</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Now I want to go through the last twelve months, one month at a time. For each month I will ask what work you were mainly doing, and then what you usually earned. It is easiest to start with the Yatra months and fill the rest afterwards.</t>
+          <t>Module C: Monthly calendar of work and income</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>अब मैं पिछले बारह महीनों के बारे में, एक-एक महीना करके पूछूँगा। हर महीने के लिए पूछूँगा कि आप मुख्य रूप से क्या काम कर रहे थे, और फिर यह कि आमतौर पर कितना कमाया। सबसे आसान यह रहता है कि पहले यात्रा वाले महीने भर लें, बाक़ी बाद में।</t>
+          <t>Module C: Monthly calendar of work and income</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2519,36 +2531,36 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>select_one activity</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>status_m5</t>
+          <t>intro_C</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>In May, what was your main work or activity?</t>
+          <t>Now I want to go through the last twelve months, one month at a time. For each month I will ask what work you were mainly doing, and then what you usually earned. It is easiest to start with the Yatra months and fill the rest afterwards.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>मई में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>अब मैं पिछले बारह महीनों के बारे में, एक-एक महीना करके पूछूँगा। हर महीने के लिए पूछूँगा कि आप मुख्य रूप से क्या काम कर रहे थे, और फिर यह कि आमतौर पर कितना कमाया। सबसे आसान यह रहता है कि पहले यात्रा वाले महीने भर लें, बाक़ी बाद में।</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
@@ -2566,17 +2578,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>status_m6</t>
+          <t>status_m5</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>In June, what was your main work or activity?</t>
+          <t>In May, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>जून में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>मई में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2603,17 +2615,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>status_m7</t>
+          <t>status_m6</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>In July, what was your main work or activity?</t>
+          <t>In June, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>जुलाई में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>जून में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2640,17 +2652,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>status_m8</t>
+          <t>status_m7</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>In August, what was your main work or activity?</t>
+          <t>In July, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>अगस्त में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>जुलाई में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2677,17 +2689,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>status_m9</t>
+          <t>status_m8</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>In September, what was your main work or activity?</t>
+          <t>In August, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>सितंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>अगस्त में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2714,17 +2726,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>status_m10</t>
+          <t>status_m9</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>In October, what was your main work or activity?</t>
+          <t>In September, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>अक्टूबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>सितंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2751,17 +2763,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>status_m11</t>
+          <t>status_m10</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>In November, what was your main work or activity?</t>
+          <t>In October, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>नवंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>अक्टूबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2788,17 +2800,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>status_m12</t>
+          <t>status_m11</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>In December, what was your main work or activity?</t>
+          <t>In November, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>दिसंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>नवंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -2820,36 +2832,36 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>select_one activity</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>calc_months_no_work</t>
+          <t>status_m12</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>months with no paid work (hidden)</t>
+          <t>In December, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>months with no paid work (hidden)</t>
+          <t>दिसंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>if(${status_m1}=8,1,0) + if(${status_m2}=8,1,0) + if(${status_m3}=8,1,0) + if(${status_m4}=8,1,0) + if(${status_m5}=8,1,0) + if(${status_m6}=8,1,0) + if(${status_m7}=8,1,0) + if(${status_m8}=8,1,0) + if(${status_m9}=8,1,0) + if(${status_m10}=8,1,0) + if(${status_m11}=8,1,0) + if(${status_m12}=8,1,0)</t>
-        </is>
-      </c>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
@@ -2862,17 +2874,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>calc_offseason_work</t>
+          <t>calc_months_no_work</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>months of other paid work (hidden)</t>
+          <t>months with no paid work (hidden)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>months of other paid work (hidden)</t>
+          <t>months with no paid work (hidden)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2884,7 +2896,7 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>if(${status_m1}&gt;=2 and ${status_m1}&lt;=7,1,0) + if(${status_m2}&gt;=2 and ${status_m2}&lt;=7,1,0) + if(${status_m3}&gt;=2 and ${status_m3}&lt;=7,1,0) + if(${status_m4}&gt;=2 and ${status_m4}&lt;=7,1,0) + if(${status_m5}&gt;=2 and ${status_m5}&lt;=7,1,0) + if(${status_m6}&gt;=2 and ${status_m6}&lt;=7,1,0) + if(${status_m7}&gt;=2 and ${status_m7}&lt;=7,1,0) + if(${status_m8}&gt;=2 and ${status_m8}&lt;=7,1,0) + if(${status_m9}&gt;=2 and ${status_m9}&lt;=7,1,0) + if(${status_m10}&gt;=2 and ${status_m10}&lt;=7,1,0) + if(${status_m11}&gt;=2 and ${status_m11}&lt;=7,1,0) + if(${status_m12}&gt;=2 and ${status_m12}&lt;=7,1,0)</t>
+          <t>if(${status_m1}=8,1,0) + if(${status_m2}=8,1,0) + if(${status_m3}=8,1,0) + if(${status_m4}=8,1,0) + if(${status_m5}=8,1,0) + if(${status_m6}=8,1,0) + if(${status_m7}=8,1,0) + if(${status_m8}=8,1,0) + if(${status_m9}=8,1,0) + if(${status_m10}=8,1,0) + if(${status_m11}=8,1,0) + if(${status_m12}=8,1,0)</t>
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
@@ -2894,36 +2906,36 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>select_one activity</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>status_m1</t>
+          <t>calc_offseason_work</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>In January, what was your main work or activity?</t>
+          <t>months of other paid work (hidden)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>जनवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>months of other paid work (hidden)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>if(${status_m1}&gt;=2 and ${status_m1}&lt;=7,1,0) + if(${status_m2}&gt;=2 and ${status_m2}&lt;=7,1,0) + if(${status_m3}&gt;=2 and ${status_m3}&lt;=7,1,0) + if(${status_m4}&gt;=2 and ${status_m4}&lt;=7,1,0) + if(${status_m5}&gt;=2 and ${status_m5}&lt;=7,1,0) + if(${status_m6}&gt;=2 and ${status_m6}&lt;=7,1,0) + if(${status_m7}&gt;=2 and ${status_m7}&lt;=7,1,0) + if(${status_m8}&gt;=2 and ${status_m8}&lt;=7,1,0) + if(${status_m9}&gt;=2 and ${status_m9}&lt;=7,1,0) + if(${status_m10}&gt;=2 and ${status_m10}&lt;=7,1,0) + if(${status_m11}&gt;=2 and ${status_m11}&lt;=7,1,0) + if(${status_m12}&gt;=2 and ${status_m12}&lt;=7,1,0)</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
@@ -2936,17 +2948,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>status_m2</t>
+          <t>status_m1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>In February, what was your main work or activity?</t>
+          <t>In January, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>फ़रवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>जनवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2973,17 +2985,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>status_m3</t>
+          <t>status_m2</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>In March, what was your main work or activity?</t>
+          <t>In February, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>मार्च में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>फ़रवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3010,17 +3022,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>status_m4</t>
+          <t>status_m3</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>In April, what was your main work or activity?</t>
+          <t>In March, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>अप्रैल में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>मार्च में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3042,27 +3054,31 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>select_one recall</t>
+          <t>select_one activity</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>knows_monthly_income</t>
+          <t>status_m4</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Can you tell me roughly what you earned in each month of the past year, or would it be easier to give one total for the whole year?</t>
+          <t>In April, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>क्या आप हर महीने की कमाई अलग-अलग बता सकते हैं, या पूरे साल का एक जोड़ बताना आसान रहेगा?</t>
+          <t>अप्रैल में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
@@ -3075,36 +3091,28 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>select_one earnrange</t>
+          <t>select_one recall</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>earnings_range</t>
+          <t>knows_monthly_income</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Which range is closest to what you usually earn in a month from work? Under Rs 5,000; Rs 5,000 to 10,000; Rs 10,000 to 20,000; Rs 20,000 or more; or don't know?</t>
+          <t>Can you tell me roughly what you earned in each month of the past year, or would it be easier to give one total for the whole year?</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>आपकी एक महीने की कमाई लगभग किस दायरे में है? 5,000 रुपये से कम; 5,000 से 10,000; 10,000 से 20,000; 20,000 या उससे ज़्यादा; या पता नहीं?</t>
+          <t>क्या आप हर महीने की कमाई अलग-अलग बता सकते हैं, या पूरे साल का एक जोड़ बताना आसान रहेगा?</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>${knows_monthly_income} = 0</t>
-        </is>
-      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
@@ -3116,47 +3124,39 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one earnrange</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>income_m5</t>
+          <t>earnings_range</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in May, after costs? (Rs)</t>
+          <t>Which range is closest to what you usually earn in a month from work? Under Rs 5,000; Rs 5,000 to 10,000; Rs 10,000 to 20,000; Rs 20,000 or more; or don't know?</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>मई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>आपकी एक महीने की कमाई लगभग किस दायरे में है? 5,000 रुपये से कम; 5,000 से 10,000; 10,000 से 20,000; 20,000 या उससे ज़्यादा; या पता नहीं?</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m5} != 8</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>. &gt;= 0</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>Earnings cannot be negative.</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Earnings cannot be negative.</t>
-        </is>
-      </c>
+          <t>${knows_monthly_income} = 0</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
@@ -3170,17 +3170,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>income_m6</t>
+          <t>income_m5</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in June, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in May, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>जून में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>मई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -3188,7 +3188,7 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m6} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m5} != 8</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3219,17 +3219,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>income_m7</t>
+          <t>income_m6</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in July, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in June, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>जुलाई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जून में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -3237,7 +3237,7 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m7} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m6} != 8</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3268,17 +3268,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>income_m8</t>
+          <t>income_m7</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in August, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in July, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>अगस्त में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जुलाई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -3286,7 +3286,7 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m8} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m7} != 8</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3317,17 +3317,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>income_m9</t>
+          <t>income_m8</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in September, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in August, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>सितंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अगस्त में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -3335,7 +3335,7 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m9} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m8} != 8</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3366,17 +3366,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>income_m10</t>
+          <t>income_m9</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in October, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in September, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>अक्टूबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>सितंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -3384,7 +3384,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m10} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m9} != 8</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3415,17 +3415,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>income_m11</t>
+          <t>income_m10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in November, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in October, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>नवंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अक्टूबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3433,7 +3433,7 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m11} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m10} != 8</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3464,17 +3464,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>income_m12</t>
+          <t>income_m11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in December, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in November, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>दिसंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>नवंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3482,7 +3482,7 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m12} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m11} != 8</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3513,17 +3513,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>income_m1</t>
+          <t>income_m12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in January, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in December, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>जनवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>दिसंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -3531,7 +3531,7 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m1} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m12} != 8</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3562,17 +3562,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>income_m2</t>
+          <t>income_m1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in February, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in January, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>फ़रवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जनवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3580,7 +3580,7 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m2} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m1} != 8</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>income_m3</t>
+          <t>income_m2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in March, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in February, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>मार्च में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>फ़रवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3629,7 +3629,7 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m3} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m2} != 8</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3660,17 +3660,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>income_m4</t>
+          <t>income_m3</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in April, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in March, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>अप्रैल में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>मार्च में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -3678,7 +3678,7 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m4} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m3} != 8</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3709,17 +3709,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>income_annual_total</t>
+          <t>income_m4</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Thinking of the whole past year, about how much did you earn in total from all your work, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in April, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>पूरे पिछले साल को मिलाकर, सारे काम से ख़र्चा निकालकर आपने कुल कितना कमाया? (रुपये)</t>
+          <t>अप्रैल में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3727,12 +3727,24 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 0</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+          <t>${knows_monthly_income} = 1 and ${status_m4} != 8</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
@@ -3746,17 +3758,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>pct_income_yatra</t>
+          <t>income_annual_total</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Out of every 100 rupees you earned in the whole year, how many came from your Yatra work? (The rest is counted as coming from your other work.)</t>
+          <t>Thinking of the whole past year, about how much did you earn in total from all your work, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>पूरे साल में आपने जो 100 रुपये कमाए, उनमें से कितने यात्रा के काम से आए? (बाकी दूसरे काम का माना जाएगा।)</t>
+          <t>पूरे पिछले साल को मिलाकर, सारे काम से ख़र्चा निकालकर आपने कुल कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3767,21 +3779,9 @@
           <t>${knows_monthly_income} = 0</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 100</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Must be between 0 and 100 out of every 100 rupees.</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>हर 100 रुपये में से 0 से 100 के बीच होना चाहिए।</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
@@ -3795,44 +3795,40 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>hours_day_offseason</t>
+          <t>pct_income_yatra</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>In the months when the Yatra is closed and you are doing other work, on a normal working day, how many hours do you work in total?</t>
+          <t>Out of every 100 rupees you earned in the whole year, how many came from your Yatra work? (The rest is counted as coming from your other work.)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>जिन महीनों में यात्रा बंद रहती है और आप कोई दूसरा काम करते हैं, उनमें आम दिन में आप कुल कितने घंटे काम करते हैं?</t>
+          <t>पूरे साल में आपने जो 100 रुपये कमाए, उनमें से कितने यात्रा के काम से आए? (बाकी दूसरे काम का माना जाएगा।)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>${calc_offseason_work} &gt; 0</t>
+          <t>${knows_monthly_income} = 0</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>. &gt;= 1 and . &lt;= 18</t>
+          <t>. &gt;= 0 and . &lt;= 100</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Hours a day must be between 1 and 18.</t>
+          <t>Must be between 0 and 100 out of every 100 rupees.</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>दिन के घंटे 1 से 18 के बीच होने चाहिए।</t>
+          <t>हर 100 रुपये में से 0 से 100 के बीच होना चाहिए।</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -3848,17 +3844,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>days_week_offseason</t>
+          <t>hours_day_offseason</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>In those months, how many days a week do you usually work?</t>
+          <t>In the months when the Yatra is closed and you are doing other work, on a normal working day, how many hours do you work in total?</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>उन महीनों में आप हफ़्ते में कितने दिन काम करते हैं?</t>
+          <t>जिन महीनों में यात्रा बंद रहती है और आप कोई दूसरा काम करते हैं, उनमें आम दिन में आप कुल कितने घंटे काम करते हैं?</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3875,17 +3871,17 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>. &gt;= 1 and . &lt;= 7</t>
+          <t>. &gt;= 1 and . &lt;= 18</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Days a week must be between 1 and 7.</t>
+          <t>Hours a day must be between 1 and 18.</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>हफ़्ते के दिन 1 से 7 के बीच होने चाहिए।</t>
+          <t>दिन के घंटे 1 से 18 के बीच होने चाहिए।</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -3896,19 +3892,51 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>days_week_offseason</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>In those months, how many days a week do you usually work?</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>उन महीनों में आप हफ़्ते में कितने दिन काम करते हैं?</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>${calc_offseason_work} &gt; 0</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 7</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Days a week must be between 1 and 7.</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>हफ़्ते के दिन 1 से 7 के बीच होने चाहिए।</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
@@ -3917,24 +3945,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>grp_D</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Module D: Migration, home place and remittances</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Module D: Migration, home place and remittances</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
@@ -3945,31 +3961,27 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>intro_D</t>
+          <t>grp_D</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Now a few questions about where your home is, and what you do when the Yatra closes for the season.</t>
+          <t>Module D: Migration, home place and remittances</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>अब कुछ सवाल इस बारे में कि आपका घर कहाँ है, और यात्रा का मौसम ख़त्म होने पर आप क्या करते हैं।</t>
+          <t>Module D: Migration, home place and remittances</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3982,36 +3994,36 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>select_one origin</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>origin</t>
+          <t>intro_D</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Where is your permanent home?</t>
+          <t>Now a few questions about where your home is, and what you do when the Yatra closes for the season.</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>आपका पक्का घर कहाँ है?</t>
+          <t>अब कुछ सवाल इस बारे में कि आपका घर कहाँ है, और यात्रा का मौसम ख़त्म होने पर आप क्या करते हैं।</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
@@ -4024,22 +4036,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>select_one state</t>
+          <t>select_one origin</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>home_state</t>
+          <t>origin</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Which state is your permanent home in?</t>
+          <t>Where is your permanent home?</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>वह घर किस राज्य में है? (अगर भारत से बाहर है तो वह बताइए।)</t>
+          <t>आपका पक्का घर कहाँ है?</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -4049,11 +4061,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>${origin} = 3</t>
-        </is>
-      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
@@ -4065,22 +4073,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>select_one ruralurban</t>
+          <t>select_one state</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>home_rural_urban</t>
+          <t>home_state</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Is that home in a village, or in a town or city?</t>
+          <t>Which state is your permanent home in?</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>वह घर गाँव में है, या क़स्बे या शहर में?</t>
+          <t>वह घर किस राज्य में है? (अगर भारत से बाहर है तो वह बताइए।)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -4090,7 +4098,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>${origin} = 3</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
@@ -4102,22 +4114,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one ruralurban</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>resp_returns_at_closure</t>
+          <t>home_rural_urban</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>When the Yatra closes for the season, do YOU go to your home place?</t>
+          <t>Is that home in a village, or in a town or city?</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>जब यात्रा का मौसम ख़त्म हो जाता है, तो क्या आप अपने घर चले जाते हैं?</t>
+          <t>वह घर गाँव में है, या क़स्बे या शहर में?</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -4144,17 +4156,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>hh_at_home_place</t>
+          <t>resp_returns_at_closure</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>For most of the year, do the rest of your household live in your home village or town?</t>
+          <t>When the Yatra closes for the season, do YOU go to your home place?</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>साल के ज़्यादातर समय, क्या आपके घर के बाक़ी लोग आपके गाँव या शहर में ही रहते हैं?</t>
+          <t>जब यात्रा का मौसम ख़त्म हो जाता है, तो क्या आप अपने घर चले जाते हैं?</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -4176,22 +4188,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>remit_out_yatra_pm</t>
+          <t>hh_at_home_place</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much money do you usually send to family or others living elsewhere? (Rs, 0 if none)</t>
+          <t>For most of the year, do the rest of your household live in your home village or town?</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप घर या कहीं और रहने वालों को कितना पैसा भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
+          <t>साल के ज़्यादातर समय, क्या आपके घर के बाक़ी लोग आपके गाँव या शहर में ही रहते हैं?</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -4218,17 +4230,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>remit_out_offseason_pm</t>
+          <t>remit_out_yatra_pm</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much do you usually send? (Rs, 0 if none)</t>
+          <t>In a normal month during the Yatra season, how much money do you usually send to family or others living elsewhere? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप घर या कहीं और रहने वालों को कितना पैसा भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -4238,11 +4250,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>${resp_returns_at_closure} = 0</t>
-        </is>
-      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -4254,22 +4262,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>select_one remitmode</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>remit_mode</t>
+          <t>remit_out_offseason_pm</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>How do you usually send it?</t>
+          <t>In a normal month when the Yatra is closed, how much do you usually send? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>आप पैसा आम तौर पर कैसे भेजते हैं?</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -4281,7 +4289,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>${remit_out_yatra_pm} &gt; 0 or ${remit_out_offseason_pm} &gt; 0</t>
+          <t>${resp_returns_at_closure} = 0</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -4295,22 +4303,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one remitmode</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>remit_in_yatra_pm</t>
+          <t>remit_mode</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much money do you usually receive from family or others? (Rs, 0 if none)</t>
+          <t>How do you usually send it?</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, घरवालों या किसी और से आपको कितना पैसा मिलता है? (रुपये, न मिलता हो तो 0)</t>
+          <t>आप पैसा आम तौर पर कैसे भेजते हैं?</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -4320,7 +4328,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>${remit_out_yatra_pm} &gt; 0 or ${remit_out_offseason_pm} &gt; 0</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -4337,17 +4349,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>remit_in_offseason_pm</t>
+          <t>remit_in_yatra_pm</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much do you usually receive? (Rs, 0 if none)</t>
+          <t>In a normal month during the Yatra season, how much money do you usually receive from family or others? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना मिलता है? (रुपये, न मिलता हो तो 0)</t>
+          <t>यात्रा के मौसम के आम महीने में, घरवालों या किसी और से आपको कितना पैसा मिलता है? (रुपये, न मिलता हो तो 0)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -4374,17 +4386,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>n_here_season</t>
+          <t>remit_in_offseason_pm</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>During the Yatra season, how many people are you feeding and spending on here, counting yourself?</t>
+          <t>In a normal month when the Yatra is closed, how much do you usually receive? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम में आप यहाँ कितने लोगों का खाना-ख़र्चा चलाते हैं, अपने आप को गिनकर?</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना मिलता है? (रुपये, न मिलता हो तो 0)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -4394,11 +4406,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>${hh_at_home_place} = 1</t>
-        </is>
-      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -4415,17 +4423,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>years_coming_here</t>
+          <t>n_here_season</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>How many years have you been coming here for the Yatra season?</t>
+          <t>During the Yatra season, how many people are you feeding and spending on here, counting yourself?</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>आप कितने सालों से यात्रा के मौसम में यहाँ आ रहे हैं?</t>
+          <t>यात्रा के मौसम में आप यहाँ कितने लोगों का खाना-ख़र्चा चलाते हैं, अपने आप को गिनकर?</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -4437,7 +4445,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>${resp_returns_at_closure} = 1</t>
+          <t>${hh_at_home_place} = 1</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -4451,22 +4459,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>select_one comereason</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>came_here_reason</t>
+          <t>years_coming_here</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>What was the main reason you first came here to work?</t>
+          <t>How many years have you been coming here for the Yatra season?</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>आप सबसे पहले यहाँ काम करने किस मुख्य वजह से आए थे?</t>
+          <t>आप कितने सालों से यात्रा के मौसम में यहाँ आ रहे हैं?</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -4478,7 +4486,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>${origin} != 1</t>
+          <t>${resp_returns_at_closure} = 1</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -4492,30 +4500,34 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one comereason</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>came_here_reason_other</t>
+          <t>came_here_reason</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>What was that reason? Write down what they say.</t>
+          <t>What was the main reason you first came here to work?</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>वह वजह क्या थी? जो वे कहें वही लिख लें।</t>
+          <t>आप सबसे पहले यहाँ काम करने किस मुख्य वजह से आए थे?</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>${came_here_reason} = 8</t>
+          <t>${origin} != 1</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -4529,32 +4541,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>worked_away_in_closure</t>
+          <t>came_here_reason_other</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Last year, in the months when the Yatra was closed, did you work away from your home place?</t>
+          <t>What was that reason? Write down what they say.</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>पिछले साल, जिन महीनों में यात्रा बंद थी, क्या आपने अपने घर वाली जगह से बाहर जाकर काम किया?</t>
+          <t>वह वजह क्या थी? जो वे कहें वही लिख लें।</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>${came_here_reason} = 8</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -4566,32 +4578,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>closure_work_detail</t>
+          <t>worked_away_in_closure</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Where did you go, and what work did you do there? Write what they say.</t>
+          <t>Last year, in the months when the Yatra was closed, did you work away from your home place?</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>कहाँ गए थे, और वहाँ क्या काम किया? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+          <t>पिछले साल, जिन महीनों में यात्रा बंद थी, क्या आपने अपने घर वाली जगह से बाहर जाकर काम किया?</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>${worked_away_in_closure} = 1</t>
-        </is>
-      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
@@ -4603,34 +4615,30 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>select_one month</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>left_here_month</t>
+          <t>closure_work_detail</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>In the past year, which month did you last leave here and go to your home place?</t>
+          <t>Where did you go, and what work did you do there? Write what they say.</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>पिछले साल आप यहाँ से आख़िरी बार किस महीने अपने घर गए थे?</t>
+          <t>कहाँ गए थे, और वहाँ क्या काम किया? जैसा वे बताएँ वैसा लिख लीजिए।</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>${resp_returns_at_closure} = 1</t>
+          <t>${worked_away_in_closure} = 1</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -4649,17 +4657,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>returned_here_month</t>
+          <t>left_here_month</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>And which month did you come back here?</t>
+          <t>In the past year, which month did you last leave here and go to your home place?</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>और किस महीने आप वापस यहाँ आए?</t>
+          <t>पिछले साल आप यहाँ से आख़िरी बार किस महीने अपने घर गए थे?</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -4685,22 +4693,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>select_one month</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>would_move_for_work</t>
+          <t>returned_here_month</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>If this work here ended, would you go away from your home place to look for work in the coming year?</t>
+          <t>And which month did you come back here?</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>अगर यहाँ का यह काम बंद हो जाए, तो क्या आप आने वाले साल में काम ढूँढने अपने घर से बाहर जाएँगे?</t>
+          <t>और किस महीने आप वापस यहाँ आए?</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -4710,7 +4718,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>${resp_returns_at_closure} = 1</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
@@ -4722,22 +4734,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>select_one referral</t>
+          <t>select_one yndk</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>migration_referral</t>
+          <t>would_move_for_work</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Who mainly helped you get this work, or arranged it for you?</t>
+          <t>If this work here ended, would you go away from your home place to look for work in the coming year?</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>यहाँ आने या यह काम पकड़ने में मुख्य रूप से किसने मदद की या रास्ता दिखाया: यहाँ पहले से रह रहा कोई घरवाला; कोई दोस्त या जान-पहचान वाला; कोई ठेकेदार या एजेंट; कोई नेता या समाज का बड़ा आदमी; कोई नहीं, आपने खुद ढूँढा; मालिक ने सीधे बुलाया; या कोई और?</t>
+          <t>अगर यहाँ का यह काम बंद हो जाए, तो क्या आप आने वाले साल में काम ढूँढने अपने घर से बाहर जाएँगे?</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -4759,32 +4771,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one referral</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>migration_referral_other</t>
+          <t>migration_referral</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Who was it? Write what they say.</t>
+          <t>Who mainly helped you get this work, or arranged it for you?</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>वे कौन थे? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+          <t>यहाँ आने या यह काम पकड़ने में मुख्य रूप से किसने मदद की या रास्ता दिखाया: यहाँ पहले से रह रहा कोई घरवाला; कोई दोस्त या जान-पहचान वाला; कोई ठेकेदार या एजेंट; कोई नेता या समाज का बड़ा आदमी; कोई नहीं, आपने खुद ढूँढा; मालिक ने सीधे बुलाया; या कोई और?</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>${migration_referral} = 7</t>
-        </is>
-      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
@@ -4796,16 +4808,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr"/>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>migration_referral_other</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Who was it? Write what they say.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>वे कौन थे? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>${migration_referral} = 7</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
@@ -4817,24 +4845,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>grp_E</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Module E: Household consumption</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Module E: Household consumption</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
@@ -4845,31 +4861,27 @@
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>intro_E</t>
+          <t>grp_E</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Now about what your household usually spends in a month. For each thing I will ask twice — once for a normal month during the Yatra season, and once for a normal month when the Yatra is closed — because spending is often quite different in the two. Rough figures are fine.</t>
+          <t>Module E: Household consumption</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>अब यह कि आपके घर का एक महीने में आमतौर पर कितना ख़र्च होता है। हर चीज़ के लिए मैं दो बार पूछूँगा — एक बार यात्रा के मौसम के आम महीने के लिए, और एक बार उस महीने के लिए जब यात्रा बंद रहती है — क्योंकि दोनों में ख़र्च अक्सर काफ़ी अलग होता है। अंदाज़े का हिसाब ही ठीक है।</t>
+          <t>Module E: Household consumption</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -4882,36 +4894,36 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>spend_differs_by_season</t>
+          <t>intro_E</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Leaving aside money you send home — is what your household spends in a normal month during the Yatra season different from what it spends when the Yatra is closed?</t>
+          <t>Now about what your household usually spends in a month. For each thing I will ask twice — once for a normal month during the Yatra season, and once for a normal month when the Yatra is closed — because spending is often quite different in the two. Rough figures are fine.</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>घर भेजे जाने वाले पैसे को छोड़कर — यात्रा के मौसम में आपके घर का महीने का ख़र्च, और जब यात्रा बंद रहती है तब का ख़र्च, क्या अलग-अलग होता है?</t>
+          <t>अब यह कि आपके घर का एक महीने में आमतौर पर कितना ख़र्च होता है। हर चीज़ के लिए मैं दो बार पूछूँगा — एक बार यात्रा के मौसम के आम महीने के लिए, और एक बार उस महीने के लिए जब यात्रा बंद रहती है — क्योंकि दोनों में ख़र्च अक्सर काफ़ी अलग होता है। अंदाज़े का हिसाब ही ठीक है।</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
@@ -4924,22 +4936,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>cons_staples_yatra_pm</t>
+          <t>spend_differs_by_season</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
+          <t>Leaving aside money you send home — is what your household spends in a normal month during the Yatra season different from what it spends when the Yatra is closed?</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>घर भेजे जाने वाले पैसे को छोड़कर — यात्रा के मौसम में आपके घर का महीने का ख़र्च, और जब यात्रा बंद रहती है तब का ख़र्च, क्या अलग-अलग होता है?</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -4966,17 +4978,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>cons_staples_offseason_pm</t>
+          <t>cons_staples_yatra_pm</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -4986,11 +4998,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
@@ -5007,17 +5015,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>cons_perishables_yatra_pm</t>
+          <t>cons_staples_offseason_pm</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -5027,7 +5035,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
@@ -5044,17 +5056,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>cons_perishables_offseason_pm</t>
+          <t>cons_perishables_yatra_pm</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -5064,11 +5076,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
@@ -5085,17 +5093,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>cons_food_own_yatra_pm</t>
+          <t>cons_perishables_offseason_pm</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>If you (and anyone staying with you here) had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month during the Yatra season? (Rs, 0 if you buy everything)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>अगर आप (और जो यहाँ आपके साथ रहते हैं) अपना खाना ख़ुद न उगाते, न पालते और न किसी से मिलता, तो यात्रा के मौसम के आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -5105,7 +5113,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
@@ -5122,17 +5134,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>cons_food_own_offseason_pm</t>
+          <t>cons_food_own_yatra_pm</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>If your household had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month when the Yatra is closed? (Rs, 0 if you buy everything)</t>
+          <t>If you (and anyone staying with you here) had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month during the Yatra season? (Rs, 0 if you buy everything)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>अगर आपका घर अपना खाना ख़ुद न उगाता, न पालता और न किसी से मिलता, तो जब यात्रा बंद रहती है उस आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
+          <t>अगर आप (और जो यहाँ आपके साथ रहते हैं) अपना खाना ख़ुद न उगाते, न पालते और न किसी से मिलता, तो यात्रा के मौसम के आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -5142,11 +5154,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
@@ -5163,17 +5171,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>cons_food_out_yatra_pm</t>
+          <t>cons_food_own_offseason_pm</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
+          <t>If your household had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month when the Yatra is closed? (Rs, 0 if you buy everything)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>अगर आपका घर अपना खाना ख़ुद न उगाता, न पालता और न किसी से मिलता, तो जब यात्रा बंद रहती है उस आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -5183,7 +5191,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
@@ -5200,17 +5212,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>cons_food_out_offseason_pm</t>
+          <t>cons_food_out_yatra_pm</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -5220,11 +5232,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
@@ -5241,17 +5249,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>cons_fuel_yatra_pm</t>
+          <t>cons_food_out_offseason_pm</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -5261,7 +5269,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
@@ -5278,17 +5290,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>cons_fuel_offseason_pm</t>
+          <t>cons_fuel_yatra_pm</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -5298,11 +5310,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
@@ -5319,17 +5327,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>cons_routine_misc_yatra_pm</t>
+          <t>cons_fuel_offseason_pm</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -5339,7 +5347,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
@@ -5356,17 +5368,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>cons_routine_misc_offseason_pm</t>
+          <t>cons_routine_misc_yatra_pm</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -5376,11 +5388,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
@@ -5397,17 +5405,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>cons_transport_comm_yatra_pm</t>
+          <t>cons_routine_misc_offseason_pm</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -5417,7 +5425,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
@@ -5434,17 +5446,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>cons_transport_comm_offseason_pm</t>
+          <t>cons_transport_comm_yatra_pm</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -5454,11 +5466,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
@@ -5475,17 +5483,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>cons_rent_yatra_pm</t>
+          <t>cons_transport_comm_offseason_pm</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -5495,7 +5503,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
@@ -5512,17 +5524,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>cons_rent_offseason_pm</t>
+          <t>cons_rent_yatra_pm</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -5532,11 +5544,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
@@ -5553,17 +5561,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>cons_med_nonhosp_yatra_pm</t>
+          <t>cons_rent_offseason_pm</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -5573,7 +5581,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
@@ -5590,17 +5602,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>cons_med_nonhosp_offseason_pm</t>
+          <t>cons_med_nonhosp_yatra_pm</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -5610,11 +5622,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
@@ -5631,17 +5639,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>cons_packaged_food_yatra_pm</t>
+          <t>cons_med_nonhosp_offseason_pm</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -5651,7 +5659,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
@@ -5668,17 +5680,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>cons_packaged_food_offseason_pm</t>
+          <t>cons_packaged_food_yatra_pm</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -5688,11 +5700,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
@@ -5709,17 +5717,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>cons_pan_tobacco_yatra_pm</t>
+          <t>cons_packaged_food_offseason_pm</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -5729,7 +5737,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
@@ -5746,17 +5758,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>cons_pan_tobacco_offseason_pm</t>
+          <t>cons_pan_tobacco_yatra_pm</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -5766,11 +5778,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
@@ -5787,17 +5795,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>cons_clothing_12m</t>
+          <t>cons_pan_tobacco_offseason_pm</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much did your household spend on clothes and footwear? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में आपके घर ने कपड़ों और जूते-चप्पल पर कितना ख़र्च किया? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -5807,7 +5815,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
@@ -5824,17 +5836,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>cons_education_12m</t>
+          <t>cons_clothing_12m</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much on education: fees, books, uniforms, tuition? (Rs)</t>
+          <t>In the last 12 months, how much did your household spend on clothes and footwear? (Rs)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में पढ़ाई पर कितना ख़र्च हुआ: फ़ीस, किताबें, ड्रेस, ट्यूशन? (रुपये)</t>
+          <t>पिछले 12 महीनों में आपके घर ने कपड़ों और जूते-चप्पल पर कितना ख़र्च किया? (रुपये)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -5861,17 +5873,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>cons_medical_hosp_12m</t>
+          <t>cons_education_12m</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much did your household pay for any hospital admission or stay? (Rs, 0 if none)</t>
+          <t>In the last 12 months, how much on education: fees, books, uniforms, tuition? (Rs)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में अस्पताल में भर्ती होने पर आपके घर का कितना ख़र्च हुआ? (रुपये, न हुआ हो तो 0)</t>
+          <t>पिछले 12 महीनों में पढ़ाई पर कितना ख़र्च हुआ: फ़ीस, किताबें, ड्रेस, ट्यूशन? (रुपये)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
@@ -5898,17 +5910,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>cons_durables_12m</t>
+          <t>cons_medical_hosp_12m</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much on durable goods: furniture, utensils, cooking appliances, phone, jewellery or ornaments, bicycle or vehicle parts? (Rs)</t>
+          <t>In the last 12 months, how much did your household pay for any hospital admission or stay? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में सामान पर कितना ख़र्च हुआ: फ़र्नीचर, बर्तन, चूल्हा-मशीन, फ़ोन, गहने, साइकिल या गाड़ी के पुर्ज़े? (रुपये)</t>
+          <t>पिछले 12 महीनों में अस्पताल में भर्ती होने पर आपके घर का कितना ख़र्च हुआ? (रुपये, न हुआ हो तो 0)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -5930,15 +5942,31 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr"/>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>cons_durables_12m</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>In the last 12 months, how much on durable goods: furniture, utensils, cooking appliances, phone, jewellery or ornaments, bicycle or vehicle parts? (Rs)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>पिछले 12 महीनों में सामान पर कितना ख़र्च हुआ: फ़र्नीचर, बर्तन, चूल्हा-मशीन, फ़ोन, गहने, साइकिल या गाड़ी के पुर्ज़े? (रुपये)</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
@@ -5951,24 +5979,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>grp_F</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Module F: Housing, amenities and assets</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Module F: Housing, amenities and assets</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
@@ -5979,31 +5995,27 @@
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>intro_F</t>
+          <t>grp_F</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Now some questions about your house and the things your household has.</t>
+          <t>Module F: Housing, amenities and assets</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>अब आपके घर और घर में मौजूद सामान के बारे में कुछ सवाल।</t>
+          <t>Module F: Housing, amenities and assets</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -6016,36 +6028,36 @@
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>select_one floor</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>floor_material</t>
+          <t>intro_F</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>What is the main material of the floor at your usual home?</t>
+          <t>Now some questions about your house and the things your household has.</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>आपके असली घर में फ़र्श मुख्य रूप से किस चीज़ का है?</t>
+          <t>अब आपके घर और घर में मौजूद सामान के बारे में कुछ सवाल।</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
@@ -6058,22 +6070,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>select_one roof</t>
+          <t>select_one floor</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>roof_material</t>
+          <t>floor_material</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>What is the main material of the roof at your usual home?</t>
+          <t>What is the main material of the floor at your usual home?</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>आपके असली घर की छत मुख्य रूप से किस चीज़ की है?</t>
+          <t>आपके असली घर में फ़र्श मुख्य रूप से किस चीज़ का है?</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
@@ -6095,22 +6107,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>select_one wall</t>
+          <t>select_one roof</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>wall_material</t>
+          <t>roof_material</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>What are the walls of your usual home mainly made of?</t>
+          <t>What is the main material of the roof at your usual home?</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>आपके असली घर की दीवारें मुख्य रूप से किस चीज़ की बनी हैं?</t>
+          <t>आपके असली घर की छत मुख्य रूप से किस चीज़ की है?</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -6132,22 +6144,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>select_one accomhere</t>
+          <t>select_one wall</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>accom_type_here</t>
+          <t>wall_material</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>While you are here for the season, where do you sleep?</t>
+          <t>What are the walls of your usual home mainly made of?</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>सीज़न में यहाँ रहते हुए आप कहाँ सोते हैं?</t>
+          <t>आपके असली घर की दीवारें मुख्य रूप से किस चीज़ की बनी हैं?</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -6169,22 +6181,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one accomhere</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>accom_type_here</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Does your usual home have an electricity connection?</t>
+          <t>While you are here for the season, where do you sleep?</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>क्या आपके असली घर में बिजली का कनेक्शन है?</t>
+          <t>सीज़न में यहाँ रहते हुए आप कहाँ सोते हैं?</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -6206,22 +6218,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>select_one toilet</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>toilet_type</t>
+          <t>electricity</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>What kind of toilet does your household use at your usual home?</t>
+          <t>Does your usual home have an electricity connection?</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>आपका घर अपने असली घर में किस तरह का शौचालय इस्तेमाल करता है?</t>
+          <t>क्या आपके असली घर में बिजली का कनेक्शन है?</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -6243,22 +6255,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>select_one water</t>
+          <t>select_one toilet</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>drinking_water</t>
+          <t>toilet_type</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>What is your main source of drinking water at your usual home?</t>
+          <t>What kind of toilet does your household use at your usual home?</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>आपके असली घर में पीने का पानी मुख्य रूप से कहाँ से आता है?</t>
+          <t>आपका घर अपने असली घर में किस तरह का शौचालय इस्तेमाल करता है?</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -6280,22 +6292,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one water</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>water_on_premises</t>
+          <t>drinking_water</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Is the drinking water available at the house itself?</t>
+          <t>What is your main source of drinking water at your usual home?</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>क्या पीने का पानी घर पर ही मिल जाता है?</t>
+          <t>आपके असली घर में पीने का पानी मुख्य रूप से कहाँ से आता है?</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -6317,22 +6329,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>water_fetch_minutes</t>
+          <t>water_on_premises</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>How long does it take to go there, get the water and come back? (minutes, round trip)</t>
+          <t>Is the drinking water available at the house itself?</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>वहाँ जाने, पानी भरने और लौटने में कुल कितना समय लगता है? (मिनट)</t>
+          <t>क्या पीने का पानी घर पर ही मिल जाता है?</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -6342,26 +6354,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>${water_on_premises} = 0</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 300</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>Minutes must be between 0 and 300.</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>मिनट 0 से 300 के बीच होने चाहिए।</t>
-        </is>
-      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
@@ -6370,22 +6366,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>select_one fuel</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>cooking_fuel</t>
+          <t>water_fetch_minutes</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>What does your household mainly use to cook at your usual home?</t>
+          <t>How long does it take to go there, get the water and come back? (minutes, round trip)</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>आपके असली घर में खाना मुख्य रूप से किस चीज़ पर बनता है?</t>
+          <t>वहाँ जाने, पानी भरने और लौटने में कुल कितना समय लगता है? (मिनट)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -6395,10 +6391,26 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>${water_on_premises} = 0</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 300</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Minutes must be between 0 and 300.</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>मिनट 0 से 300 के बीच होने चाहिए।</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
@@ -6407,22 +6419,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one fuel</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>owns_tv</t>
+          <t>cooking_fuel</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Does your household own: a television?</t>
+          <t>What does your household mainly use to cook at your usual home?</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>क्या आपके घर में टीवी है?</t>
+          <t>आपके असली घर में खाना मुख्य रूप से किस चीज़ पर बनता है?</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -6449,17 +6461,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>owns_radio</t>
+          <t>owns_tv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>... a radio?</t>
+          <t>Does your household own: a television?</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>...रेडियो?</t>
+          <t>क्या आपके घर में टीवी है?</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -6486,17 +6498,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>owns_bicycle</t>
+          <t>owns_radio</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>... a bicycle?</t>
+          <t>... a radio?</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>...साइकिल?</t>
+          <t>...रेडियो?</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -6523,17 +6535,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>owns_motorcycle</t>
+          <t>owns_bicycle</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>... a motorcycle or scooter?</t>
+          <t>... a bicycle?</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>...मोटरसाइकिल या स्कूटर?</t>
+          <t>...साइकिल?</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -6560,17 +6572,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>owns_car</t>
+          <t>owns_motorcycle</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>... a car, jeep or truck?</t>
+          <t>... a motorcycle or scooter?</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>...कार, जीप या ट्रक?</t>
+          <t>...मोटरसाइकिल या स्कूटर?</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -6597,17 +6609,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>owns_phone</t>
+          <t>owns_car</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>... a telephone of any kind, mobile or landline?</t>
+          <t>... a car, jeep or truck?</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>...कोई फ़ोन, मोबाइल या लैंडलाइन?</t>
+          <t>...कार, जीप या ट्रक?</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -6634,17 +6646,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>owns_computer</t>
+          <t>owns_phone</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>... a computer or laptop?</t>
+          <t>... a telephone of any kind, mobile or landline?</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>...कंप्यूटर या लैपटॉप?</t>
+          <t>...कोई फ़ोन, मोबाइल या लैंडलाइन?</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -6671,17 +6683,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>owns_animal_cart</t>
+          <t>owns_computer</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>... a cart pulled by an animal?</t>
+          <t>... a computer or laptop?</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>...जानवर से खींची जाने वाली गाड़ी?</t>
+          <t>...कंप्यूटर या लैपटॉप?</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -6708,17 +6720,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>owns_fridge</t>
+          <t>owns_animal_cart</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>... a refrigerator?</t>
+          <t>... a cart pulled by an animal?</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>...फ़्रिज?</t>
+          <t>...जानवर से खींची जाने वाली गाड़ी?</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -6740,22 +6752,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>select_one landunit</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>land_unit</t>
+          <t>owns_fridge</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>In what unit do you count your land — nali, bigha, acres or hectares?</t>
+          <t>... a refrigerator?</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>आप अपनी ज़मीन किस हिसाब से गिनते हैं — नाली, बीघा, एकड़ या हेक्टेयर?</t>
+          <t>...फ़्रिज?</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -6777,22 +6789,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>select_one landunit</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>land_cultivable_acres</t>
+          <t>land_unit</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>And how much CULTIVABLE land is that? Do not count the land the house stands on.</t>
+          <t>In what unit do you count your land — nali, bigha, acres or hectares?</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>आपके घर के पास कितनी जोतने लायक़ ज़मीन है, अपनी या जोतने की, एकड़ में? जिस ज़मीन पर घर बना है उसे मत गिनिए। (न हो तो 0)</t>
+          <t>आप अपनी ज़मीन किस हिसाब से गिनते हैं — नाली, बीघा, एकड़ या हेक्टेयर?</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -6802,26 +6814,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>${land_unit} != 5</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>. &gt;= 0</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>Land cannot be negative.</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>Land cannot be negative.</t>
-        </is>
-      </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
@@ -6830,22 +6826,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>owns_cow_buffalo</t>
+          <t>land_cultivable_acres</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Does your household own any cows or buffaloes?</t>
+          <t>And how much CULTIVABLE land is that? Do not count the land the house stands on.</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>क्या आपके घर में गाय या भैंस है?</t>
+          <t>आपके घर के पास कितनी जोतने लायक़ ज़मीन है, अपनी या जोतने की, एकड़ में? जिस ज़मीन पर घर बना है उसे मत गिनिए। (न हो तो 0)</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -6855,10 +6851,26 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>${land_unit} != 5</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Land cannot be negative.</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Land cannot be negative.</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr"/>
@@ -6872,17 +6884,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>owns_goat_sheep</t>
+          <t>owns_cow_buffalo</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Does your household own any goats or sheep?</t>
+          <t>Does your household own any cows or buffaloes?</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>क्या आपके घर में बकरी या भेड़ है?</t>
+          <t>क्या आपके घर में गाय या भैंस है?</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -6909,17 +6921,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>owns_pony_mule</t>
+          <t>owns_goat_sheep</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Does your household own any ponies or mules?</t>
+          <t>Does your household own any goats or sheep?</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>क्या आपके घर में घोड़ा या खच्चर है?</t>
+          <t>क्या आपके घर में बकरी या भेड़ है?</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -6946,17 +6958,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>owns_shop_stall</t>
+          <t>owns_pony_mule</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Does your household own a shop or stall that you use to earn?</t>
+          <t>Does your household own any ponies or mules?</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>क्या आपके घर की अपनी दुकान या खोखा है जिससे आप कमाते हैं?</t>
+          <t>क्या आपके घर में घोड़ा या खच्चर है?</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -6983,17 +6995,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>owns_work_vehicle</t>
+          <t>owns_shop_stall</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Does your household own a vehicle you use to earn (for example a jeep, truck or taxi)?</t>
+          <t>Does your household own a shop or stall that you use to earn?</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>क्या आपके घर की अपनी गाड़ी है जिससे आप कमाते हैं (जैसे जीप, ट्रक या टैक्सी)?</t>
+          <t>क्या आपके घर की अपनी दुकान या खोखा है जिससे आप कमाते हैं?</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -7020,17 +7032,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>owns_work_equipment</t>
+          <t>owns_work_vehicle</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Does your household own equipment or tools that you use to earn?</t>
+          <t>Does your household own a vehicle you use to earn (for example a jeep, truck or taxi)?</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>क्या आपके घर के पास काम के औज़ार या मशीन है जिससे आप कमाते हैं?</t>
+          <t>क्या आपके घर की अपनी गाड़ी है जिससे आप कमाते हैं (जैसे जीप, ट्रक या टैक्सी)?</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -7052,32 +7064,32 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>work_equipment_detail</t>
+          <t>owns_work_equipment</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>What are they? Write what they say. Leave blank if they cannot say.</t>
+          <t>Does your household own equipment or tools that you use to earn?</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>वे क्या हैं? जैसा वे बताएँ वैसा लिख लीजिए। न बता पाएँ तो खाली छोड़ दीजिए।</t>
+          <t>क्या आपके घर के पास काम के औज़ार या मशीन है जिससे आप कमाते हैं?</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>${owns_work_equipment} = 1</t>
-        </is>
-      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
@@ -7089,16 +7101,32 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr"/>
-      <c r="C169" t="inlineStr"/>
-      <c r="D169" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>work_equipment_detail</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>What are they? Write what they say. Leave blank if they cannot say.</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>वे क्या हैं? जैसा वे बताएँ वैसा लिख लीजिए। न बता पाएँ तो खाली छोड़ दीजिए।</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>${owns_work_equipment} = 1</t>
+        </is>
+      </c>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
@@ -7110,24 +7138,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>grp_G</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Module G: Finance, insurance and schemes</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>Module G: Finance, insurance and schemes</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
@@ -7138,31 +7154,27 @@
       <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>intro_G</t>
+          <t>grp_G</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Now about savings, loans, insurance and government schemes.</t>
+          <t>Module G: Finance, insurance and schemes</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>अब बचत, क़र्ज़, बीमा और सरकारी योजनाओं के बारे में।</t>
+          <t>Module G: Finance, insurance and schemes</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -7175,36 +7187,36 @@
       <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr"/>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>has_bank_account</t>
+          <t>intro_G</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Does anyone in your household have a bank account or a post office account?</t>
+          <t>Now about savings, loans, insurance and government schemes.</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>क्या आपके घर में किसी का बैंक खाता या डाकघर का खाता है?</t>
+          <t>अब बचत, क़र्ज़, बीमा और सरकारी योजनाओं के बारे में।</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
@@ -7222,17 +7234,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>took_loan_12m</t>
+          <t>has_bank_account</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>In the last 12 months, did you or anyone in your household borrow money?</t>
+          <t>Does anyone in your household have a bank account or a post office account?</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपने या आपके घर के किसी सदस्य ने पैसा उधार लिया?</t>
+          <t>क्या आपके घर में किसी का बैंक खाता या डाकघर का खाता है?</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -7254,22 +7266,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>select_one credit</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>credit_source</t>
+          <t>took_loan_12m</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Who was the main lender?</t>
+          <t>In the last 12 months, did you or anyone in your household borrow money?</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>मुख्य रूप से किससे उधार लिया?</t>
+          <t>पिछले 12 महीनों में क्या आपने या आपके घर के किसी सदस्य ने पैसा उधार लिया?</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -7279,11 +7291,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>${took_loan_12m} = 1</t>
-        </is>
-      </c>
+      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr"/>
@@ -7295,22 +7303,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>select_one loanpurpose</t>
+          <t>select_one credit</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>loan_purpose</t>
+          <t>credit_source</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>What did you take it for?</t>
+          <t>Who was the main lender?</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>वह क़र्ज़ आपने किस काम के लिए लिया था?</t>
+          <t>मुख्य रूप से किससे उधार लिया?</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -7336,22 +7344,22 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one loanpurpose</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>loan_amount_borrowed</t>
+          <t>loan_purpose</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>How much did you borrow in total? (Rs)</t>
+          <t>What did you take it for?</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>आपने कुल कितना क़र्ज़ लिया था? (रुपये)</t>
+          <t>वह क़र्ज़ आपने किस काम के लिए लिया था?</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -7366,21 +7374,9 @@
           <t>${took_loan_12m} = 1</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>. &gt;= 0</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>An amount cannot be negative.</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>An amount cannot be negative.</t>
-        </is>
-      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
@@ -7394,17 +7390,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>loan_amount</t>
+          <t>loan_amount_borrowed</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>How much of that loan is still left to repay? (Rs)</t>
+          <t>How much did you borrow in total? (Rs)</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>उस क़र्ज़ में से अब भी कितना चुकाना बाक़ी है? (रुपये)</t>
+          <t>आपने कुल कितना क़र्ज़ लिया था? (रुपये)</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -7442,22 +7438,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>pays_interest</t>
+          <t>loan_amount</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Do you pay interest on it?</t>
+          <t>How much of that loan is still left to repay? (Rs)</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>क्या आप उस पर ब्याज देते हैं?</t>
+          <t>उस क़र्ज़ में से अब भी कितना चुकाना बाक़ी है? (रुपये)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -7472,9 +7468,21 @@
           <t>${took_loan_12m} = 1</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>An amount cannot be negative.</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>An amount cannot be negative.</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
@@ -7483,30 +7491,34 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>loan_interest_per100_pm</t>
+          <t>pays_interest</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>On every 100 rupees you borrowed, about how much interest do you pay in a month? (Rs; 0 if none, leave blank if not known)</t>
+          <t>Do you pay interest on it?</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>आपने जो 100 रुपये उधार लिए, उन पर महीने का कितना ब्याज देते हैं? (रुपये; दर पता न हो तो खाली छोड़ दें)</t>
+          <t>क्या आप उस पर ब्याज देते हैं?</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>${pays_interest} = 1</t>
+          <t>${took_loan_12m} = 1</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -7520,34 +7532,30 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>loan_against_asset</t>
+          <t>loan_interest_per100_pm</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Did you have to give something as security for it — an animal, a vehicle, jewellery, land or your business?</t>
+          <t>On every 100 rupees you borrowed, about how much interest do you pay in a month? (Rs; 0 if none, leave blank if not known)</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>क्या उसके बदले कुछ गिरवी रखना पड़ा — जानवर, गाड़ी, गहने, ज़मीन या आपका धंधा?</t>
+          <t>आपने जो 100 रुपये उधार लिए, उन पर महीने का कितना ब्याज देते हैं? (रुपये; दर पता न हो तो खाली छोड़ दें)</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr">
         <is>
-          <t>${took_loan_12m} = 1</t>
+          <t>${pays_interest} = 1</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -7561,22 +7569,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>select_one collat</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>loan_collateral</t>
+          <t>loan_against_asset</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>What did you have to give as security?</t>
+          <t>Did you have to give something as security for it — an animal, a vehicle, jewellery, land or your business?</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>आपको क्या गिरवी रखना पड़ा?</t>
+          <t>क्या उसके बदले कुछ गिरवी रखना पड़ा — जानवर, गाड़ी, गहने, ज़मीन या आपका धंधा?</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -7588,7 +7596,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>${loan_against_asset} = 1</t>
+          <t>${took_loan_12m} = 1</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -7602,22 +7610,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one collat</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>n_health_insured</t>
+          <t>loan_collateral</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>How many people in your household are covered by any health insurance or health scheme, including government ones? (0 if none)</t>
+          <t>What did you have to give as security?</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोगों का कोई स्वास्थ्य बीमा या स्वास्थ्य योजना है, सरकारी भी मिलाकर? (कोई नहीं तो 0)</t>
+          <t>आपको क्या गिरवी रखना पड़ा?</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -7627,22 +7635,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>Cannot be more than the number of people in the household.</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
-        </is>
-      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>${loan_against_asset} = 1</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
@@ -7656,17 +7656,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>n_life_insured</t>
+          <t>n_health_insured</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>How many people in your household have life insurance? (0 if none)</t>
+          <t>How many people in your household are covered by any health insurance or health scheme, including government ones? (0 if none)</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोगों का जीवन बीमा है? (कोई नहीं तो 0)</t>
+          <t>आपके घर में कितने लोगों का कोई स्वास्थ्य बीमा या स्वास्थ्य योजना है, सरकारी भी मिलाकर? (कोई नहीं तो 0)</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -7700,22 +7700,22 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>has_crop_insurance</t>
+          <t>n_life_insured</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Is your crop insured?</t>
+          <t>How many people in your household have life insurance? (0 if none)</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>क्या आपकी फ़सल का बीमा है?</t>
+          <t>आपके घर में कितने लोगों का जीवन बीमा है? (कोई नहीं तो 0)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -7725,14 +7725,22 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>${land_cultivable_acres} &gt; 0</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Cannot be more than the number of people in the household.</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
@@ -7746,35 +7754,31 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>govt_any_benefit</t>
+          <t>has_crop_insurance</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>In the last 12 months, did your household get anything from any government scheme? Read the list out before you take an answer.</t>
+          <t>Is your crop insured?</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके घर को किसी सरकारी योजना से कुछ मिला? जवाब लेने से पहले सूची पढ़कर सुनाइए।</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>READ THE LIST OUT; do not ask the bare question, because people fail to recall the category and say no. Ration card or PDS grain; MGNREGA work or job card; old-age, widow or disability pension; PM-KISAN; Ujjwala LPG; PM-SYM or Atal Pension; Ayushman Bharat or a health card; a housing scheme (PMAY or state). Any one of them is a Yes.</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>सूची पढ़कर सुनाइए; सीधा सवाल न पूछिए, वरना लोग याद न कर पाकर नहीं कह देते हैं। राशन कार्ड या सरकारी राशन; मनरेगा का काम या जॉब कार्ड; बुढ़ापा, विधवा या दिव्यांग पेंशन; पीएम-किसान; उज्ज्वला गैस; पीएम-एसवाईएम या अटल पेंशन; आयुष्मान या स्वास्थ्य कार्ड; आवास योजना (पीएमएवाई या राज्य की)। इनमें से कोई भी एक = हाँ।</t>
-        </is>
-      </c>
+          <t>क्या आपकी फ़सल का बीमा है?</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>${land_cultivable_acres} &gt; 0</t>
+        </is>
+      </c>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
@@ -7786,32 +7790,32 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>govt_schemes_detail</t>
+          <t>govt_any_benefit</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Which ones? Write down every scheme they name, in their own words.</t>
+          <t>In the last 12 months, did your household get anything from any government scheme? Read the list out before you take an answer.</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>कौन-कौन सी? वे जितनी योजनाएँ बताएँ, सब उन्हीं के शब्दों में लिख लीजिए।</t>
+          <t>पिछले 12 महीनों में क्या आपके घर को किसी सरकारी योजना से कुछ मिला? जवाब लेने से पहले सूची पढ़कर सुनाइए।</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Write the scheme names in their own words, all of them, including any not on the list you just read. Office-coded afterwards, so do not try to fit the answer to a category.</t>
+          <t>READ THE LIST OUT; do not ask the bare question, because people fail to recall the category and say no. Ration card or PDS grain; MGNREGA work or job card; old-age, widow or disability pension; PM-KISAN; Ujjwala LPG; PM-SYM or Atal Pension; Ayushman Bharat or a health card; a housing scheme (PMAY or state). Any one of them is a Yes.</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>जितनी योजनाएँ वे बताएँ, सब उन्हीं के शब्दों में लिखिए — सूची में न होने वाली भी। कोडिंग बाद में दफ़्तर में होगी, इसलिए जवाब को किसी खाने में बिठाने की कोशिश न करें।</t>
+          <t>सूची पढ़कर सुनाइए; सीधा सवाल न पूछिए, वरना लोग याद न कर पाकर नहीं कह देते हैं। राशन कार्ड या सरकारी राशन; मनरेगा का काम या जॉब कार्ड; बुढ़ापा, विधवा या दिव्यांग पेंशन; पीएम-किसान; उज्ज्वला गैस; पीएम-एसवाईएम या अटल पेंशन; आयुष्मान या स्वास्थ्य कार्ड; आवास योजना (पीएमएवाई या राज्य की)। इनमें से कोई भी एक = हाँ।</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -7819,11 +7823,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>${govt_any_benefit} = 1</t>
-        </is>
-      </c>
+      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
@@ -7835,32 +7835,44 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>select_one portable</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ration_portable_here</t>
+          <t>govt_schemes_detail</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Can you draw your ration here, or only at your home place?</t>
+          <t>Which ones? Write down every scheme they name, in their own words.</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>क्या आप अपना राशन यहाँ ले सकते हैं, या सिर्फ़ अपने घर वाली जगह पर?</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
+          <t>कौन-कौन सी? वे जितनी योजनाएँ बताएँ, सब उन्हीं के शब्दों में लिख लीजिए।</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Write the scheme names in their own words, all of them, including any not on the list you just read. Office-coded afterwards, so do not try to fit the answer to a category.</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>जितनी योजनाएँ वे बताएँ, सब उन्हीं के शब्दों में लिखिए — सूची में न होने वाली भी। कोडिंग बाद में दफ़्तर में होगी, इसलिए जवाब को किसी खाने में बिठाने की कोशिश न करें।</t>
+        </is>
+      </c>
       <c r="G187" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>${govt_any_benefit} = 1</t>
+        </is>
+      </c>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
@@ -7872,22 +7884,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one portable</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>smartphone_owned</t>
+          <t>ration_portable_here</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Do you own a smartphone?</t>
+          <t>Can you draw your ration here, or only at your home place?</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>क्या आपके पास स्मार्टफ़ोन है?</t>
+          <t>क्या आप अपना राशन यहाँ ले सकते हैं, या सिर्फ़ अपने घर वाली जगह पर?</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -7914,17 +7926,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>uses_digital_payment</t>
+          <t>smartphone_owned</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Do you ever use UPI or another way of paying by phone?</t>
+          <t>Do you own a smartphone?</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>क्या आप कभी UPI या फ़ोन से पैसे का लेन-देन करते हैं?</t>
+          <t>क्या आपके पास स्मार्टफ़ोन है?</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
@@ -7946,22 +7958,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>n_can_transact_online</t>
+          <t>uses_digital_payment</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>How many people in your household can make a payment by phone themselves, without help? (0 if none)</t>
+          <t>Do you ever use UPI or another way of paying by phone?</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोग बिना किसी की मदद के फ़ोन से पैसे भेज सकते हैं? (कोई नहीं तो 0)</t>
+          <t>क्या आप कभी UPI या फ़ोन से पैसे का लेन-देन करते हैं?</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -7972,21 +7984,9 @@
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>Cannot be more than the number of people in the household.</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
-        </is>
-      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
@@ -7995,19 +7995,47 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr"/>
-      <c r="C191" t="inlineStr"/>
-      <c r="D191" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>n_can_transact_online</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>How many people in your household can make a payment by phone themselves, without help? (0 if none)</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>आपके घर में कितने लोग बिना किसी की मदद के फ़ोन से पैसे भेज सकते हैं? (कोई नहीं तो 0)</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Cannot be more than the number of people in the household.</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
@@ -8016,24 +8044,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>grp_H</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Module H: Health</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>Module H: Health</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr"/>
@@ -8044,31 +8060,27 @@
       <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>intro_H</t>
+          <t>grp_H</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Now a few questions about health in your household. You may leave out any of these.</t>
+          <t>Module H: Health</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>अब आपके घर में सेहत के बारे में कुछ सवाल। इनमें से कोई भी सवाल आप छोड़ सकते हैं।</t>
+          <t>Module H: Health</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -8081,36 +8093,36 @@
       <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr"/>
       <c r="N193" t="inlineStr"/>
-      <c r="O193" t="inlineStr"/>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>morbidity_15d</t>
+          <t>intro_H</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>In the last 15 days, was anyone in your household ill?</t>
+          <t>Now a few questions about health in your household. You may leave out any of these.</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>पिछले 15 दिनों में क्या आपके घर में कोई बीमार पड़ा?</t>
+          <t>अब आपके घर में सेहत के बारे में कुछ सवाल। इनमें से कोई भी सवाल आप छोड़ सकते हैं।</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
@@ -8123,22 +8135,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>select_one coping</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>morbidity_coping_15d</t>
+          <t>morbidity_15d</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>How did the household mainly cope with the cost of this: used savings; borrowed money; sold or pawned assets; cut other consumption; got help from relatives or community; or something else?</t>
+          <t>In the last 15 days, was anyone in your household ill?</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>इसका ख़र्च आपके घर ने मुख्य रूप से कैसे उठाया: जमा पैसे से; उधार लेकर; कुछ बेचकर या गिरवी रखकर; बाकी ख़र्च घटाकर; रिश्तेदारों या गाँव वालों की मदद से; या किसी और तरह?</t>
+          <t>पिछले 15 दिनों में क्या आपके घर में कोई बीमार पड़ा?</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -8148,11 +8160,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>${morbidity_15d} = 1</t>
-        </is>
-      </c>
+      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
@@ -8164,22 +8172,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one coping</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>morbidity_cost_15d</t>
+          <t>morbidity_coping_15d</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>About how much did the household spend on this in the last 15 days (medicine, doctor or clinic fees, travel for care)? (Rs)</t>
+          <t>How did the household mainly cope with the cost of this: used savings; borrowed money; sold or pawned assets; cut other consumption; got help from relatives or community; or something else?</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>पिछले 15 दिनों में इस पर घर का लगभग कितना ख़र्च हुआ (दवाई, डॉक्टर या क्लीनिक की फ़ीस, आने-जाने का ख़र्च)? (रुपये)</t>
+          <t>इसका ख़र्च आपके घर ने मुख्य रूप से कैसे उठाया: जमा पैसे से; उधार लेकर; कुछ बेचकर या गिरवी रखकर; बाकी ख़र्च घटाकर; रिश्तेदारों या गाँव वालों की मदद से; या किसी और तरह?</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -8205,22 +8213,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>select_one wgdiff</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>func_limitation</t>
+          <t>morbidity_cost_15d</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Do you have difficulty walking or climbing steps?</t>
+          <t>About how much did the household spend on this in the last 15 days (medicine, doctor or clinic fees, travel for care)? (Rs)</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>क्या आपको चलने या सीढ़ियाँ चढ़ने में दिक़्क़त होती है?</t>
+          <t>पिछले 15 दिनों में इस पर घर का लगभग कितना ख़र्च हुआ (दवाई, डॉक्टर या क्लीनिक की फ़ीस, आने-जाने का ख़र्च)? (रुपये)</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -8230,7 +8238,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr"/>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>${morbidity_15d} = 1</t>
+        </is>
+      </c>
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr"/>
@@ -8242,22 +8254,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one wgdiff</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>hospitalization_365d</t>
+          <t>func_limitation</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>In the last 12 months, was anyone in your household admitted to hospital overnight?</t>
+          <t>Do you have difficulty walking or climbing steps?</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके घर का कोई रात भर के लिए अस्पताल में भर्ती हुआ?</t>
+          <t>क्या आपको चलने या सीढ़ियाँ चढ़ने में दिक़्क़त होती है?</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -8284,17 +8296,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>health_access_barrier_3m</t>
+          <t>hospitalization_365d</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>In the last 3 months, was there a time when someone in your household needed medical care but could not get it?</t>
+          <t>In the last 12 months, was anyone in your household admitted to hospital overnight?</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>पिछले 3 महीनों में क्या कभी ऐसा हुआ कि आपके घर में किसी को इलाज की ज़रूरत थी पर मिल नहीं पाया?</t>
+          <t>पिछले 12 महीनों में क्या आपके घर का कोई रात भर के लिए अस्पताल में भर्ती हुआ?</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -8321,17 +8333,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>child_death_5y</t>
+          <t>health_access_barrier_3m</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>In the last five years, has any child or young person under 18 in your household died?</t>
+          <t>In the last 3 months, was there a time when someone in your household needed medical care but could not get it?</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>पिछले पाँच साल में क्या आपके घर के 18 साल से छोटे किसी बच्चे या किशोर की मृत्यु हुई?</t>
+          <t>पिछले 3 महीनों में क्या कभी ऐसा हुआ कि आपके घर में किसी को इलाज की ज़रूरत थी पर मिल नहीं पाया?</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
@@ -8358,17 +8370,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>birth_last_5y</t>
+          <t>child_death_5y</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>In the last five years, did any woman in your household give birth?</t>
+          <t>In the last five years, has any child or young person under 18 in your household died?</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>पिछले पाँच साल में क्या आपके घर की किसी महिला ने बच्चे को जन्म दिया?</t>
+          <t>पिछले पाँच साल में क्या आपके घर के 18 साल से छोटे किसी बच्चे या किशोर की मृत्यु हुई?</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
@@ -8395,39 +8407,27 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>anc_4_visits</t>
+          <t>birth_last_5y</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>For the most recent birth, did she have at least four check-ups before the delivery?</t>
+          <t>In the last five years, did any woman in your household give birth?</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>सबसे हाल के जन्म के लिए, क्या डिलीवरी से पहले उनकी कम से कम चार बार जाँच हुई थी?</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>Ask the mother herself if she is there. If not, probe: did she go for check-ups before the birth, and about how many times? Four or more is Yes; two or three is No. Do not accept a shrug — ask how many times she went.</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>अगर माँ वहीं हैं तो उनसे ही पूछिए। नहीं तो कुरेदिए: डिलीवरी से पहले वे जाँच कराने गई थीं, और लगभग कितनी बार? चार या उससे ज़्यादा = हाँ; दो-तीन = नहीं। 'पता नहीं' पर न रुकिए — कितनी बार गईं, यह पूछिए।</t>
-        </is>
-      </c>
+          <t>पिछले पाँच साल में क्या आपके घर की किसी महिला ने बच्चे को जन्म दिया?</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>${birth_last_5y} = 1</t>
-        </is>
-      </c>
+      <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
@@ -8439,32 +8439,32 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>select_one birthattend</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>skilled_birth_attendant</t>
+          <t>anc_4_visits</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Who conducted that delivery — a doctor, a nurse or ANM, an ASHA or Anganwadi worker, a dai, or nobody trained?</t>
+          <t>For the most recent birth, did she have at least four check-ups before the delivery?</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>वह डिलीवरी किसने कराई — डॉक्टर, नर्स या एएनएम, आशा या आँगनवाड़ी कार्यकर्ता, दाई, या कोई प्रशिक्षित व्यक्ति नहीं?</t>
+          <t>सबसे हाल के जन्म के लिए, क्या डिलीवरी से पहले उनकी कम से कम चार बार जाँच हुई थी?</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Code who CONDUCTED the delivery, not who was in the room. An ASHA or Anganwadi worker accompanying a birth is code 3, not a nurse: NITI counts only a doctor, nurse, ANM or LHV as skilled. A dai is code 4. If an ANM conducted it and an ASHA brought her, that is 2.</t>
+          <t>Ask the mother herself if she is there. If not, probe: did she go for check-ups before the birth, and about how many times? Four or more is Yes; two or three is No. Do not accept a shrug — ask how many times she went.</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>जिसने डिलीवरी कराई, वही भरिए — जो साथ में थे, वह नहीं। आशा या आँगनवाड़ी कार्यकर्ता साथ गई हो — यह कोड 3 है, नर्स नहीं: नीति आयोग सिर्फ़ डॉक्टर, नर्स, एएनएम या एलएचवी को प्रशिक्षित मानता है। दाई = कोड 4। अगर एएनएम ने कराई और आशा उन्हें लाई थीं, तो कोड 2।</t>
+          <t>अगर माँ वहीं हैं तो उनसे ही पूछिए। नहीं तो कुरेदिए: डिलीवरी से पहले वे जाँच कराने गई थीं, और लगभग कितनी बार? चार या उससे ज़्यादा = हाँ; दो-तीन = नहीं। 'पता नहीं' पर न रुकिए — कितनी बार गईं, यह पूछिए।</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -8488,16 +8488,44 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr"/>
-      <c r="C204" t="inlineStr"/>
-      <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr"/>
-      <c r="H204" t="inlineStr"/>
+          <t>select_one birthattend</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>skilled_birth_attendant</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Who conducted that delivery — a doctor, a nurse or ANM, an ASHA or Anganwadi worker, a dai, or nobody trained?</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>वह डिलीवरी किसने कराई — डॉक्टर, नर्स या एएनएम, आशा या आँगनवाड़ी कार्यकर्ता, दाई, या कोई प्रशिक्षित व्यक्ति नहीं?</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Code who CONDUCTED the delivery, not who was in the room. An ASHA or Anganwadi worker accompanying a birth is code 3, not a nurse: NITI counts only a doctor, nurse, ANM or LHV as skilled. A dai is code 4. If an ANM conducted it and an ASHA brought her, that is 2.</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>जिसने डिलीवरी कराई, वही भरिए — जो साथ में थे, वह नहीं। आशा या आँगनवाड़ी कार्यकर्ता साथ गई हो — यह कोड 3 है, नर्स नहीं: नीति आयोग सिर्फ़ डॉक्टर, नर्स, एएनएम या एलएचवी को प्रशिक्षित मानता है। दाई = कोड 4। अगर एएनएम ने कराई और आशा उन्हें लाई थीं, तो कोड 2।</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>${birth_last_5y} = 1</t>
+        </is>
+      </c>
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr"/>
@@ -8509,24 +8537,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>grp_I</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Module I: Food security, shocks and coping</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>Module I: Food security, shocks and coping</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr"/>
@@ -8537,31 +8553,27 @@
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
-      <c r="O205" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>intro_I</t>
+          <t>grp_I</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Now about food, and about any difficult times in the last year and how your household managed.</t>
+          <t>Module I: Food security, shocks and coping</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>अब खाने के बारे में, और पिछले साल आई किसी मुश्किल के बारे में कि आपके घर ने उसे कैसे सँभाला।</t>
+          <t>Module I: Food security, shocks and coping</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -8574,52 +8586,40 @@
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
-      <c r="O206" t="inlineStr"/>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>select_multiple distress</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>distress_event_last365d</t>
+          <t>intro_I</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>In the last 12 months, did any of these happen — to your household, or to the Yatra route you work on? Check every one that applies.</t>
+          <t>Now about food, and about any difficult times in the last year and how your household managed.</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में इनमें से क्या-क्या हुआ — आपके घर के साथ, या जिस यात्रा मार्ग पर आप काम करते हैं उस पर? जो-जो हुआ, सब चुनिए।</t>
+          <t>अब खाने के बारे में, और पिछले साल आई किसी मुश्किल के बारे में कि आपके घर ने उसे कैसे सँभाला।</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr"/>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>not(selected(., '9') and count-selected(.) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>'Nothing of this kind happened' cannot be ticked with a shock. Choose one or the other.</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>'Nothing of this kind happened' cannot be ticked with a shock. Choose one or the other.</t>
-        </is>
-      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr"/>
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr"/>
@@ -8628,22 +8628,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_multiple distress</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>shock_work_lost_weeks</t>
+          <t>distress_event_last365d</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Thinking of whichever of those hit you hardest — about how many weeks of work did you lose because of it? (0 if none)</t>
+          <t>In the last 12 months, did any of these happen — to your household, or to the Yatra route you work on? Check every one that applies.</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>इनमें से जो सबसे भारी पड़ा — उसके कारण लगभग कितने हफ़्ते का काम छूटा? (कुछ न छूटा हो तो 0)</t>
+          <t>पिछले 12 महीनों में इनमें से क्या-क्या हुआ — आपके घर के साथ, या जिस यात्रा मार्ग पर आप काम करते हैं उस पर? जो-जो हुआ, सब चुनिए।</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -8653,24 +8653,20 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>not(selected(${distress_event_last365d}, '9')) and count-selected(${distress_event_last365d}) &gt; 0</t>
-        </is>
-      </c>
+      <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
-          <t>. &gt;= 0 and . &lt;= 52</t>
+          <t>not(selected(., '9') and count-selected(.) &gt; 1)</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Weeks of work lost must be between 0 and 52.</t>
+          <t>'Nothing of this kind happened' cannot be ticked with a shock. Choose one or the other.</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>हफ़्ते 0 से 52 के बीच होने चाहिए।</t>
+          <t>'Nothing of this kind happened' cannot be ticked with a shock. Choose one or the other.</t>
         </is>
       </c>
       <c r="L208" t="inlineStr"/>
@@ -8686,17 +8682,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>shock_money_spent</t>
+          <t>shock_work_lost_weeks</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>And about how much money did your household have to spend because of it — treatment, repairs, replacing what was lost? (Rs, 0 if nothing)</t>
+          <t>Thinking of whichever of those hit you hardest — about how many weeks of work did you lose because of it? (0 if none)</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>और उसके कारण आपके घर को लगभग कितना पैसा ख़र्च करना पड़ा — इलाज, मरम्मत, जो नुक़सान हुआ उसे पूरा करना? (रुपये, कुछ नहीं तो 0)</t>
+          <t>इनमें से जो सबसे भारी पड़ा — उसके कारण लगभग कितने हफ़्ते का काम छूटा? (कुछ न छूटा हो तो 0)</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -8713,17 +8709,17 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>. &gt;= 0</t>
+          <t>. &gt;= 0 and . &lt;= 52</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>An amount cannot be negative.</t>
+          <t>Weeks of work lost must be between 0 and 52.</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>An amount cannot be negative.</t>
+          <t>हफ़्ते 0 से 52 के बीच होने चाहिए।</t>
         </is>
       </c>
       <c r="L209" t="inlineStr"/>
@@ -8734,22 +8730,22 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>select_one month</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>shock_month</t>
+          <t>shock_money_spent</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>And in which month did that one happen?</t>
+          <t>And about how much money did your household have to spend because of it — treatment, repairs, replacing what was lost? (Rs, 0 if nothing)</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>और वह किस महीने हुआ था?</t>
+          <t>और उसके कारण आपके घर को लगभग कितना पैसा ख़र्च करना पड़ा — इलाज, मरम्मत, जो नुक़सान हुआ उसे पूरा करना? (रुपये, कुछ नहीं तो 0)</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -8764,9 +8760,21 @@
           <t>not(selected(${distress_event_last365d}, '9')) and count-selected(${distress_event_last365d}) &gt; 0</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>An amount cannot be negative.</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>An amount cannot be negative.</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr"/>
       <c r="N210" t="inlineStr"/>
@@ -8775,22 +8783,22 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>select_multiple coping</t>
+          <t>select_one month</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>shock_coping</t>
+          <t>shock_month</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>How did your household manage? Check every one they used.</t>
+          <t>And in which month did that one happen?</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>आपके घर ने कैसे सँभाला? उन्होंने जो-जो किया, सब चुनिए।</t>
+          <t>और वह किस महीने हुआ था?</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
@@ -8805,21 +8813,9 @@
           <t>not(selected(${distress_event_last365d}, '9')) and count-selected(${distress_event_last365d}) &gt; 0</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>not(selected(., '6') and count-selected(.) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>'Paid it out of normal earnings' cannot be ticked with another answer. Choose one or the other.</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>'Paid it out of normal earnings' cannot be ticked with another answer. Choose one or the other.</t>
-        </is>
-      </c>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr"/>
       <c r="N211" t="inlineStr"/>
@@ -8828,22 +8824,22 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_multiple coping</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_yatra_wk</t>
+          <t>shock_coping</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
+          <t>How did your household manage? Check every one they used.</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
+          <t>आपके घर ने कैसे सँभाला? उन्होंने जो-जो किया, सब चुनिए।</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -8853,20 +8849,24 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr"/>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>not(selected(${distress_event_last365d}, '9')) and count-selected(${distress_event_last365d}) &gt; 0</t>
+        </is>
+      </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>. &gt;= 0 and . &lt;= 7</t>
+          <t>not(selected(., '6') and count-selected(.) &gt; 1)</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Must be between 0 and 7 days.</t>
+          <t>'Paid it out of normal earnings' cannot be ticked with another answer. Choose one or the other.</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>0 से 7 दिन के बीच होना चाहिए।</t>
+          <t>'Paid it out of normal earnings' cannot be ticked with another answer. Choose one or the other.</t>
         </is>
       </c>
       <c r="L212" t="inlineStr"/>
@@ -8882,17 +8882,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_offseason_wk</t>
+          <t>cope_less_pref_food_yatra_wk</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -8931,17 +8931,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>cope_borrow_food_yatra_wk</t>
+          <t>cope_less_pref_food_offseason_wk</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
@@ -8980,17 +8980,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>cope_borrow_food_offseason_wk</t>
+          <t>cope_borrow_food_yatra_wk</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -9029,17 +9029,17 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>cope_reduce_meals_yatra_wk</t>
+          <t>cope_borrow_food_offseason_wk</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -9078,17 +9078,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>cope_reduce_meals_offseason_wk</t>
+          <t>cope_reduce_meals_yatra_wk</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -9127,17 +9127,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>cope_reduce_portion_yatra_wk</t>
+          <t>cope_reduce_meals_offseason_wk</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
@@ -9176,17 +9176,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>cope_reduce_portion_offseason_wk</t>
+          <t>cope_reduce_portion_yatra_wk</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -9225,17 +9225,17 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>cope_restrict_adult_yatra_wk</t>
+          <t>cope_reduce_portion_offseason_wk</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -9274,17 +9274,17 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>cope_restrict_adult_offseason_wk</t>
+          <t>cope_restrict_adult_yatra_wk</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -9318,19 +9318,47 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr"/>
-      <c r="C222" t="inlineStr"/>
-      <c r="D222" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>cope_restrict_adult_offseason_wk</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H222" t="inlineStr"/>
-      <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 7</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Must be between 0 and 7 days.</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>0 से 7 दिन के बीच होना चाहिए।</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr"/>
       <c r="N222" t="inlineStr"/>
@@ -9339,24 +9367,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>grp_J</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Module J: Ropeway</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>Module J: Ropeway</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr"/>
@@ -9367,31 +9383,27 @@
       <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr"/>
       <c r="N223" t="inlineStr"/>
-      <c r="O223" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>intro_J</t>
+          <t>grp_J</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Now two questions about the ropeway that has been proposed between Gaurikund and Kedarnath.</t>
+          <t>Module J: Ropeway</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>अब गौरीकुंड से केदारनाथ के बीच जो रोपवे प्रस्तावित है, उस पर दो सवाल।</t>
+          <t>Module J: Ropeway</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
@@ -9404,41 +9416,37 @@
       <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr"/>
       <c r="N224" t="inlineStr"/>
-      <c r="O224" t="inlineStr"/>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>select_one stance</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>ropeway_stance</t>
+          <t>intro_J</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>A ropeway is proposed between Gaurikund and Kedarnath. Are you in favour, neutral, or against?</t>
+          <t>Now two questions about the ropeway that has been proposed between Gaurikund and Kedarnath.</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>गौरीकुंड से केदारनाथ तक रोपवे बनाने की बात चल रही है। आप इसके पक्ष में हैं, बीच में हैं, या ख़िलाफ़ हैं?</t>
+          <t>अब गौरीकुंड से केदारनाथ के बीच जो रोपवे प्रस्तावित है, उस पर दो सवाल।</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>${site} = 1</t>
-        </is>
-      </c>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr"/>
@@ -9450,22 +9458,22 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>select_one ropexp</t>
+          <t>select_one stance</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>ropeway_expect_work</t>
+          <t>ropeway_stance</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>If the ropeway is built, what do you think will happen to your own work? More work for you; less work; about the same; or don't know?</t>
+          <t>A ropeway is proposed between Gaurikund and Kedarnath. Are you in favour, neutral, or against?</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>अगर रोपवे बन गया, तो आपके अपने काम पर क्या असर होगा? मेरे लिए ज़्यादा काम; मेरे लिए कम काम; लगभग वैसा ही; या पता नहीं?</t>
+          <t>गौरीकुंड से केदारनाथ तक रोपवे बनाने की बात चल रही है। आप इसके पक्ष में हैं, बीच में हैं, या ख़िलाफ़ हैं?</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -9491,22 +9499,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>select_one ropjobs</t>
+          <t>select_one ropexp</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>ropeway_expect_jobs</t>
+          <t>ropeway_expect_work</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Who do you think will get most of the jobs the ropeway creates? People from these villages; people from outside the area; nobody will get jobs; or don't know?</t>
+          <t>If the ropeway is built, what do you think will happen to your own work? More work for you; less work; about the same; or don't know?</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>रोपवे में जो नौकरियाँ बनेंगी, वे ज़्यादातर किसे मिलेंगी? इन गाँवों के लोगों को; इलाके के बाहर के लोगों को; किसी को नहीं मिलेंगी; या पता नहीं?</t>
+          <t>अगर रोपवे बन गया, तो आपके अपने काम पर क्या असर होगा? मेरे लिए ज़्यादा काम; मेरे लिए कम काम; लगभग वैसा ही; या पता नहीं?</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -9532,22 +9540,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>select_one ropjobs</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>ropeway_trust</t>
+          <t>ropeway_expect_jobs</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Do you think the ropeway will improve the livelihoods of people here? Yes; no; or don't know?</t>
+          <t>Who do you think will get most of the jobs the ropeway creates? People from these villages; people from outside the area; nobody will get jobs; or don't know?</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>क्या आपको लगता है कि रोपवे से यहाँ के लोगों की रोज़ी-रोटी सुधरेगी? हाँ; नहीं; या पता नहीं?</t>
+          <t>रोपवे में जो नौकरियाँ बनेंगी, वे ज़्यादातर किसे मिलेंगी? इन गाँवों के लोगों को; इलाके के बाहर के लोगों को; किसी को नहीं मिलेंगी; या पता नहीं?</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
@@ -9573,22 +9581,22 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one yndk</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>trek_dependent</t>
+          <t>ropeway_trust</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Is your main work carrying, transporting or guiding people or goods on foot along the pilgrimage trek?</t>
+          <t>Do you think the ropeway will improve the livelihoods of people here? Yes; no; or don't know?</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
+          <t>क्या आपको लगता है कि रोपवे से यहाँ के लोगों की रोज़ी-रोटी सुधरेगी? हाँ; नहीं; या पता नहीं?</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
@@ -9598,7 +9606,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr"/>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>${site} = 1</t>
+        </is>
+      </c>
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr"/>
@@ -9610,15 +9622,31 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr"/>
-      <c r="C230" t="inlineStr"/>
-      <c r="D230" t="inlineStr"/>
+          <t>select_one yn</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>trek_dependent</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Is your main work carrying, transporting or guiding people or goods on foot along the pilgrimage trek?</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr"/>
-      <c r="G230" t="inlineStr"/>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr"/>
@@ -9631,24 +9659,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>grp_K</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr"/>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr"/>
       <c r="G231" t="inlineStr"/>
@@ -9659,31 +9675,27 @@
       <c r="L231" t="inlineStr"/>
       <c r="M231" t="inlineStr"/>
       <c r="N231" t="inlineStr"/>
-      <c r="O231" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>intro_K</t>
+          <t>grp_K</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Now a set of questions about the conditions of your work — hours, pay, contract and so on. These come from a standard list used in many countries, so one or two may not fit your situation. Say so and we will move on.</t>
+          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>अब आपके काम के हालात पर कुछ सवाल — घंटे, मज़दूरी, ठेका वग़ैरह। ये एक बनी-बनाई सूची से हैं जो कई देशों में इस्तेमाल होती है, इसलिए एक-दो सवाल आपकी स्थिति पर शायद ठीक न बैठें। बता दीजिएगा, हम आगे बढ़ जाएँगे।</t>
+          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -9696,44 +9708,36 @@
       <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr"/>
       <c r="N232" t="inlineStr"/>
-      <c r="O232" t="inlineStr"/>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>select_one jobsit</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>job_situation</t>
+          <t>intro_K</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>During the last month, what were you mainly doing? Ask it open and code the closest one; do not read the list out.</t>
+          <t>Now a set of questions about the conditions of your work — hours, pay, contract and so on. These come from a standard list used in many countries, so one or two may not fit your situation. Say so and we will move on.</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>पिछले महीने आप मुख्य रूप से क्या कर रहे थे? खुला पूछें और जो सबसे मिलता हो वह कोड करें; पूरी सूची पढ़कर न सुनाएँ।</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>Code what they were MAINLY doing, by time, over the last month. Work for pay = full-time if it was their main activity on most working days, part-time or occasional if it was picked up here and there around something else. Seasonal preparation (buying stock, repairing tack, bringing animals up) IS working for pay — it is their trade — so code 1 or 2, not 10. Unemployed (8) means looking for work and not finding it; between seasons with work expected is not unemployed. Code 10 is the genuine none: not working, not studying, not looking.</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>Code what they were MAINLY doing, by time, over the last month. Work for pay = full-time if it was their main activity on most working days, part-time or occasional if it was picked up here and there around something else. Seasonal preparation (buying stock, repairing tack, bringing animals up) IS working for pay — it is their trade — so code 1 or 2, not 10. Unemployed (8) means looking for work and not finding it; between seasons with work expected is not unemployed. Code 10 is the genuine none: not working, not studying, not looking.</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>अब आपके काम के हालात पर कुछ सवाल — घंटे, मज़दूरी, ठेका वग़ैरह। ये एक बनी-बनाई सूची से हैं जो कई देशों में इस्तेमाल होती है, इसलिए एक-दो सवाल आपकी स्थिति पर शायद ठीक न बैठें। बता दीजिएगा, हम आगे बढ़ जाएँगे।</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr"/>
@@ -9746,32 +9750,32 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>select_one jobperm</t>
+          <t>select_one jobsit</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>job_permanence</t>
+          <t>job_situation</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
+          <t>During the last month, what were you mainly doing? Ask it open and code the closest one; do not read the list out.</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
+          <t>पिछले महीने आप मुख्य रूप से क्या कर रहे थे? खुला पूछें और जो सबसे मिलता हो वह कोड करें; पूरी सूची पढ़कर न सुनाएँ।</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Both will sound seasonal here — the Yatra closes for everyone. Ask about WITHIN the season. One employer keeps them on for a stretch = Seasonal or temporary. They take work day by day from whoever offers it = Occasional or casual. Self-employed: answer for how their own work runs. On probation and Fixed-term are rare here; do not reach for them.</t>
+          <t>Code what they were MAINLY doing, by time, over the last month. Work for pay = full-time if it was their main activity on most working days, part-time or occasional if it was picked up here and there around something else. Seasonal preparation (buying stock, repairing tack, bringing animals up) IS working for pay — it is their trade — so code 1 or 2, not 10. Unemployed (8) means looking for work and not finding it; between seasons with work expected is not unemployed. Code 10 is the genuine none: not working, not studying, not looking.</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>यहाँ दोनों ही मौसमी लगेंगे — यात्रा तो सबके लिए बंद होती है। मौसम के अंदर की बात पूछिए। एक ही मालिक कुछ समय तक रखे हुए है = मौसमी या अस्थायी। जो भी काम रोज़-रोज़ मिल जाए वह कर लेते हैं = कभी-कभार या दिहाड़ी। अपना काम करने वालों के लिए: उनका अपना काम कैसे चलता है, वह देखिए। परख पर और तय अवधि वाले यहाँ बहुत कम मिलेंगे; इन्हें यूँ ही न चुनें।</t>
+          <t>Code what they were MAINLY doing, by time, over the last month. Work for pay = full-time if it was their main activity on most working days, part-time or occasional if it was picked up here and there around something else. Seasonal preparation (buying stock, repairing tack, bringing animals up) IS working for pay — it is their trade — so code 1 or 2, not 10. Unemployed (8) means looking for work and not finding it; between seasons with work expected is not unemployed. Code 10 is the genuine none: not working, not studying, not looking.</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -9779,11 +9783,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>${job_situation} &lt;= 3</t>
-        </is>
-      </c>
+      <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr"/>
@@ -9795,26 +9795,34 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>select_one contract</t>
+          <t>select_one jobperm</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>contract_status</t>
+          <t>job_permanence</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
+          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
+          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Both will sound seasonal here — the Yatra closes for everyone. Ask about WITHIN the season. One employer keeps them on for a stretch = Seasonal or temporary. They take work day by day from whoever offers it = Occasional or casual. Self-employed: answer for how their own work runs. On probation and Fixed-term are rare here; do not reach for them.</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>यहाँ दोनों ही मौसमी लगेंगे — यात्रा तो सबके लिए बंद होती है। मौसम के अंदर की बात पूछिए। एक ही मालिक कुछ समय तक रखे हुए है = मौसमी या अस्थायी। जो भी काम रोज़-रोज़ मिल जाए वह कर लेते हैं = कभी-कभार या दिहाड़ी। अपना काम करने वालों के लिए: उनका अपना काम कैसे चलता है, वह देखिए। परख पर और तय अवधि वाले यहाँ बहुत कम मिलेंगे; इन्हें यूँ ही न चुनें।</t>
+        </is>
+      </c>
       <c r="G235" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9822,7 +9830,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
+          <t>${job_situation} &lt;= 3</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -9836,22 +9844,22 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one contract</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>workplace_registered</t>
+          <t>contract_status</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
+          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
+          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -9863,7 +9871,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>${job_situation} &lt;= 3</t>
+          <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -9877,22 +9885,22 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>select_one pension</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>pension_contrib</t>
+          <t>workplace_registered</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
+          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
+          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -9904,7 +9912,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
+          <t>${job_situation} &lt;= 3</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -9918,22 +9926,22 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>select_one workins</t>
+          <t>select_one pension</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>work_health_ins</t>
+          <t>pension_contrib</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
+          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
+          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -9959,22 +9967,22 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>select_one workins</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>leave_rights</t>
+          <t>work_health_ins</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
+          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
+          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -10005,17 +10013,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>injured_ever</t>
+          <t>leave_rights</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Have you ever been physically injured at your workplace?</t>
+          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
+          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -10027,7 +10035,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>${job_situation} &lt;= 3</t>
+          <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -10046,17 +10054,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>workplace_injury_12m</t>
+          <t>injured_ever</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>In the last 12 months, was anyone physically injured at your workplace because of work?</t>
+          <t>Have you ever been physically injured at your workplace?</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी?</t>
+          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -10087,17 +10095,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>workplace_death_12m</t>
+          <t>workplace_injury_12m</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>And in the last 12 months, did anyone die at your workplace because of work?</t>
+          <t>In the last 12 months, was anyone physically injured at your workplace because of work?</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>और पिछले 12 महीनों में, क्या आपके काम की जगह पर काम की वजह से किसी की मौत हुई?</t>
+          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी?</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -10128,17 +10136,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>wants_more_work</t>
+          <t>workplace_death_12m</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Would you like to work more hours than you do?</t>
+          <t>And in the last 12 months, did anyone die at your workplace because of work?</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
+          <t>और पिछले 12 महीनों में, क्या आपके काम की जगह पर काम की वजह से किसी की मौत हुई?</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -10150,7 +10158,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>${job_situation} &lt;= 7</t>
+          <t>${job_situation} &lt;= 3</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -10164,22 +10172,22 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yndk</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>more_hours_day</t>
+          <t>wants_more_work</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>On a working day, how many MORE hours would you like to work?</t>
+          <t>Would you like to work more hours than you do?</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
+          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -10191,24 +10199,12 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>${wants_more_work} = 1 or ${job_situation} = 8</t>
-        </is>
-      </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . + ${hours_day_yatra} &lt;= 18</t>
-        </is>
-      </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>Hours wanted plus hours already worked cannot exceed 18 in a day.</t>
-        </is>
-      </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t>Hours wanted plus hours already worked cannot exceed 18 in a day.</t>
-        </is>
-      </c>
+          <t>${job_situation} &lt;= 7</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr"/>
       <c r="M244" t="inlineStr"/>
       <c r="N244" t="inlineStr"/>
@@ -10222,17 +10218,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>months_looked_for_work</t>
+          <t>more_hours_day</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
+          <t>On a working day, how many MORE hours would you like to work?</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
+          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -10244,12 +10240,24 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>${calc_months_no_work} &gt; 0 or ${job_situation} = 8</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
+          <t>${wants_more_work} = 1 or ${job_situation} = 8</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . + ${hours_day_yatra} &lt;= 18</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>Hours wanted plus hours already worked cannot exceed 18 in a day.</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Hours wanted plus hours already worked cannot exceed 18 in a day.</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr"/>
       <c r="M245" t="inlineStr"/>
       <c r="N245" t="inlineStr"/>
@@ -10258,22 +10266,22 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>first_job_ever</t>
+          <t>months_looked_for_work</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Was your current work the first paid job you ever had?</t>
+          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
+          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -10283,7 +10291,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr"/>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>${calc_months_no_work} &gt; 0 or ${job_situation} = 8</t>
+        </is>
+      </c>
       <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr"/>
@@ -10300,17 +10312,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>higher_ed</t>
+          <t>first_job_ever</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Have you completed any college, diploma or university course?</t>
+          <t>Was your current work the first paid job you ever had?</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>क्या आपने कॉलेज, डिप्लोमा या यूनिवर्सिटी का कोई कोर्स पूरा किया है?</t>
+          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -10320,11 +10332,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>${job_situation} &lt;= 3</t>
-        </is>
-      </c>
+      <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr"/>
@@ -10341,17 +10349,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>social_security_any</t>
+          <t>higher_ed</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Are you enrolled in any pension, insurance or social-security scheme? For example, EPFO or PM-SYM pension, or Ayushman Bharat health cover.</t>
+          <t>Have you completed any college, diploma or university course?</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>क्या आप किसी पेंशन, बीमा या सरकारी सामाजिक सुरक्षा योजना में शामिल हैं? जैसे EPFO या PM-SYM पेंशन, या आयुष्मान भारत स्वास्थ्य कवर।</t>
+          <t>क्या आपने कॉलेज, डिप्लोमा या यूनिवर्सिटी का कोई कोर्स पूरा किया है?</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -10382,17 +10390,17 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>intens_speed</t>
+          <t>social_security_any</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you work at very high speed?</t>
+          <t>Are you enrolled in any pension, insurance or social-security scheme? For example, EPFO or PM-SYM pension, or Ayushman Bharat health cover.</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप बहुत तेज़ रफ़्तार से काम करते हैं?</t>
+          <t>क्या आप किसी पेंशन, बीमा या सरकारी सामाजिक सुरक्षा योजना में शामिल हैं? जैसे EPFO या PM-SYM पेंशन, या आयुष्मान भारत स्वास्थ्य कवर।</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
@@ -10423,17 +10431,17 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>intens_deadline</t>
+          <t>intens_speed</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you work to tight deadlines?</t>
+          <t>For more than half of your working day, do you work at very high speed?</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आपको कड़ी समय-सीमा में काम करना पड़ता है?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप बहुत तेज़ रफ़्तार से काम करते हैं?</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -10464,17 +10472,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>intens_time</t>
+          <t>intens_deadline</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you not have enough time to finish your tasks?</t>
+          <t>For more than half of your working day, do you work to tight deadlines?</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आपके पास काम पूरा करने के लिए काफ़ी समय नहीं होता?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आपको कड़ी समय-सीमा में काम करना पड़ता है?</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -10505,17 +10513,17 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>posture_position</t>
+          <t>intens_time</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you work in a tiring or painful position?</t>
+          <t>For more than half of your working day, do you not have enough time to finish your tasks?</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप थकाने वाली या दर्द वाली स्थिति में काम करते हैं?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आपके पास काम पूरा करने के लिए काफ़ी समय नहीं होता?</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -10546,17 +10554,17 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>posture_loads</t>
+          <t>posture_position</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you carry or move heavy loads?</t>
+          <t>For more than half of your working day, do you work in a tiring or painful position?</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप भारी बोझ उठाते या ढोते हैं?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप थकाने वाली या दर्द वाली स्थिति में काम करते हैं?</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -10587,17 +10595,17 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>posture_repetitive</t>
+          <t>posture_loads</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you make the same movements again and again?</t>
+          <t>For more than half of your working day, do you carry or move heavy loads?</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप एक ही तरह की हरकत बार-बार करते हैं?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप भारी बोझ उठाते या ढोते हैं?</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -10628,17 +10636,17 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>phys_noise</t>
+          <t>posture_repetitive</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>For more than half of your working day, are you exposed to loud noise?</t>
+          <t>For more than half of your working day, do you make the same movements again and again?</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप तेज़ शोर में रहते हैं?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप एक ही तरह की हरकत बार-बार करते हैं?</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
@@ -10669,17 +10677,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>phys_temperature</t>
+          <t>phys_noise</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>For more than half of your working day, are you exposed to extreme heat or cold?</t>
+          <t>For more than half of your working day, are you exposed to loud noise?</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप बहुत गर्मी या बहुत ठंड में रहते हैं?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप तेज़ शोर में रहते हैं?</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -10705,16 +10713,36 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr"/>
-      <c r="C257" t="inlineStr"/>
-      <c r="D257" t="inlineStr"/>
+          <t>select_one yndk</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>phys_temperature</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>For more than half of your working day, are you exposed to extreme heat or cold?</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप बहुत गर्मी या बहुत ठंड में रहते हैं?</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr"/>
-      <c r="H257" t="inlineStr"/>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>${job_situation} &lt;= 3</t>
+        </is>
+      </c>
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr"/>
@@ -10726,24 +10754,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>grp_L</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Module L: Tasks and skills (short block)</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>Module L: Tasks and skills (short block)</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr"/>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr"/>
@@ -10754,31 +10770,27 @@
       <c r="L258" t="inlineStr"/>
       <c r="M258" t="inlineStr"/>
       <c r="N258" t="inlineStr"/>
-      <c r="O258" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>intro_L</t>
+          <t>grp_L</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Last, I will read out some kinds of work-tasks and ask whether you do them. There is no right or wrong answer — we are trying to understand what skills the work here actually uses.</t>
+          <t>Module L: Tasks and skills (short block)</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>आख़िर में, मैं कुछ तरह के कामों के नाम पढ़ूँगा और पूछूँगा कि आप वे करते हैं या नहीं। इसमें सही या ग़लत जवाब कुछ नहीं है — हम बस यह समझना चाहते हैं कि यहाँ के काम में कौन-कौन से हुनर लगते हैं।</t>
+          <t>Module L: Tasks and skills (short block)</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
@@ -10791,36 +10803,36 @@
       <c r="L259" t="inlineStr"/>
       <c r="M259" t="inlineStr"/>
       <c r="N259" t="inlineStr"/>
-      <c r="O259" t="inlineStr"/>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>select_one task3</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>tk_load</t>
+          <t>intro_L</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you load, unload, stack or count goods? </t>
+          <t>Last, I will read out some kinds of work-tasks and ask whether you do them. There is no right or wrong answer — we are trying to understand what skills the work here actually uses.</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>आख़िर में, मैं कुछ तरह के कामों के नाम पढ़ूँगा और पूछूँगा कि आप वे करते हैं या नहीं। इसमें सही या ग़लत जवाब कुछ नहीं है — हम बस यह समझना चाहते हैं कि यहाँ के काम में कौन-कौन से हुनर लगते हैं।</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr"/>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr"/>
@@ -10838,17 +10850,17 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>tk_drive</t>
+          <t>tk_load</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you drive a motor vehicle? </t>
+          <t xml:space="preserve">Do you load, unload, stack or count goods? </t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
@@ -10875,17 +10887,17 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>tk_engine</t>
+          <t>tk_drive</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you operate an engine or machine? </t>
+          <t xml:space="preserve">Do you drive a motor vehicle? </t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
@@ -10912,17 +10924,17 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>tk_electric</t>
+          <t>tk_engine</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you do electrical or wiring work? </t>
+          <t xml:space="preserve">Do you operate an engine or machine? </t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E263" t="inlineStr"/>
@@ -10949,17 +10961,17 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>tk_safety</t>
+          <t>tk_electric</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you check equipment or the route for safety? </t>
+          <t xml:space="preserve">Do you do electrical or wiring work? </t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
@@ -10986,17 +10998,17 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>tk_sell</t>
+          <t>tk_safety</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you sell goods or services? </t>
+          <t xml:space="preserve">Do you check equipment or the route for safety? </t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E265" t="inlineStr"/>
@@ -11023,17 +11035,17 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>tk_cash</t>
+          <t>tk_sell</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you handle cash and payments? </t>
+          <t xml:space="preserve">Do you sell goods or services? </t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E266" t="inlineStr"/>
@@ -11060,17 +11072,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>tk_cook</t>
+          <t>tk_cash</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you cook or prepare food or drink? </t>
+          <t xml:space="preserve">Do you handle cash and payments? </t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -11097,17 +11109,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>tk_serve</t>
+          <t>tk_cook</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you serve guests or customers? </t>
+          <t xml:space="preserve">Do you cook or prepare food or drink? </t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -11134,17 +11146,17 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>tk_clean</t>
+          <t>tk_serve</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you clean rooms or public areas? </t>
+          <t xml:space="preserve">Do you serve guests or customers? </t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E269" t="inlineStr"/>
@@ -11171,17 +11183,17 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>tk_guide</t>
+          <t>tk_clean</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you guide or explain things to visitors? </t>
+          <t xml:space="preserve">Do you clean rooms or public areas? </t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
@@ -11208,17 +11220,17 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>tk_coord</t>
+          <t>tk_guide</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you coordinate work by phone, radio or signals? </t>
+          <t xml:space="preserve">Do you guide or explain things to visitors? </t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E271" t="inlineStr"/>
@@ -11240,22 +11252,22 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one task3</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>drove_twowheeler</t>
+          <t>tk_coord</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
+          <t xml:space="preserve">Do you coordinate work by phone, radio or signals? </t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
+          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E272" t="inlineStr"/>
@@ -11265,11 +11277,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>${tk_drive} = 1 or ${tk_drive} = 2</t>
-        </is>
-      </c>
+      <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr"/>
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr"/>
@@ -11286,17 +11294,17 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>drove_car</t>
+          <t>drove_twowheeler</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>... a car or jeep?</t>
+          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>...कार या जीप?</t>
+          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
         </is>
       </c>
       <c r="E273" t="inlineStr"/>
@@ -11327,17 +11335,17 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>drove_heavy</t>
+          <t>drove_car</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>... a truck or bus?</t>
+          <t>... a car or jeep?</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>...ट्रक या बस?</t>
+          <t>...कार या जीप?</t>
         </is>
       </c>
       <c r="E274" t="inlineStr"/>
@@ -11368,17 +11376,17 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>read_at_work</t>
+          <t>drove_heavy</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
+          <t>... a truck or bus?</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
+          <t>...ट्रक या बस?</t>
         </is>
       </c>
       <c r="E275" t="inlineStr"/>
@@ -11388,7 +11396,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr"/>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>${tk_drive} = 1 or ${tk_drive} = 2</t>
+        </is>
+      </c>
       <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr"/>
@@ -11405,17 +11417,17 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>calc_at_work</t>
+          <t>read_at_work</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>In your work, do you work out prices or costs?</t>
+          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
+          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
@@ -11437,15 +11449,31 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr"/>
-      <c r="C277" t="inlineStr"/>
-      <c r="D277" t="inlineStr"/>
+          <t>select_one yn</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>calc_at_work</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>In your work, do you work out prices or costs?</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr"/>
-      <c r="G277" t="inlineStr"/>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H277" t="inlineStr"/>
       <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr"/>
@@ -11458,24 +11486,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>grp_M</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>Module M: Access to common resources (short block)</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>Module M: Access to common resources (short block)</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr"/>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr"/>
       <c r="G278" t="inlineStr"/>
@@ -11486,40 +11502,32 @@
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="inlineStr"/>
       <c r="N278" t="inlineStr"/>
-      <c r="O278" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>cpr_firewood</t>
+          <t>grp_M</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>In the last 12 months, did anyone in your household collect firewood or dead wood from common land or forest near here?</t>
+          <t>Module M: Access to common resources (short block)</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने आस-पास की साझा ज़मीन या जंगल से लकड़ी या सूखी टहनियाँ इकट्ठी कीं?</t>
+          <t>Module M: Access to common resources (short block)</t>
         </is>
       </c>
       <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr"/>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr"/>
       <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr"/>
@@ -11527,7 +11535,11 @@
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="inlineStr"/>
       <c r="N279" t="inlineStr"/>
-      <c r="O279" t="inlineStr"/>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -11537,17 +11549,17 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>cpr_fodder</t>
+          <t>cpr_firewood</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>In the last 12 months, did anyone in your household cut grass or fodder from common land near here?</t>
+          <t>In the last 12 months, did anyone in your household collect firewood or dead wood from common land or forest near here?</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने साझा ज़मीन से घास या चारा काटा?</t>
+          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने आस-पास की साझा ज़मीन या जंगल से लकड़ी या सूखी टहनियाँ इकट्ठी कीं?</t>
         </is>
       </c>
       <c r="E280" t="inlineStr"/>
@@ -11574,17 +11586,17 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>cpr_forest_produce</t>
+          <t>cpr_fodder</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>In the last 12 months, did anyone in your household collect herbs, mushrooms or wild fruit from the forest?</t>
+          <t>In the last 12 months, did anyone in your household cut grass or fodder from common land near here?</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने जंगल से जड़ी-बूटी, मशरूम या जंगली फल इकट्ठे किए?</t>
+          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने साझा ज़मीन से घास या चारा काटा?</t>
         </is>
       </c>
       <c r="E281" t="inlineStr"/>
@@ -11611,17 +11623,17 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>cpr_grazing</t>
+          <t>cpr_forest_produce</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>In the last 12 months, did any animal of your household graze on common pasture?</t>
+          <t>In the last 12 months, did anyone in your household collect herbs, mushrooms or wild fruit from the forest?</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर का कोई जानवर साझा चरागाह में चरा?</t>
+          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने जंगल से जड़ी-बूटी, मशरूम या जंगली फल इकट्ठे किए?</t>
         </is>
       </c>
       <c r="E282" t="inlineStr"/>
@@ -11648,17 +11660,17 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>cpr_restricted</t>
+          <t>cpr_grazing</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>In the last 12 months, has anyone in your household been stopped from using a common forest, pasture or path, or been asked to pay to use it?</t>
+          <t>In the last 12 months, did any animal of your household graze on common pasture?</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी को साझा जंगल, चरागाह या रास्ते के इस्तेमाल से रोका गया, या इसके लिए पैसे देने को कहा गया?</t>
+          <t>पिछले 12 महीनों में, क्या आपके घर का कोई जानवर साझा चरागाह में चरा?</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
@@ -11685,17 +11697,17 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>cpr_lost_access</t>
+          <t>cpr_restricted</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>In the last 12 months, has a common place you used to collect from or graze on been closed because of building, road or ropeway work?</t>
+          <t>In the last 12 months, has anyone in your household been stopped from using a common forest, pasture or path, or been asked to pay to use it?</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या कोई साझा जगह, जहाँ आप पहले लकड़ी, घास या चारा लेते थे, निर्माण, सड़क या रोपवे के काम की वजह से बंद हो गई?</t>
+          <t>पिछले 12 महीनों में, क्या आपके घर के किसी को साझा जंगल, चरागाह या रास्ते के इस्तेमाल से रोका गया, या इसके लिए पैसे देने को कहा गया?</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
@@ -11717,22 +11729,22 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>select_one cprwater</t>
+          <t>select_one yndk</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>cpr_water_route</t>
+          <t>cpr_lost_access</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>On your route or near your worksite, can you use a common water source (spring, tap or stream) without paying?</t>
+          <t>In the last 12 months, has a common place you used to collect from or graze on been closed because of building, road or ropeway work?</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>रास्ते पर या काम की जगह के पास, क्या आप कोई साझा पानी का स्रोत (झरना, नल या नदी-नाला) बिना पैसे दिए इस्तेमाल कर सकते हैं?</t>
+          <t>पिछले 12 महीनों में, क्या कोई साझा जगह, जहाँ आप पहले लकड़ी, घास या चारा लेते थे, निर्माण, सड़क या रोपवे के काम की वजह से बंद हो गई?</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
@@ -11754,22 +11766,22 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>select_one cprgov</t>
+          <t>select_one cprwater</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>cpr_governance</t>
+          <t>cpr_water_route</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>In this area, who decides who may use the common land and forest? Ask and code what they name; do not read the list.</t>
+          <t>On your route or near your worksite, can you use a common water source (spring, tap or stream) without paying?</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>इस इलाके की साझा ज़मीन और जंगल का फ़ैसला कौन करता है, कि कौन उसका इस्तेमाल कर सकता है? जो नाम लें वही लिख लें; सूची न पढ़ें।</t>
+          <t>रास्ते पर या काम की जगह के पास, क्या आप कोई साझा पानी का स्रोत (झरना, नल या नदी-नाला) बिना पैसे दिए इस्तेमाल कर सकते हैं?</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
@@ -11791,15 +11803,31 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr"/>
-      <c r="C287" t="inlineStr"/>
-      <c r="D287" t="inlineStr"/>
+          <t>select_one cprgov</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>cpr_governance</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>In this area, who decides who may use the common land and forest? Ask and code what they name; do not read the list.</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>इस इलाके की साझा ज़मीन और जंगल का फ़ैसला कौन करता है, कि कौन उसका इस्तेमाल कर सकता है? जो नाम लें वही लिख लें; सूची न पढ़ें।</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr"/>
-      <c r="G287" t="inlineStr"/>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H287" t="inlineStr"/>
       <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr"/>
@@ -11830,6 +11858,27 @@
       <c r="N288" t="inlineStr"/>
       <c r="O288" t="inlineStr"/>
     </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr"/>
+      <c r="C289" t="inlineStr"/>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr"/>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr"/>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr"/>
+      <c r="J289" t="inlineStr"/>
+      <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr"/>
+      <c r="M289" t="inlineStr"/>
+      <c r="N289" t="inlineStr"/>
+      <c r="O289" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11841,7 +11890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E334"/>
+  <dimension ref="A1:E340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18958,7 +19007,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>wall</t>
+          <t>wageemp</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -18966,12 +19015,12 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Mud, thatch, bamboo or other natural material</t>
+          <t>Private company</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>मिट्टी, फूस, बाँस या ऐसी ही कोई चीज़</t>
+          <t>निजी कंपनी</t>
         </is>
       </c>
       <c r="E310" t="n">
@@ -18981,7 +19030,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>wall</t>
+          <t>wageemp</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -18989,12 +19038,12 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Unburnt brick, wood or tin</t>
+          <t>Government or public body</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>कच्ची ईंट, लकड़ी या टीन</t>
+          <t>सरकारी या सार्वजनिक विभाग</t>
         </is>
       </c>
       <c r="E311" t="n">
@@ -19004,7 +19053,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>wall</t>
+          <t>wageemp</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -19012,12 +19061,12 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Burnt brick, cement, concrete or stone</t>
+          <t>A household (domestic work)</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>पक्की ईंट, सीमेंट, कंक्रीट या पत्थर</t>
+          <t>कोई घर (घरेलू काम)</t>
         </is>
       </c>
       <c r="E312" t="n">
@@ -19027,139 +19076,139 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>wageemp</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Piped into the house or yard</t>
+          <t>A contractor or agent</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>घर या आँगन में नल</t>
+          <t>ठेकेदार या एजेंट</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>wageemp</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Public tap or standpipe</t>
+          <t>An individual employer</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>सार्वजनिक नल या स्टैंडपोस्ट</t>
+          <t>कोई व्यक्ति जो सीधे पैसे देता है</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>wageemp</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>3</v>
+        <v>97</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Handpump, tubewell or borewell</t>
+          <t>Don't know</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>हैंडपंप, ट्यूबवेल या बोरवेल</t>
+          <t>पता नहीं</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>3</v>
+        <v>97</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>wall</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Protected well or protected spring</t>
+          <t>Mud, thatch, bamboo or other natural material</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>ढका हुआ कुआँ या ढका हुआ सोता</t>
+          <t>मिट्टी, फूस, बाँस या ऐसी ही कोई चीज़</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>wall</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Rainwater collection</t>
+          <t>Unburnt brick, wood or tin</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>बारिश का पानी जमा करके</t>
+          <t>कच्ची ईंट, लकड़ी या टीन</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>wall</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Bottled, packaged or community RO</t>
+          <t>Burnt brick, cement, concrete or stone</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>बोतलबंद, पैकेट या सामुदायिक RO</t>
+          <t>पक्की ईंट, सीमेंट, कंक्रीट या पत्थर</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319">
@@ -19169,20 +19218,20 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Unprotected well or unprotected spring</t>
+          <t>Piped into the house or yard</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>खुला कुआँ या खुला सोता</t>
+          <t>घर या आँगन में नल</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320">
@@ -19192,20 +19241,20 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>River, stream, pond or canal</t>
+          <t>Public tap or standpipe</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>नदी, गाड़, तालाब या नहर</t>
+          <t>सार्वजनिक नल या स्टैंडपोस्ट</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="321">
@@ -19215,318 +19264,456 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Tanker truck or cart with drum</t>
+          <t>Handpump, tubewell or borewell</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>टैंकर या ड्रम वाली गाड़ी</t>
+          <t>हैंडपंप, ट्यूबवेल या बोरवेल</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>wgdiff</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>No difficulty</t>
+          <t>Protected well or protected spring</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>कोई दिक़्क़त नहीं</t>
+          <t>ढका हुआ कुआँ या ढका हुआ सोता</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>wgdiff</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Some difficulty</t>
+          <t>Rainwater collection</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>थोड़ी दिक़्क़त</t>
+          <t>बारिश का पानी जमा करके</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>wgdiff</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>A lot of difficulty</t>
+          <t>Bottled, packaged or community RO</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>बहुत दिक़्क़त</t>
+          <t>बोतलबंद, पैकेट या सामुदायिक RO</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>wgdiff</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Cannot do it at all</t>
+          <t>Unprotected well or unprotected spring</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>बिलकुल नहीं कर पाते</t>
+          <t>खुला कुआँ या खुला सोता</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>workins</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Yes, through work</t>
+          <t>River, stream, pond or canal</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>हाँ, काम की तरफ़ से</t>
+          <t>नदी, गाड़, तालाब या नहर</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>workins</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Only private or other insurance</t>
+          <t>Tanker truck or cart with drum</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>सिर्फ़ अपना या कोई और बीमा</t>
+          <t>टैंकर या ड्रम वाली गाड़ी</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>workins</t>
+          <t>wgdiff</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No difficulty</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>कोई नहीं</t>
+          <t>कोई दिक़्क़त नहीं</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>workins</t>
+          <t>wgdiff</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Don't know</t>
+          <t>Some difficulty</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>पता नहीं</t>
+          <t>थोड़ी दिक़्क़त</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>yn</t>
+          <t>wgdiff</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>A lot of difficulty</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>नहीं</t>
+          <t>बहुत दिक़्क़त</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>yn</t>
+          <t>wgdiff</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot do it at all</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>हाँ</t>
+          <t>बिलकुल नहीं कर पाते</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>yndk</t>
+          <t>workins</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes, through work</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>नहीं</t>
+          <t>हाँ, काम की तरफ़ से</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>yndk</t>
+          <t>workins</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only private or other insurance</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>हाँ</t>
+          <t>सिर्फ़ अपना या कोई और बीमा</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
+          <t>workins</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>3</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>कोई नहीं</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>workins</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>4</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Don't know</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>पता नहीं</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>yn</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>0</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>नहीं</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>yn</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>1</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>हाँ</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
           <t>yndk</t>
         </is>
       </c>
-      <c r="B334" t="n">
+      <c r="B338" t="n">
+        <v>0</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>नहीं</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>yndk</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>1</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>हाँ</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>yndk</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
         <v>97</v>
       </c>
-      <c r="C334" t="inlineStr">
+      <c r="C340" t="inlineStr">
         <is>
           <t>Don't know</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr">
+      <c r="D340" t="inlineStr">
         <is>
           <t>पता नहीं</t>
         </is>
       </c>
-      <c r="E334" t="n">
+      <c r="E340" t="n">
         <v>97</v>
       </c>
     </row>

--- a/Kedarnath_final_kobo.xlsx
+++ b/Kedarnath_final_kobo.xlsx
@@ -2005,8 +2005,16 @@
           <t>वे कौन-कौन से काम हैं? जो-जो लागू हो, सब बताइए।</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ENUMERATOR: hauling luggage or goods on the back, shoulders or a head-load, for pilgrims or shops, is code 3 (porter). Carrying a person in a kandi is also code 3; carrying a person on a palanquin as part of a team is code 4. Hauling luggage or goods on a pony or mule is code 1 if the respondent works the animal for someone else, and code 2 if they own it.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>सर्वेक्षक के लिए: पीठ, कंधे या सिर पर सामान या लगेज ढोना (तीर्थयात्रियों या दुकानों के लिए) = कोड 3 (पोर्टर)। कंडी में इंसान ढोना भी कोड 3; पालकी या डंडी टीम में ढोना कोड 4। पोनी या खच्चर पर सामान ढोना: अगर किसी और का जानवर चलाते हैं तो कोड 1, अगर जानवर खुद का है तो कोड 2।</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>yes</t>

--- a/Kedarnath_final_kobo.xlsx
+++ b/Kedarnath_final_kobo.xlsx
@@ -11562,12 +11562,12 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>In the last 12 months, did anyone in your household collect firewood or dead wood from common land or forest near here?</t>
+          <t>In this Yatra season or last Yatra season, did you or anyone staying with you here collect firewood or dead wood from common land or forest in the Yatra region or workplace region?</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने आस-पास की साझा ज़मीन या जंगल से लकड़ी या सूखी टहनियाँ इकट्ठी कीं?</t>
+          <t>इस यात्रा सीज़न या पिछले यात्रा सीज़न में, क्या आपने या आपके साथ यहाँ रहने वाले किसी ने यात्रा क्षेत्र या काम की जगह की साझा ज़मीन या जंगल से लकड़ी या सूखी टहनियाँ इकट्ठी कीं?</t>
         </is>
       </c>
       <c r="E280" t="inlineStr"/>
@@ -11599,12 +11599,12 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>In the last 12 months, did anyone in your household cut grass or fodder from common land near here?</t>
+          <t>In this Yatra season or last Yatra season, did you or anyone staying with you here cut grass or fodder from common land in the Yatra region or workplace region?</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने साझा ज़मीन से घास या चारा काटा?</t>
+          <t>इस यात्रा सीज़न या पिछले यात्रा सीज़न में, क्या आपने या आपके साथ यहाँ रहने वाले किसी ने यात्रा क्षेत्र या काम की जगह की साझा ज़मीन से घास या चारा काटा?</t>
         </is>
       </c>
       <c r="E281" t="inlineStr"/>
@@ -11636,12 +11636,12 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>In the last 12 months, did anyone in your household collect herbs, mushrooms or wild fruit from the forest?</t>
+          <t>In this Yatra season or last Yatra season, did you or anyone staying with you here collect herbs, mushrooms or wild fruit from the forest in the Yatra region or workplace region?</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने जंगल से जड़ी-बूटी, मशरूम या जंगली फल इकट्ठे किए?</t>
+          <t>इस यात्रा सीज़न या पिछले यात्रा सीज़न में, क्या आपने या आपके साथ यहाँ रहने वाले किसी ने यात्रा क्षेत्र या काम की जगह के जंगल से जड़ी-बूटी, मशरूम या जंगली फल इकट्ठे किए?</t>
         </is>
       </c>
       <c r="E282" t="inlineStr"/>
@@ -11673,12 +11673,12 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>In the last 12 months, did any animal of your household graze on common pasture?</t>
+          <t>In this Yatra season or last Yatra season, did any animal of yours or of anyone staying with you here graze on common pasture in the Yatra region or workplace region?</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर का कोई जानवर साझा चरागाह में चरा?</t>
+          <t>इस यात्रा सीज़न या पिछले यात्रा सीज़न में, क्या आपका या आपके साथ यहाँ रहने वाले किसी का कोई जानवर यात्रा क्षेत्र या काम की जगह की साझा चरागाह में चरा?</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
@@ -11710,12 +11710,12 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>In the last 12 months, has anyone in your household been stopped from using a common forest, pasture or path, or been asked to pay to use it?</t>
+          <t>In this Yatra season or last Yatra season, has anyone you or someone staying with you here been stopped from using a common forest, pasture or path, or been asked to pay to use it, in the Yatra region or workplace region?</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी को साझा जंगल, चरागाह या रास्ते के इस्तेमाल से रोका गया, या इसके लिए पैसे देने को कहा गया?</t>
+          <t>इस यात्रा सीज़न या पिछले यात्रा सीज़न में, क्या आपको या आपके साथ यहाँ रहने वाले किसी को यात्रा क्षेत्र या काम की जगह में साझा जंगल, चरागाह या रास्ते के इस्तेमाल से रोका गया, या इसके लिए पैसे देने को कहा गया?</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
@@ -11747,12 +11747,12 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>In the last 12 months, has a common place you used to collect from or graze on been closed because of building, road or ropeway work?</t>
+          <t>In this Yatra season or last Yatra season, has a common place you used to collect from or graze on been closed, because of a landslide, flood, road or bridge damage, or construction work, in the Yatra region or workplace region?</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या कोई साझा जगह, जहाँ आप पहले लकड़ी, घास या चारा लेते थे, निर्माण, सड़क या रोपवे के काम की वजह से बंद हो गई?</t>
+          <t>इस यात्रा सीज़न या पिछले यात्रा सीज़न में, क्या कोई साझा जगह, जहाँ आप पहले लकड़ी, घास या चारा लेते थे, भूस्खलन, बाढ़, सड़क या पुल टूटने, या निर्माण कार्य की वजह से बंद हो गई?</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
@@ -11821,12 +11821,12 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>In this area, who decides who may use the common land and forest? Ask and code what they name; do not read the list.</t>
+          <t>In the Yatra region or workplace region, who decides who may use the common land and forest? Ask and code what they name; do not read the list.</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>इस इलाके की साझा ज़मीन और जंगल का फ़ैसला कौन करता है, कि कौन उसका इस्तेमाल कर सकता है? जो नाम लें वही लिख लें; सूची न पढ़ें।</t>
+          <t>यात्रा क्षेत्र या काम की जगह की साझा ज़मीन और जंगल का फ़ैसला कौन करता है, कि कौन उसका इस्तेमाल कर सकता है? जो नाम लें वही लिख लें; सूची न पढ़ें।</t>
         </is>
       </c>
       <c r="E287" t="inlineStr"/>
